--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -20,7 +20,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -69,8 +69,12 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -105,6 +109,11 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFF8D7DA"/>
         <bgColor rgb="FFDDDDDD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C00000"/>
       </patternFill>
     </fill>
   </fills>
@@ -142,7 +151,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -195,6 +204,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -513,7 +523,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:I1408"/>
+  <dimension ref="A1:K1408"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.54296875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="6" customWidth="1" style="9" min="1" max="1"/>
@@ -524,6 +534,7 @@
     <col width="14" customWidth="1" style="9" min="6" max="6"/>
     <col width="12" customWidth="1" style="9" min="7" max="8"/>
     <col width="16" customWidth="1" style="9" min="9" max="9"/>
+    <col width="10" customWidth="1" style="10" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="10">
@@ -570,6 +581,11 @@
       <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Ойлик_дона (тахлил)</t>
+        </is>
+      </c>
+      <c r="K1" s="18" t="inlineStr">
+        <is>
+          <t>Кузатув</t>
         </is>
       </c>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -564,37 +564,37 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1" s="13">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="16" t="inlineStr">
         <is>
           <t>№</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="16" t="inlineStr">
         <is>
           <t>Товар</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="16" t="inlineStr">
         <is>
           <t>Категория</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="16" t="inlineStr">
         <is>
           <t>ABC</t>
         </is>
       </c>
-      <c r="E1" s="14" t="inlineStr">
+      <c r="E1" s="16" t="inlineStr">
         <is>
           <t>Кунлик_Истеъмол</t>
         </is>
       </c>
-      <c r="F1" s="14" t="inlineStr">
+      <c r="F1" s="16" t="inlineStr">
         <is>
           <t>Асосий_Захира</t>
         </is>
       </c>
-      <c r="G1" s="14" t="inlineStr">
+      <c r="G1" s="16" t="inlineStr">
         <is>
           <t>Цех_Захира</t>
         </is>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="D84" s="20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E84" s="18">
@@ -3116,7 +3116,7 @@
       </c>
       <c r="D92" s="20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E92" s="18">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="D101" s="20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E101" s="18">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="D103" s="20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E103" s="18">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="D145" s="20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E145" s="18">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="D262" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E262" s="18">
@@ -10559,7 +10559,7 @@
       </c>
       <c r="D358" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E358" s="18">
@@ -18457,7 +18457,7 @@
       </c>
       <c r="D640" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E640" s="18">
@@ -19719,7 +19719,7 @@
       </c>
       <c r="D685" s="21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="E685" s="18">

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -4506,39 +4506,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -7827,10 +7827,10 @@
       </c>
       <c r="E134" s="5" t="n">
         <f aca="false">IF((F134+G134)&gt;0,ROUND((F134+G134)/30,2),"")</f>
-        <v>16.67</v>
+        <v>30</v>
       </c>
       <c r="F134" s="5" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="G134" s="5"/>
     </row>
@@ -18360,10 +18360,10 @@
       </c>
       <c r="E613" s="5" t="n">
         <f aca="false">IF((F613+G613)&gt;0,ROUND((F613+G613)/30,2),"")</f>
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F613" s="5" t="n">
-        <v>150</v>
+        <v>300</v>
       </c>
       <c r="G613" s="5"/>
     </row>
@@ -18624,10 +18624,10 @@
       </c>
       <c r="E625" s="5" t="n">
         <f aca="false">IF((F625+G625)&gt;0,ROUND((F625+G625)/30,2),"")</f>
-        <v>3.33</v>
+        <v>16.67</v>
       </c>
       <c r="F625" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G625" s="5"/>
     </row>
@@ -19130,12 +19130,12 @@
       <c r="D648" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E648" s="5" t="n">
+      <c r="E648" s="5" t="str">
         <f aca="false">IF((F648+G648)&gt;0,ROUND((F648+G648)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F648" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G648" s="5"/>
     </row>
@@ -19220,10 +19220,10 @@
       </c>
       <c r="E652" s="5" t="n">
         <f aca="false">IF((F652+G652)&gt;0,ROUND((F652+G652)/30,2),"")</f>
-        <v>6.67</v>
+        <v>16.67</v>
       </c>
       <c r="F652" s="5" t="n">
-        <v>200</v>
+        <v>500</v>
       </c>
       <c r="G652" s="5"/>
     </row>
@@ -19900,12 +19900,12 @@
       <c r="D683" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E683" s="5" t="n">
+      <c r="E683" s="5" t="str">
         <f aca="false">IF((F683+G683)&gt;0,ROUND((F683+G683)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F683" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G683" s="5"/>
     </row>
@@ -20408,10 +20408,10 @@
       </c>
       <c r="E706" s="5" t="n">
         <f aca="false">IF((F706+G706)&gt;0,ROUND((F706+G706)/30,2),"")</f>
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="F706" s="5" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G706" s="5"/>
     </row>
@@ -32925,12 +32925,12 @@
         <v>44</v>
       </c>
       <c r="D1305" s="9"/>
-      <c r="E1305" s="5" t="n">
+      <c r="E1305" s="5" t="str">
         <f aca="false">IF((F1305+G1305)&gt;0,ROUND((F1305+G1305)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1305" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1305" s="5"/>
     </row>
@@ -33067,10 +33067,10 @@
       <c r="D1312" s="9"/>
       <c r="E1312" s="5" t="n">
         <f aca="false">IF((F1312+G1312)&gt;0,ROUND((F1312+G1312)/30,2),"")</f>
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="F1312" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G1312" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3803" uniqueCount="1439">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3806" uniqueCount="1439">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -8089,7 +8089,7 @@
         <v>44</v>
       </c>
       <c r="D146" s="7" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E146" s="5" t="n">
         <f aca="false">IF((F146+G146)&gt;0,ROUND((F146+G146)/30,2),"")</f>
@@ -18620,7 +18620,7 @@
         <v>44</v>
       </c>
       <c r="D625" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E625" s="5" t="n">
         <f aca="false">IF((F625+G625)&gt;0,ROUND((F625+G625)/30,2),"")</f>
@@ -23528,7 +23528,7 @@
         <v>75</v>
       </c>
       <c r="D848" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E848" s="5" t="n">
         <f aca="false">IF((F848+G848)&gt;0,ROUND((F848+G848)/30,2),"")</f>
@@ -23880,7 +23880,7 @@
         <v>75</v>
       </c>
       <c r="D864" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E864" s="5" t="n">
         <f aca="false">IF((F864+G864)&gt;0,ROUND((F864+G864)/30,2),"")</f>
@@ -24232,7 +24232,7 @@
         <v>75</v>
       </c>
       <c r="D880" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E880" s="5" t="n">
         <f aca="false">IF((F880+G880)&gt;0,ROUND((F880+G880)/30,2),"")</f>
@@ -24320,7 +24320,7 @@
         <v>75</v>
       </c>
       <c r="D884" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E884" s="5" t="n">
         <f aca="false">IF((F884+G884)&gt;0,ROUND((F884+G884)/30,2),"")</f>
@@ -24540,7 +24540,7 @@
         <v>75</v>
       </c>
       <c r="D894" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E894" s="5" t="n">
         <f aca="false">IF((F894+G894)&gt;0,ROUND((F894+G894)/30,2),"")</f>
@@ -24650,14 +24650,14 @@
         <v>75</v>
       </c>
       <c r="D899" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E899" s="5" t="n">
         <f aca="false">IF((F899+G899)&gt;0,ROUND((F899+G899)/30,2),"")</f>
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="F899" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G899" s="5"/>
     </row>
@@ -24848,7 +24848,7 @@
         <v>75</v>
       </c>
       <c r="D908" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E908" s="5" t="n">
         <f aca="false">IF((F908+G908)&gt;0,ROUND((F908+G908)/30,2),"")</f>
@@ -24870,7 +24870,7 @@
         <v>75</v>
       </c>
       <c r="D909" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E909" s="5" t="n">
         <f aca="false">IF((F909+G909)&gt;0,ROUND((F909+G909)/30,2),"")</f>
@@ -24958,7 +24958,7 @@
         <v>75</v>
       </c>
       <c r="D913" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E913" s="5" t="n">
         <f aca="false">IF((F913+G913)&gt;0,ROUND((F913+G913)/30,2),"")</f>
@@ -25002,7 +25002,7 @@
         <v>75</v>
       </c>
       <c r="D915" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E915" s="5" t="n">
         <f aca="false">IF((F915+G915)&gt;0,ROUND((F915+G915)/30,2),"")</f>
@@ -25090,7 +25090,7 @@
         <v>75</v>
       </c>
       <c r="D919" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E919" s="5" t="n">
         <f aca="false">IF((F919+G919)&gt;0,ROUND((F919+G919)/30,2),"")</f>
@@ -34084,7 +34084,9 @@
       <c r="C1363" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D1363" s="9"/>
+      <c r="D1363" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="E1363" s="5" t="n">
         <f aca="false">IF((F1363+G1363)&gt;0,ROUND((F1363+G1363)/30,2),"")</f>
         <v>1.67</v>
@@ -34424,13 +34426,15 @@
       <c r="C1380" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D1380" s="9"/>
+      <c r="D1380" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="E1380" s="5" t="n">
         <f aca="false">IF((F1380+G1380)&gt;0,ROUND((F1380+G1380)/30,2),"")</f>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="F1380" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G1380" s="5"/>
     </row>
@@ -34724,7 +34728,9 @@
       <c r="C1395" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="D1395" s="9"/>
+      <c r="D1395" s="9" t="s">
+        <v>12</v>
+      </c>
       <c r="E1395" s="5" t="n">
         <f aca="false">IF((F1395+G1395)&gt;0,ROUND((F1395+G1395)/30,2),"")</f>
         <v>0.67</v>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -8881,14 +8881,14 @@
         <v>75</v>
       </c>
       <c r="D182" s="7" t="s">
-        <v>91</v>
+        <v>12</v>
       </c>
       <c r="E182" s="5" t="n">
         <f aca="false">IF((F182+G182)&gt;0,ROUND((F182+G182)/30,2),"")</f>
-        <v>3.33</v>
+        <v>33.33</v>
       </c>
       <c r="F182" s="5" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="G182" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -8729,12 +8729,12 @@
       <c r="D175" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E175" s="5" t="n">
+      <c r="E175" s="5" t="str">
         <f aca="false">IF((F175+G175)&gt;0,ROUND((F175+G175)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F175" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G175" s="5"/>
     </row>
@@ -8817,12 +8817,12 @@
       <c r="D179" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E179" s="5" t="n">
+      <c r="E179" s="5" t="str">
         <f aca="false">IF((F179+G179)&gt;0,ROUND((F179+G179)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F179" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G179" s="5"/>
     </row>
@@ -18382,10 +18382,10 @@
       </c>
       <c r="E614" s="5" t="n">
         <f aca="false">IF((F614+G614)&gt;0,ROUND((F614+G614)/30,2),"")</f>
-        <v>16.67</v>
+        <v>23.33</v>
       </c>
       <c r="F614" s="5" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G614" s="5"/>
     </row>
@@ -18578,12 +18578,12 @@
       <c r="D623" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E623" s="5" t="n">
+      <c r="E623" s="5" t="str">
         <f aca="false">IF((F623+G623)&gt;0,ROUND((F623+G623)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F623" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G623" s="5"/>
     </row>
@@ -19174,12 +19174,12 @@
       <c r="D650" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E650" s="5" t="n">
+      <c r="E650" s="5" t="str">
         <f aca="false">IF((F650+G650)&gt;0,ROUND((F650+G650)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F650" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G650" s="5"/>
     </row>
@@ -19196,12 +19196,12 @@
       <c r="D651" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E651" s="5" t="n">
+      <c r="E651" s="5" t="str">
         <f aca="false">IF((F651+G651)&gt;0,ROUND((F651+G651)/30,2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="F651" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G651" s="5"/>
     </row>
@@ -19680,12 +19680,12 @@
       <c r="D673" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E673" s="5" t="n">
+      <c r="E673" s="5" t="str">
         <f aca="false">IF((F673+G673)&gt;0,ROUND((F673+G673)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F673" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G673" s="5"/>
     </row>
@@ -19922,12 +19922,12 @@
       <c r="D684" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E684" s="5" t="n">
+      <c r="E684" s="5" t="str">
         <f aca="false">IF((F684+G684)&gt;0,ROUND((F684+G684)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F684" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G684" s="5"/>
     </row>
@@ -20054,12 +20054,12 @@
       <c r="D690" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E690" s="5" t="n">
+      <c r="E690" s="5" t="str">
         <f aca="false">IF((F690+G690)&gt;0,ROUND((F690+G690)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F690" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G690" s="5"/>
     </row>
@@ -20340,12 +20340,12 @@
       <c r="D703" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E703" s="5" t="n">
+      <c r="E703" s="5" t="str">
         <f aca="false">IF((F703+G703)&gt;0,ROUND((F703+G703)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F703" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G703" s="5"/>
     </row>
@@ -20384,12 +20384,12 @@
       <c r="D705" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E705" s="5" t="n">
+      <c r="E705" s="5" t="str">
         <f aca="false">IF((F705+G705)&gt;0,ROUND((F705+G705)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F705" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G705" s="5"/>
     </row>
@@ -20626,12 +20626,12 @@
       <c r="D716" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E716" s="5" t="n">
+      <c r="E716" s="5" t="str">
         <f aca="false">IF((F716+G716)&gt;0,ROUND((F716+G716)/30,2),"")</f>
-        <v>8.33</v>
+        <v/>
       </c>
       <c r="F716" s="5" t="n">
-        <v>250</v>
+        <v>0</v>
       </c>
       <c r="G716" s="5"/>
     </row>
@@ -20714,12 +20714,12 @@
       <c r="D720" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E720" s="5" t="n">
+      <c r="E720" s="5" t="str">
         <f aca="false">IF((F720+G720)&gt;0,ROUND((F720+G720)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F720" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G720" s="5"/>
     </row>
@@ -24080,12 +24080,12 @@
       <c r="D873" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E873" s="5" t="n">
+      <c r="E873" s="5" t="str">
         <f aca="false">IF((F873+G873)&gt;0,ROUND((F873+G873)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F873" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G873" s="5"/>
     </row>
@@ -24212,12 +24212,12 @@
       <c r="D879" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E879" s="5" t="n">
+      <c r="E879" s="5" t="str">
         <f aca="false">IF((F879+G879)&gt;0,ROUND((F879+G879)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F879" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G879" s="5"/>
     </row>
@@ -26719,12 +26719,12 @@
         <v>17</v>
       </c>
       <c r="D995" s="9"/>
-      <c r="E995" s="5" t="n">
+      <c r="E995" s="5" t="str">
         <f aca="false">IF((F995+G995)&gt;0,ROUND((F995+G995)/30,2),"")</f>
-        <v>13.33</v>
+        <v/>
       </c>
       <c r="F995" s="5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G995" s="5"/>
     </row>
@@ -32183,12 +32183,12 @@
         <v>44</v>
       </c>
       <c r="D1268" s="9"/>
-      <c r="E1268" s="5" t="n">
+      <c r="E1268" s="5" t="str">
         <f aca="false">IF((F1268+G1268)&gt;0,ROUND((F1268+G1268)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1268" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1268" s="5"/>
     </row>
@@ -32203,12 +32203,12 @@
         <v>44</v>
       </c>
       <c r="D1269" s="9"/>
-      <c r="E1269" s="5" t="n">
+      <c r="E1269" s="5" t="str">
         <f aca="false">IF((F1269+G1269)&gt;0,ROUND((F1269+G1269)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1269" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1269" s="5"/>
     </row>
@@ -32223,12 +32223,12 @@
         <v>44</v>
       </c>
       <c r="D1270" s="9"/>
-      <c r="E1270" s="5" t="n">
+      <c r="E1270" s="5" t="str">
         <f aca="false">IF((F1270+G1270)&gt;0,ROUND((F1270+G1270)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1270" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1270" s="5"/>
     </row>
@@ -32343,12 +32343,12 @@
         <v>44</v>
       </c>
       <c r="D1276" s="9"/>
-      <c r="E1276" s="5" t="n">
+      <c r="E1276" s="5" t="str">
         <f aca="false">IF((F1276+G1276)&gt;0,ROUND((F1276+G1276)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1276" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1276" s="5"/>
     </row>
@@ -32383,12 +32383,12 @@
         <v>44</v>
       </c>
       <c r="D1278" s="9"/>
-      <c r="E1278" s="5" t="n">
+      <c r="E1278" s="5" t="str">
         <f aca="false">IF((F1278+G1278)&gt;0,ROUND((F1278+G1278)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1278" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1278" s="5"/>
     </row>
@@ -32403,12 +32403,12 @@
         <v>44</v>
       </c>
       <c r="D1279" s="9"/>
-      <c r="E1279" s="5" t="n">
+      <c r="E1279" s="5" t="str">
         <f aca="false">IF((F1279+G1279)&gt;0,ROUND((F1279+G1279)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1279" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1279" s="5"/>
     </row>
@@ -32423,12 +32423,12 @@
         <v>44</v>
       </c>
       <c r="D1280" s="9"/>
-      <c r="E1280" s="5" t="n">
+      <c r="E1280" s="5" t="str">
         <f aca="false">IF((F1280+G1280)&gt;0,ROUND((F1280+G1280)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1280" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1280" s="5"/>
     </row>
@@ -32583,12 +32583,12 @@
         <v>44</v>
       </c>
       <c r="D1288" s="9"/>
-      <c r="E1288" s="5" t="n">
+      <c r="E1288" s="5" t="str">
         <f aca="false">IF((F1288+G1288)&gt;0,ROUND((F1288+G1288)/30,2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="F1288" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G1288" s="5"/>
     </row>
@@ -32785,12 +32785,12 @@
         <v>44</v>
       </c>
       <c r="D1298" s="9"/>
-      <c r="E1298" s="5" t="n">
+      <c r="E1298" s="5" t="str">
         <f aca="false">IF((F1298+G1298)&gt;0,ROUND((F1298+G1298)/30,2),"")</f>
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="F1298" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G1298" s="5"/>
     </row>
@@ -32805,12 +32805,12 @@
         <v>44</v>
       </c>
       <c r="D1299" s="9"/>
-      <c r="E1299" s="5" t="n">
+      <c r="E1299" s="5" t="str">
         <f aca="false">IF((F1299+G1299)&gt;0,ROUND((F1299+G1299)/30,2),"")</f>
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="F1299" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G1299" s="5"/>
     </row>
@@ -32985,12 +32985,12 @@
         <v>44</v>
       </c>
       <c r="D1308" s="9"/>
-      <c r="E1308" s="5" t="n">
+      <c r="E1308" s="5" t="str">
         <f aca="false">IF((F1308+G1308)&gt;0,ROUND((F1308+G1308)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1308" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1308" s="5"/>
     </row>
@@ -33005,12 +33005,12 @@
         <v>44</v>
       </c>
       <c r="D1309" s="9"/>
-      <c r="E1309" s="5" t="n">
+      <c r="E1309" s="5" t="str">
         <f aca="false">IF((F1309+G1309)&gt;0,ROUND((F1309+G1309)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1309" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1309" s="5"/>
     </row>
@@ -34127,12 +34127,12 @@
         <v>75</v>
       </c>
       <c r="D1365" s="9"/>
-      <c r="E1365" s="5" t="n">
+      <c r="E1365" s="5" t="str">
         <f aca="false">IF((F1365+G1365)&gt;0,ROUND((F1365+G1365)/30,2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="F1365" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G1365" s="5"/>
     </row>
@@ -34267,12 +34267,12 @@
         <v>75</v>
       </c>
       <c r="D1372" s="9"/>
-      <c r="E1372" s="5" t="n">
+      <c r="E1372" s="5" t="str">
         <f aca="false">IF((F1372+G1372)&gt;0,ROUND((F1372+G1372)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F1372" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G1372" s="5"/>
     </row>
@@ -34347,12 +34347,12 @@
         <v>75</v>
       </c>
       <c r="D1376" s="9"/>
-      <c r="E1376" s="5" t="n">
+      <c r="E1376" s="5" t="str">
         <f aca="false">IF((F1376+G1376)&gt;0,ROUND((F1376+G1376)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1376" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1376" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -22916,10 +22916,10 @@
       </c>
       <c r="E820" s="5" t="n">
         <f aca="false">IF((F820+G820)&gt;0,ROUND((F820+G820)/30,2),"")</f>
-        <v>26.67</v>
+        <v>16.67</v>
       </c>
       <c r="F820" s="5" t="n">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="G820" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -8597,12 +8597,12 @@
       <c r="D169" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E169" s="5" t="n">
+      <c r="E169" s="5" t="str">
         <f aca="false">IF((F169+G169)&gt;0,ROUND((F169+G169)/30,2),"")</f>
-        <v>50</v>
+        <v/>
       </c>
       <c r="F169" s="5" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="G169" s="5"/>
     </row>
@@ -8665,10 +8665,10 @@
       </c>
       <c r="E172" s="5" t="n">
         <f aca="false">IF((F172+G172)&gt;0,ROUND((F172+G172)/30,2),"")</f>
-        <v>66.67</v>
+        <v>100</v>
       </c>
       <c r="F172" s="5" t="n">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="G172" s="5"/>
     </row>
@@ -23070,10 +23070,10 @@
       </c>
       <c r="E827" s="5" t="n">
         <f aca="false">IF((F827+G827)&gt;0,ROUND((F827+G827)/30,2),"")</f>
-        <v>83.33</v>
+        <v>66.67</v>
       </c>
       <c r="F827" s="5" t="n">
-        <v>2500</v>
+        <v>2000</v>
       </c>
       <c r="G827" s="5"/>
     </row>
@@ -23334,10 +23334,10 @@
       </c>
       <c r="E839" s="5" t="n">
         <f aca="false">IF((F839+G839)&gt;0,ROUND((F839+G839)/30,2),"")</f>
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="F839" s="5" t="n">
-        <v>500</v>
+        <v>600</v>
       </c>
       <c r="G839" s="5"/>
     </row>
@@ -23508,12 +23508,12 @@
       <c r="D847" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E847" s="5" t="n">
+      <c r="E847" s="5" t="str">
         <f aca="false">IF((F847+G847)&gt;0,ROUND((F847+G847)/30,2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="F847" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G847" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -8093,10 +8093,10 @@
       </c>
       <c r="E146" s="5" t="n">
         <f aca="false">IF((F146+G146)&gt;0,ROUND((F146+G146)/30,2),"")</f>
-        <v>10</v>
+        <v>16.67</v>
       </c>
       <c r="F146" s="5" t="n">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="G146" s="5"/>
     </row>
@@ -8115,10 +8115,10 @@
       </c>
       <c r="E147" s="5" t="n">
         <f aca="false">IF((F147+G147)&gt;0,ROUND((F147+G147)/30,2),"")</f>
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F147" s="5" t="n">
-        <v>150</v>
+        <v>600</v>
       </c>
       <c r="G147" s="5"/>
     </row>
@@ -18534,12 +18534,12 @@
       <c r="D621" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E621" s="5" t="n">
+      <c r="E621" s="5" t="str">
         <f aca="false">IF((F621+G621)&gt;0,ROUND((F621+G621)/30,2),"")</f>
-        <v>13.33</v>
+        <v/>
       </c>
       <c r="F621" s="5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G621" s="5"/>
     </row>
@@ -19506,10 +19506,10 @@
       </c>
       <c r="E665" s="5" t="n">
         <f aca="false">IF((F665+G665)&gt;0,ROUND((F665+G665)/30,2),"")</f>
-        <v>13.33</v>
+        <v>6.67</v>
       </c>
       <c r="F665" s="5" t="n">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="G665" s="5"/>
     </row>
@@ -19856,12 +19856,12 @@
       <c r="D681" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E681" s="5" t="n">
+      <c r="E681" s="5" t="str">
         <f aca="false">IF((F681+G681)&gt;0,ROUND((F681+G681)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F681" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G681" s="5"/>
     </row>
@@ -20186,12 +20186,12 @@
       <c r="D696" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E696" s="5" t="n">
+      <c r="E696" s="5" t="str">
         <f aca="false">IF((F696+G696)&gt;0,ROUND((F696+G696)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F696" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G696" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -7759,12 +7759,12 @@
       <c r="D131" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E131" s="5" t="n">
+      <c r="E131" s="5" t="str">
         <f aca="false">IF((F131+G131)&gt;0,ROUND((F131+G131)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F131" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G131" s="5"/>
     </row>
@@ -7959,10 +7959,10 @@
       </c>
       <c r="E140" s="5" t="n">
         <f aca="false">IF((F140+G140)&gt;0,ROUND((F140+G140)/30,2),"")</f>
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>1350</v>
+        <v>1500</v>
       </c>
       <c r="G140" s="5"/>
     </row>
@@ -7979,12 +7979,12 @@
       <c r="D141" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E141" s="5" t="n">
+      <c r="E141" s="5" t="str">
         <f aca="false">IF((F141+G141)&gt;0,ROUND((F141+G141)/30,2),"")</f>
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="F141" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G141" s="5"/>
     </row>
@@ -8001,12 +8001,12 @@
       <c r="D142" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E142" s="5" t="n">
+      <c r="E142" s="5" t="str">
         <f aca="false">IF((F142+G142)&gt;0,ROUND((F142+G142)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F142" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G142" s="5"/>
     </row>
@@ -8047,10 +8047,10 @@
       </c>
       <c r="E144" s="5" t="n">
         <f aca="false">IF((F144+G144)&gt;0,ROUND((F144+G144)/30,2),"")</f>
-        <v>16.67</v>
+        <v>23.33</v>
       </c>
       <c r="F144" s="5" t="n">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="G144" s="5"/>
     </row>
@@ -8643,10 +8643,10 @@
       </c>
       <c r="E171" s="5" t="n">
         <f aca="false">IF((F171+G171)&gt;0,ROUND((F171+G171)/30,2),"")</f>
-        <v>5</v>
+        <v>16.67</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="G171" s="5"/>
     </row>
@@ -8685,12 +8685,12 @@
       <c r="D173" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E173" s="5" t="n">
+      <c r="E173" s="5" t="str">
         <f aca="false">IF((F173+G173)&gt;0,ROUND((F173+G173)/30,2),"")</f>
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="F173" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G173" s="5"/>
     </row>
@@ -8707,12 +8707,12 @@
       <c r="D174" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="E174" s="5" t="n">
+      <c r="E174" s="5" t="str">
         <f aca="false">IF((F174+G174)&gt;0,ROUND((F174+G174)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F174" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G174" s="5"/>
     </row>
@@ -8753,10 +8753,10 @@
       </c>
       <c r="E176" s="5" t="n">
         <f aca="false">IF((F176+G176)&gt;0,ROUND((F176+G176)/30,2),"")</f>
-        <v>23.33</v>
+        <v>33.33</v>
       </c>
       <c r="F176" s="5" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="G176" s="5"/>
     </row>
@@ -8797,10 +8797,10 @@
       </c>
       <c r="E178" s="5" t="n">
         <f aca="false">IF((F178+G178)&gt;0,ROUND((F178+G178)/30,2),"")</f>
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="F178" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G178" s="5"/>
     </row>
@@ -8863,10 +8863,10 @@
       </c>
       <c r="E181" s="5" t="n">
         <f aca="false">IF((F181+G181)&gt;0,ROUND((F181+G181)/30,2),"")</f>
-        <v>6.67</v>
+        <v>8.33</v>
       </c>
       <c r="F181" s="5" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G181" s="5"/>
     </row>
@@ -11602,12 +11602,12 @@
       <c r="D306" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E306" s="5" t="n">
+      <c r="E306" s="5" t="str">
         <f aca="false">IF((F306+G306)&gt;0,ROUND((F306+G306)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F306" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G306" s="5"/>
     </row>
@@ -11780,10 +11780,10 @@
       </c>
       <c r="E314" s="5" t="n">
         <f aca="false">IF((F314+G314)&gt;0,ROUND((F314+G314)/30,2),"")</f>
-        <v>1.67</v>
+        <v>8.33</v>
       </c>
       <c r="F314" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G314" s="5"/>
     </row>
@@ -11956,10 +11956,10 @@
       </c>
       <c r="E322" s="5" t="n">
         <f aca="false">IF((F322+G322)&gt;0,ROUND((F322+G322)/30,2),"")</f>
-        <v>3.33</v>
+        <v>16.67</v>
       </c>
       <c r="F322" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G322" s="5"/>
     </row>
@@ -12064,12 +12064,12 @@
       <c r="D327" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E327" s="5" t="n">
+      <c r="E327" s="5" t="str">
         <f aca="false">IF((F327+G327)&gt;0,ROUND((F327+G327)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F327" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G327" s="5"/>
     </row>
@@ -12108,12 +12108,12 @@
       <c r="D329" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E329" s="5" t="n">
+      <c r="E329" s="5" t="str">
         <f aca="false">IF((F329+G329)&gt;0,ROUND((F329+G329)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F329" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G329" s="5"/>
     </row>
@@ -12592,12 +12592,12 @@
       <c r="D351" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E351" s="5" t="n">
+      <c r="E351" s="5" t="str">
         <f aca="false">IF((F351+G351)&gt;0,ROUND((F351+G351)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F351" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G351" s="5"/>
     </row>
@@ -12946,12 +12946,12 @@
       <c r="D367" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E367" s="5" t="n">
+      <c r="E367" s="5" t="str">
         <f aca="false">IF((F367+G367)&gt;0,ROUND((F367+G367)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F367" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G367" s="5"/>
     </row>
@@ -13080,10 +13080,10 @@
       </c>
       <c r="E373" s="5" t="n">
         <f aca="false">IF((F373+G373)&gt;0,ROUND((F373+G373)/30,2),"")</f>
-        <v>3.33</v>
+        <v>10</v>
       </c>
       <c r="F373" s="5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G373" s="5"/>
     </row>
@@ -13122,12 +13122,12 @@
       <c r="D375" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E375" s="5" t="n">
+      <c r="E375" s="5" t="str">
         <f aca="false">IF((F375+G375)&gt;0,ROUND((F375+G375)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F375" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G375" s="5"/>
     </row>
@@ -13232,12 +13232,12 @@
       <c r="D380" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E380" s="5" t="n">
+      <c r="E380" s="5" t="str">
         <f aca="false">IF((F380+G380)&gt;0,ROUND((F380+G380)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F380" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G380" s="5"/>
     </row>
@@ -13408,12 +13408,12 @@
       <c r="D388" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E388" s="5" t="n">
+      <c r="E388" s="5" t="str">
         <f aca="false">IF((F388+G388)&gt;0,ROUND((F388+G388)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F388" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G388" s="5"/>
     </row>
@@ -13540,12 +13540,12 @@
       <c r="D394" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E394" s="5" t="n">
+      <c r="E394" s="5" t="str">
         <f aca="false">IF((F394+G394)&gt;0,ROUND((F394+G394)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F394" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G394" s="5"/>
     </row>
@@ -13672,12 +13672,12 @@
       <c r="D400" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E400" s="5" t="n">
+      <c r="E400" s="5" t="str">
         <f aca="false">IF((F400+G400)&gt;0,ROUND((F400+G400)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F400" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G400" s="5"/>
     </row>
@@ -13958,12 +13958,12 @@
       <c r="D413" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E413" s="5" t="n">
+      <c r="E413" s="5" t="str">
         <f aca="false">IF((F413+G413)&gt;0,ROUND((F413+G413)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F413" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G413" s="5"/>
     </row>
@@ -15674,12 +15674,12 @@
       <c r="D491" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E491" s="5" t="n">
+      <c r="E491" s="5" t="str">
         <f aca="false">IF((F491+G491)&gt;0,ROUND((F491+G491)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F491" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G491" s="5"/>
     </row>
@@ -15696,12 +15696,12 @@
       <c r="D492" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E492" s="5" t="n">
+      <c r="E492" s="5" t="str">
         <f aca="false">IF((F492+G492)&gt;0,ROUND((F492+G492)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F492" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G492" s="5"/>
     </row>
@@ -15784,12 +15784,12 @@
       <c r="D496" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E496" s="5" t="n">
+      <c r="E496" s="5" t="str">
         <f aca="false">IF((F496+G496)&gt;0,ROUND((F496+G496)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F496" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G496" s="5"/>
     </row>
@@ -16708,12 +16708,12 @@
       <c r="D538" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E538" s="5" t="n">
+      <c r="E538" s="5" t="str">
         <f aca="false">IF((F538+G538)&gt;0,ROUND((F538+G538)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F538" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G538" s="5"/>
     </row>
@@ -16996,10 +16996,10 @@
       </c>
       <c r="E551" s="5" t="n">
         <f aca="false">IF((F551+G551)&gt;0,ROUND((F551+G551)/30,2),"")</f>
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="F551" s="5" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G551" s="5"/>
     </row>
@@ -17104,12 +17104,12 @@
       <c r="D556" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E556" s="5" t="n">
+      <c r="E556" s="5" t="str">
         <f aca="false">IF((F556+G556)&gt;0,ROUND((F556+G556)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F556" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G556" s="5"/>
     </row>
@@ -17214,12 +17214,12 @@
       <c r="D561" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E561" s="5" t="n">
+      <c r="E561" s="5" t="str">
         <f aca="false">IF((F561+G561)&gt;0,ROUND((F561+G561)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F561" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G561" s="5"/>
     </row>
@@ -17236,12 +17236,12 @@
       <c r="D562" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E562" s="5" t="n">
+      <c r="E562" s="5" t="str">
         <f aca="false">IF((F562+G562)&gt;0,ROUND((F562+G562)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F562" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G562" s="5"/>
     </row>
@@ -17302,12 +17302,12 @@
       <c r="D565" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E565" s="5" t="n">
+      <c r="E565" s="5" t="str">
         <f aca="false">IF((F565+G565)&gt;0,ROUND((F565+G565)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F565" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G565" s="5"/>
     </row>
@@ -17368,12 +17368,12 @@
       <c r="D568" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E568" s="5" t="n">
+      <c r="E568" s="5" t="str">
         <f aca="false">IF((F568+G568)&gt;0,ROUND((F568+G568)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F568" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G568" s="5"/>
     </row>
@@ -17412,12 +17412,12 @@
       <c r="D570" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E570" s="5" t="n">
+      <c r="E570" s="5" t="str">
         <f aca="false">IF((F570+G570)&gt;0,ROUND((F570+G570)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F570" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G570" s="5"/>
     </row>
@@ -17434,12 +17434,12 @@
       <c r="D571" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E571" s="5" t="n">
+      <c r="E571" s="5" t="str">
         <f aca="false">IF((F571+G571)&gt;0,ROUND((F571+G571)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F571" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G571" s="5"/>
     </row>
@@ -17456,12 +17456,12 @@
       <c r="D572" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E572" s="5" t="n">
+      <c r="E572" s="5" t="str">
         <f aca="false">IF((F572+G572)&gt;0,ROUND((F572+G572)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F572" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G572" s="5"/>
     </row>
@@ -17478,12 +17478,12 @@
       <c r="D573" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E573" s="5" t="n">
+      <c r="E573" s="5" t="str">
         <f aca="false">IF((F573+G573)&gt;0,ROUND((F573+G573)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F573" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G573" s="5"/>
     </row>
@@ -17742,12 +17742,12 @@
       <c r="D585" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E585" s="5" t="n">
+      <c r="E585" s="5" t="str">
         <f aca="false">IF((F585+G585)&gt;0,ROUND((F585+G585)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F585" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G585" s="5"/>
     </row>
@@ -18402,12 +18402,12 @@
       <c r="D615" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E615" s="5" t="n">
+      <c r="E615" s="5" t="str">
         <f aca="false">IF((F615+G615)&gt;0,ROUND((F615+G615)/30,2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="F615" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G615" s="5"/>
     </row>
@@ -18512,12 +18512,12 @@
       <c r="D620" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E620" s="5" t="n">
+      <c r="E620" s="5" t="str">
         <f aca="false">IF((F620+G620)&gt;0,ROUND((F620+G620)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F620" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G620" s="5"/>
     </row>
@@ -18600,12 +18600,12 @@
       <c r="D624" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E624" s="5" t="n">
+      <c r="E624" s="5" t="str">
         <f aca="false">IF((F624+G624)&gt;0,ROUND((F624+G624)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F624" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G624" s="5"/>
     </row>
@@ -18690,10 +18690,10 @@
       </c>
       <c r="E628" s="5" t="n">
         <f aca="false">IF((F628+G628)&gt;0,ROUND((F628+G628)/30,2),"")</f>
-        <v>3.33</v>
+        <v>10</v>
       </c>
       <c r="F628" s="5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G628" s="5"/>
     </row>
@@ -18710,12 +18710,12 @@
       <c r="D629" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E629" s="5" t="n">
+      <c r="E629" s="5" t="str">
         <f aca="false">IF((F629+G629)&gt;0,ROUND((F629+G629)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F629" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G629" s="5"/>
     </row>
@@ -18732,12 +18732,12 @@
       <c r="D630" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E630" s="5" t="n">
+      <c r="E630" s="5" t="str">
         <f aca="false">IF((F630+G630)&gt;0,ROUND((F630+G630)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F630" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G630" s="5"/>
     </row>
@@ -18844,10 +18844,10 @@
       </c>
       <c r="E635" s="5" t="n">
         <f aca="false">IF((F635+G635)&gt;0,ROUND((F635+G635)/30,2),"")</f>
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="F635" s="5" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G635" s="5"/>
     </row>
@@ -18866,10 +18866,10 @@
       </c>
       <c r="E636" s="5" t="n">
         <f aca="false">IF((F636+G636)&gt;0,ROUND((F636+G636)/30,2),"")</f>
-        <v>3.33</v>
+        <v>10</v>
       </c>
       <c r="F636" s="5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G636" s="5"/>
     </row>
@@ -18910,10 +18910,10 @@
       </c>
       <c r="E638" s="5" t="n">
         <f aca="false">IF((F638+G638)&gt;0,ROUND((F638+G638)/30,2),"")</f>
-        <v>5</v>
+        <v>13.33</v>
       </c>
       <c r="F638" s="5" t="n">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="G638" s="5"/>
     </row>
@@ -18978,10 +18978,10 @@
       </c>
       <c r="E641" s="5" t="n">
         <f aca="false">IF((F641+G641)&gt;0,ROUND((F641+G641)/30,2),"")</f>
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="F641" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G641" s="5"/>
     </row>
@@ -19000,10 +19000,10 @@
       </c>
       <c r="E642" s="5" t="n">
         <f aca="false">IF((F642+G642)&gt;0,ROUND((F642+G642)/30,2),"")</f>
-        <v>1.67</v>
+        <v>8.33</v>
       </c>
       <c r="F642" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G642" s="5"/>
     </row>
@@ -19086,12 +19086,12 @@
       <c r="D646" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E646" s="5" t="n">
+      <c r="E646" s="5" t="str">
         <f aca="false">IF((F646+G646)&gt;0,ROUND((F646+G646)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F646" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G646" s="5"/>
     </row>
@@ -19350,12 +19350,12 @@
       <c r="D658" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E658" s="5" t="n">
+      <c r="E658" s="5" t="str">
         <f aca="false">IF((F658+G658)&gt;0,ROUND((F658+G658)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F658" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G658" s="5"/>
     </row>
@@ -19394,12 +19394,12 @@
       <c r="D660" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E660" s="5" t="n">
+      <c r="E660" s="5" t="str">
         <f aca="false">IF((F660+G660)&gt;0,ROUND((F660+G660)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F660" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G660" s="5"/>
     </row>
@@ -19416,12 +19416,12 @@
       <c r="D661" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E661" s="5" t="n">
+      <c r="E661" s="5" t="str">
         <f aca="false">IF((F661+G661)&gt;0,ROUND((F661+G661)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F661" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G661" s="5"/>
     </row>
@@ -19482,12 +19482,12 @@
       <c r="D664" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E664" s="5" t="n">
+      <c r="E664" s="5" t="str">
         <f aca="false">IF((F664+G664)&gt;0,ROUND((F664+G664)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F664" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G664" s="5"/>
     </row>
@@ -19790,12 +19790,12 @@
       <c r="D678" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E678" s="5" t="n">
+      <c r="E678" s="5" t="str">
         <f aca="false">IF((F678+G678)&gt;0,ROUND((F678+G678)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F678" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G678" s="5"/>
     </row>
@@ -20010,12 +20010,12 @@
       <c r="D688" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E688" s="5" t="n">
+      <c r="E688" s="5" t="str">
         <f aca="false">IF((F688+G688)&gt;0,ROUND((F688+G688)/30,2),"")</f>
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="F688" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G688" s="5"/>
     </row>
@@ -20142,12 +20142,12 @@
       <c r="D694" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E694" s="5" t="n">
+      <c r="E694" s="5" t="str">
         <f aca="false">IF((F694+G694)&gt;0,ROUND((F694+G694)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F694" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G694" s="5"/>
     </row>
@@ -20164,12 +20164,12 @@
       <c r="D695" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E695" s="5" t="n">
+      <c r="E695" s="5" t="str">
         <f aca="false">IF((F695+G695)&gt;0,ROUND((F695+G695)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F695" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G695" s="5"/>
     </row>
@@ -20252,12 +20252,12 @@
       <c r="D699" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E699" s="5" t="n">
+      <c r="E699" s="5" t="str">
         <f aca="false">IF((F699+G699)&gt;0,ROUND((F699+G699)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F699" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G699" s="5"/>
     </row>
@@ -20318,12 +20318,12 @@
       <c r="D702" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E702" s="5" t="n">
+      <c r="E702" s="5" t="str">
         <f aca="false">IF((F702+G702)&gt;0,ROUND((F702+G702)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F702" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G702" s="5"/>
     </row>
@@ -20428,12 +20428,12 @@
       <c r="D707" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E707" s="5" t="n">
+      <c r="E707" s="5" t="str">
         <f aca="false">IF((F707+G707)&gt;0,ROUND((F707+G707)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F707" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G707" s="5"/>
     </row>
@@ -20472,12 +20472,12 @@
       <c r="D709" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E709" s="5" t="n">
+      <c r="E709" s="5" t="str">
         <f aca="false">IF((F709+G709)&gt;0,ROUND((F709+G709)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F709" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G709" s="5"/>
     </row>
@@ -20516,12 +20516,12 @@
       <c r="D711" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E711" s="5" t="n">
+      <c r="E711" s="5" t="str">
         <f aca="false">IF((F711+G711)&gt;0,ROUND((F711+G711)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F711" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G711" s="5"/>
     </row>
@@ -20692,12 +20692,12 @@
       <c r="D719" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E719" s="5" t="n">
+      <c r="E719" s="5" t="str">
         <f aca="false">IF((F719+G719)&gt;0,ROUND((F719+G719)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F719" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G719" s="5"/>
     </row>
@@ -20868,12 +20868,12 @@
       <c r="D727" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E727" s="5" t="n">
+      <c r="E727" s="5" t="str">
         <f aca="false">IF((F727+G727)&gt;0,ROUND((F727+G727)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F727" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G727" s="5"/>
     </row>
@@ -20890,12 +20890,12 @@
       <c r="D728" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E728" s="5" t="n">
+      <c r="E728" s="5" t="str">
         <f aca="false">IF((F728+G728)&gt;0,ROUND((F728+G728)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F728" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G728" s="5"/>
     </row>
@@ -20934,12 +20934,12 @@
       <c r="D730" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E730" s="5" t="n">
+      <c r="E730" s="5" t="str">
         <f aca="false">IF((F730+G730)&gt;0,ROUND((F730+G730)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F730" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G730" s="5"/>
     </row>
@@ -22936,12 +22936,12 @@
       <c r="D821" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E821" s="5" t="n">
+      <c r="E821" s="5" t="str">
         <f aca="false">IF((F821+G821)&gt;0,ROUND((F821+G821)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F821" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G821" s="5"/>
     </row>
@@ -22960,10 +22960,10 @@
       </c>
       <c r="E822" s="5" t="n">
         <f aca="false">IF((F822+G822)&gt;0,ROUND((F822+G822)/30,2),"")</f>
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="F822" s="5" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G822" s="5"/>
     </row>
@@ -23002,12 +23002,12 @@
       <c r="D824" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E824" s="5" t="n">
+      <c r="E824" s="5" t="str">
         <f aca="false">IF((F824+G824)&gt;0,ROUND((F824+G824)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F824" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G824" s="5"/>
     </row>
@@ -23046,12 +23046,12 @@
       <c r="D826" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E826" s="5" t="n">
+      <c r="E826" s="5" t="str">
         <f aca="false">IF((F826+G826)&gt;0,ROUND((F826+G826)/30,2),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F826" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G826" s="5"/>
     </row>
@@ -23114,10 +23114,10 @@
       </c>
       <c r="E829" s="5" t="n">
         <f aca="false">IF((F829+G829)&gt;0,ROUND((F829+G829)/30,2),"")</f>
-        <v>5</v>
+        <v>8.33</v>
       </c>
       <c r="F829" s="5" t="n">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="G829" s="5"/>
     </row>
@@ -23156,12 +23156,12 @@
       <c r="D831" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E831" s="5" t="n">
+      <c r="E831" s="5" t="str">
         <f aca="false">IF((F831+G831)&gt;0,ROUND((F831+G831)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F831" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G831" s="5"/>
     </row>
@@ -23200,12 +23200,12 @@
       <c r="D833" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E833" s="5" t="n">
+      <c r="E833" s="5" t="str">
         <f aca="false">IF((F833+G833)&gt;0,ROUND((F833+G833)/30,2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="F833" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G833" s="5"/>
     </row>
@@ -23268,10 +23268,10 @@
       </c>
       <c r="E836" s="5" t="n">
         <f aca="false">IF((F836+G836)&gt;0,ROUND((F836+G836)/30,2),"")</f>
-        <v>5</v>
+        <v>6.67</v>
       </c>
       <c r="F836" s="5" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G836" s="5"/>
     </row>
@@ -23290,10 +23290,10 @@
       </c>
       <c r="E837" s="5" t="n">
         <f aca="false">IF((F837+G837)&gt;0,ROUND((F837+G837)/30,2),"")</f>
-        <v>3.33</v>
+        <v>8.33</v>
       </c>
       <c r="F837" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G837" s="5"/>
     </row>
@@ -23312,10 +23312,10 @@
       </c>
       <c r="E838" s="5" t="n">
         <f aca="false">IF((F838+G838)&gt;0,ROUND((F838+G838)/30,2),"")</f>
-        <v>3.33</v>
+        <v>5</v>
       </c>
       <c r="F838" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G838" s="5"/>
     </row>
@@ -23354,12 +23354,12 @@
       <c r="D840" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E840" s="5" t="n">
+      <c r="E840" s="5" t="str">
         <f aca="false">IF((F840+G840)&gt;0,ROUND((F840+G840)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F840" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G840" s="5"/>
     </row>
@@ -23378,10 +23378,10 @@
       </c>
       <c r="E841" s="5" t="n">
         <f aca="false">IF((F841+G841)&gt;0,ROUND((F841+G841)/30,2),"")</f>
-        <v>1.67</v>
+        <v>8.33</v>
       </c>
       <c r="F841" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G841" s="5"/>
     </row>
@@ -23532,10 +23532,10 @@
       </c>
       <c r="E848" s="5" t="n">
         <f aca="false">IF((F848+G848)&gt;0,ROUND((F848+G848)/30,2),"")</f>
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="F848" s="5" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G848" s="5"/>
     </row>
@@ -23576,10 +23576,10 @@
       </c>
       <c r="E850" s="5" t="n">
         <f aca="false">IF((F850+G850)&gt;0,ROUND((F850+G850)/30,2),"")</f>
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="F850" s="5" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G850" s="5"/>
     </row>
@@ -23596,12 +23596,12 @@
       <c r="D851" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E851" s="5" t="n">
+      <c r="E851" s="5" t="str">
         <f aca="false">IF((F851+G851)&gt;0,ROUND((F851+G851)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F851" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G851" s="5"/>
     </row>
@@ -23618,12 +23618,12 @@
       <c r="D852" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E852" s="5" t="n">
+      <c r="E852" s="5" t="str">
         <f aca="false">IF((F852+G852)&gt;0,ROUND((F852+G852)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F852" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G852" s="5"/>
     </row>
@@ -23686,10 +23686,10 @@
       </c>
       <c r="E855" s="5" t="n">
         <f aca="false">IF((F855+G855)&gt;0,ROUND((F855+G855)/30,2),"")</f>
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="F855" s="5" t="n">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="G855" s="5"/>
     </row>
@@ -23838,12 +23838,12 @@
       <c r="D862" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E862" s="5" t="n">
+      <c r="E862" s="5" t="str">
         <f aca="false">IF((F862+G862)&gt;0,ROUND((F862+G862)/30,2),"")</f>
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="F862" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G862" s="5"/>
     </row>
@@ -23906,10 +23906,10 @@
       </c>
       <c r="E865" s="5" t="n">
         <f aca="false">IF((F865+G865)&gt;0,ROUND((F865+G865)/30,2),"")</f>
-        <v>3.33</v>
+        <v>8.33</v>
       </c>
       <c r="F865" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G865" s="5"/>
     </row>
@@ -23970,12 +23970,12 @@
       <c r="D868" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E868" s="5" t="n">
+      <c r="E868" s="5" t="str">
         <f aca="false">IF((F868+G868)&gt;0,ROUND((F868+G868)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F868" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G868" s="5"/>
     </row>
@@ -23992,12 +23992,12 @@
       <c r="D869" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E869" s="5" t="n">
+      <c r="E869" s="5" t="str">
         <f aca="false">IF((F869+G869)&gt;0,ROUND((F869+G869)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F869" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G869" s="5"/>
     </row>
@@ -24016,10 +24016,10 @@
       </c>
       <c r="E870" s="5" t="n">
         <f aca="false">IF((F870+G870)&gt;0,ROUND((F870+G870)/30,2),"")</f>
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="F870" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G870" s="5"/>
     </row>
@@ -24038,10 +24038,10 @@
       </c>
       <c r="E871" s="5" t="n">
         <f aca="false">IF((F871+G871)&gt;0,ROUND((F871+G871)/30,2),"")</f>
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="F871" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G871" s="5"/>
     </row>
@@ -24058,12 +24058,12 @@
       <c r="D872" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E872" s="5" t="n">
+      <c r="E872" s="5" t="str">
         <f aca="false">IF((F872+G872)&gt;0,ROUND((F872+G872)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F872" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G872" s="5"/>
     </row>
@@ -24278,12 +24278,12 @@
       <c r="D882" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E882" s="5" t="n">
+      <c r="E882" s="5" t="str">
         <f aca="false">IF((F882+G882)&gt;0,ROUND((F882+G882)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F882" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G882" s="5"/>
     </row>
@@ -24346,10 +24346,10 @@
       </c>
       <c r="E885" s="5" t="n">
         <f aca="false">IF((F885+G885)&gt;0,ROUND((F885+G885)/30,2),"")</f>
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="F885" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G885" s="5"/>
     </row>
@@ -24454,12 +24454,12 @@
       <c r="D890" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E890" s="5" t="n">
+      <c r="E890" s="5" t="str">
         <f aca="false">IF((F890+G890)&gt;0,ROUND((F890+G890)/30,2),"")</f>
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="F890" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G890" s="5"/>
     </row>
@@ -24586,12 +24586,12 @@
       <c r="D896" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E896" s="5" t="n">
+      <c r="E896" s="5" t="str">
         <f aca="false">IF((F896+G896)&gt;0,ROUND((F896+G896)/30,2),"")</f>
-        <v>10</v>
+        <v/>
       </c>
       <c r="F896" s="5" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G896" s="5"/>
     </row>
@@ -24630,12 +24630,12 @@
       <c r="D898" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E898" s="5" t="n">
+      <c r="E898" s="5" t="str">
         <f aca="false">IF((F898+G898)&gt;0,ROUND((F898+G898)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F898" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G898" s="5"/>
     </row>
@@ -24696,12 +24696,12 @@
       <c r="D901" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E901" s="5" t="n">
+      <c r="E901" s="5" t="str">
         <f aca="false">IF((F901+G901)&gt;0,ROUND((F901+G901)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F901" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G901" s="5"/>
     </row>
@@ -24852,10 +24852,10 @@
       </c>
       <c r="E908" s="5" t="n">
         <f aca="false">IF((F908+G908)&gt;0,ROUND((F908+G908)/30,2),"")</f>
-        <v>1.67</v>
+        <v>4</v>
       </c>
       <c r="F908" s="5" t="n">
-        <v>50</v>
+        <v>120</v>
       </c>
       <c r="G908" s="5"/>
     </row>
@@ -26499,12 +26499,12 @@
         <v>17</v>
       </c>
       <c r="D984" s="9"/>
-      <c r="E984" s="5" t="n">
+      <c r="E984" s="5" t="str">
         <f aca="false">IF((F984+G984)&gt;0,ROUND((F984+G984)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F984" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G984" s="5"/>
     </row>
@@ -26519,12 +26519,12 @@
         <v>17</v>
       </c>
       <c r="D985" s="9"/>
-      <c r="E985" s="5" t="n">
+      <c r="E985" s="5" t="str">
         <f aca="false">IF((F985+G985)&gt;0,ROUND((F985+G985)/30,2),"")</f>
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="F985" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G985" s="5"/>
     </row>
@@ -26539,12 +26539,12 @@
         <v>17</v>
       </c>
       <c r="D986" s="9"/>
-      <c r="E986" s="5" t="n">
+      <c r="E986" s="5" t="str">
         <f aca="false">IF((F986+G986)&gt;0,ROUND((F986+G986)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F986" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G986" s="5"/>
     </row>
@@ -26601,10 +26601,10 @@
       <c r="D989" s="9"/>
       <c r="E989" s="5" t="n">
         <f aca="false">IF((F989+G989)&gt;0,ROUND((F989+G989)/30,2),"")</f>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="F989" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G989" s="5"/>
     </row>
@@ -26659,12 +26659,12 @@
         <v>17</v>
       </c>
       <c r="D992" s="9"/>
-      <c r="E992" s="5" t="n">
+      <c r="E992" s="5" t="str">
         <f aca="false">IF((F992+G992)&gt;0,ROUND((F992+G992)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F992" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G992" s="5"/>
     </row>
@@ -26679,12 +26679,12 @@
         <v>17</v>
       </c>
       <c r="D993" s="9"/>
-      <c r="E993" s="5" t="n">
+      <c r="E993" s="5" t="str">
         <f aca="false">IF((F993+G993)&gt;0,ROUND((F993+G993)/30,2),"")</f>
-        <v>5</v>
+        <v/>
       </c>
       <c r="F993" s="5" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="G993" s="5"/>
     </row>
@@ -26699,12 +26699,12 @@
         <v>17</v>
       </c>
       <c r="D994" s="9"/>
-      <c r="E994" s="5" t="n">
+      <c r="E994" s="5" t="str">
         <f aca="false">IF((F994+G994)&gt;0,ROUND((F994+G994)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F994" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G994" s="5"/>
     </row>
@@ -31339,12 +31339,12 @@
         <v>30</v>
       </c>
       <c r="D1226" s="9"/>
-      <c r="E1226" s="5" t="n">
+      <c r="E1226" s="5" t="str">
         <f aca="false">IF((F1226+G1226)&gt;0,ROUND((F1226+G1226)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1226" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1226" s="5"/>
     </row>
@@ -31359,12 +31359,12 @@
         <v>30</v>
       </c>
       <c r="D1227" s="9"/>
-      <c r="E1227" s="5" t="n">
+      <c r="E1227" s="5" t="str">
         <f aca="false">IF((F1227+G1227)&gt;0,ROUND((F1227+G1227)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1227" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1227" s="5"/>
     </row>
@@ -31419,12 +31419,12 @@
         <v>30</v>
       </c>
       <c r="D1230" s="9"/>
-      <c r="E1230" s="5" t="n">
+      <c r="E1230" s="5" t="str">
         <f aca="false">IF((F1230+G1230)&gt;0,ROUND((F1230+G1230)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1230" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1230" s="5"/>
     </row>
@@ -31439,12 +31439,12 @@
         <v>30</v>
       </c>
       <c r="D1231" s="9"/>
-      <c r="E1231" s="5" t="n">
+      <c r="E1231" s="5" t="str">
         <f aca="false">IF((F1231+G1231)&gt;0,ROUND((F1231+G1231)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1231" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1231" s="5"/>
     </row>
@@ -31459,12 +31459,12 @@
         <v>30</v>
       </c>
       <c r="D1232" s="9"/>
-      <c r="E1232" s="5" t="n">
+      <c r="E1232" s="5" t="str">
         <f aca="false">IF((F1232+G1232)&gt;0,ROUND((F1232+G1232)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1232" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1232" s="5"/>
     </row>
@@ -31499,12 +31499,12 @@
         <v>30</v>
       </c>
       <c r="D1234" s="9"/>
-      <c r="E1234" s="5" t="n">
+      <c r="E1234" s="5" t="str">
         <f aca="false">IF((F1234+G1234)&gt;0,ROUND((F1234+G1234)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1234" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1234" s="5"/>
     </row>
@@ -31519,12 +31519,12 @@
         <v>30</v>
       </c>
       <c r="D1235" s="9"/>
-      <c r="E1235" s="5" t="n">
+      <c r="E1235" s="5" t="str">
         <f aca="false">IF((F1235+G1235)&gt;0,ROUND((F1235+G1235)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1235" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1235" s="5"/>
     </row>
@@ -31583,12 +31583,12 @@
         <v>30</v>
       </c>
       <c r="D1238" s="9"/>
-      <c r="E1238" s="5" t="n">
+      <c r="E1238" s="5" t="str">
         <f aca="false">IF((F1238+G1238)&gt;0,ROUND((F1238+G1238)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1238" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1238" s="5"/>
     </row>
@@ -31603,12 +31603,12 @@
         <v>30</v>
       </c>
       <c r="D1239" s="9"/>
-      <c r="E1239" s="5" t="n">
+      <c r="E1239" s="5" t="str">
         <f aca="false">IF((F1239+G1239)&gt;0,ROUND((F1239+G1239)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1239" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1239" s="5"/>
     </row>
@@ -31643,12 +31643,12 @@
         <v>30</v>
       </c>
       <c r="D1241" s="9"/>
-      <c r="E1241" s="5" t="n">
+      <c r="E1241" s="5" t="str">
         <f aca="false">IF((F1241+G1241)&gt;0,ROUND((F1241+G1241)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1241" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1241" s="5"/>
     </row>
@@ -31663,12 +31663,12 @@
         <v>30</v>
       </c>
       <c r="D1242" s="9"/>
-      <c r="E1242" s="5" t="n">
+      <c r="E1242" s="5" t="str">
         <f aca="false">IF((F1242+G1242)&gt;0,ROUND((F1242+G1242)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1242" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1242" s="5"/>
     </row>
@@ -31683,12 +31683,12 @@
         <v>30</v>
       </c>
       <c r="D1243" s="9"/>
-      <c r="E1243" s="5" t="n">
+      <c r="E1243" s="5" t="str">
         <f aca="false">IF((F1243+G1243)&gt;0,ROUND((F1243+G1243)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1243" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1243" s="5"/>
     </row>
@@ -31703,12 +31703,12 @@
         <v>30</v>
       </c>
       <c r="D1244" s="9"/>
-      <c r="E1244" s="5" t="n">
+      <c r="E1244" s="5" t="str">
         <f aca="false">IF((F1244+G1244)&gt;0,ROUND((F1244+G1244)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1244" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1244" s="5"/>
     </row>
@@ -31763,12 +31763,12 @@
         <v>30</v>
       </c>
       <c r="D1247" s="9"/>
-      <c r="E1247" s="5" t="n">
+      <c r="E1247" s="5" t="str">
         <f aca="false">IF((F1247+G1247)&gt;0,ROUND((F1247+G1247)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1247" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1247" s="5"/>
     </row>
@@ -31783,12 +31783,12 @@
         <v>30</v>
       </c>
       <c r="D1248" s="9"/>
-      <c r="E1248" s="5" t="n">
+      <c r="E1248" s="5" t="str">
         <f aca="false">IF((F1248+G1248)&gt;0,ROUND((F1248+G1248)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1248" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1248" s="5"/>
     </row>
@@ -31803,12 +31803,12 @@
         <v>30</v>
       </c>
       <c r="D1249" s="9"/>
-      <c r="E1249" s="5" t="n">
+      <c r="E1249" s="5" t="str">
         <f aca="false">IF((F1249+G1249)&gt;0,ROUND((F1249+G1249)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1249" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1249" s="5"/>
     </row>
@@ -31843,12 +31843,12 @@
         <v>30</v>
       </c>
       <c r="D1251" s="9"/>
-      <c r="E1251" s="5" t="n">
+      <c r="E1251" s="5" t="str">
         <f aca="false">IF((F1251+G1251)&gt;0,ROUND((F1251+G1251)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1251" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1251" s="5"/>
     </row>
@@ -31883,12 +31883,12 @@
         <v>30</v>
       </c>
       <c r="D1253" s="9"/>
-      <c r="E1253" s="5" t="n">
+      <c r="E1253" s="5" t="str">
         <f aca="false">IF((F1253+G1253)&gt;0,ROUND((F1253+G1253)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1253" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1253" s="5"/>
     </row>
@@ -31923,12 +31923,12 @@
         <v>30</v>
       </c>
       <c r="D1255" s="9"/>
-      <c r="E1255" s="5" t="n">
+      <c r="E1255" s="5" t="str">
         <f aca="false">IF((F1255+G1255)&gt;0,ROUND((F1255+G1255)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1255" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1255" s="5"/>
     </row>
@@ -31943,12 +31943,12 @@
         <v>30</v>
       </c>
       <c r="D1256" s="9"/>
-      <c r="E1256" s="5" t="n">
+      <c r="E1256" s="5" t="str">
         <f aca="false">IF((F1256+G1256)&gt;0,ROUND((F1256+G1256)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1256" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1256" s="5"/>
     </row>
@@ -31963,12 +31963,12 @@
         <v>30</v>
       </c>
       <c r="D1257" s="9"/>
-      <c r="E1257" s="5" t="n">
+      <c r="E1257" s="5" t="str">
         <f aca="false">IF((F1257+G1257)&gt;0,ROUND((F1257+G1257)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1257" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1257" s="5"/>
     </row>
@@ -32003,12 +32003,12 @@
         <v>30</v>
       </c>
       <c r="D1259" s="9"/>
-      <c r="E1259" s="5" t="n">
+      <c r="E1259" s="5" t="str">
         <f aca="false">IF((F1259+G1259)&gt;0,ROUND((F1259+G1259)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1259" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1259" s="5"/>
     </row>
@@ -32023,12 +32023,12 @@
         <v>30</v>
       </c>
       <c r="D1260" s="9"/>
-      <c r="E1260" s="5" t="n">
+      <c r="E1260" s="5" t="str">
         <f aca="false">IF((F1260+G1260)&gt;0,ROUND((F1260+G1260)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1260" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1260" s="5"/>
     </row>
@@ -32163,12 +32163,12 @@
         <v>44</v>
       </c>
       <c r="D1267" s="9"/>
-      <c r="E1267" s="5" t="n">
+      <c r="E1267" s="5" t="str">
         <f aca="false">IF((F1267+G1267)&gt;0,ROUND((F1267+G1267)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1267" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1267" s="5"/>
     </row>
@@ -32283,12 +32283,12 @@
         <v>44</v>
       </c>
       <c r="D1273" s="9"/>
-      <c r="E1273" s="5" t="n">
+      <c r="E1273" s="5" t="str">
         <f aca="false">IF((F1273+G1273)&gt;0,ROUND((F1273+G1273)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1273" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1273" s="5"/>
     </row>
@@ -32363,12 +32363,12 @@
         <v>44</v>
       </c>
       <c r="D1277" s="9"/>
-      <c r="E1277" s="5" t="n">
+      <c r="E1277" s="5" t="str">
         <f aca="false">IF((F1277+G1277)&gt;0,ROUND((F1277+G1277)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1277" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1277" s="5"/>
     </row>
@@ -32443,12 +32443,12 @@
         <v>44</v>
       </c>
       <c r="D1281" s="9"/>
-      <c r="E1281" s="5" t="n">
+      <c r="E1281" s="5" t="str">
         <f aca="false">IF((F1281+G1281)&gt;0,ROUND((F1281+G1281)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1281" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1281" s="5"/>
     </row>
@@ -32563,12 +32563,12 @@
         <v>44</v>
       </c>
       <c r="D1287" s="9"/>
-      <c r="E1287" s="5" t="n">
+      <c r="E1287" s="5" t="str">
         <f aca="false">IF((F1287+G1287)&gt;0,ROUND((F1287+G1287)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1287" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1287" s="5"/>
     </row>
@@ -32825,12 +32825,12 @@
         <v>44</v>
       </c>
       <c r="D1300" s="9"/>
-      <c r="E1300" s="5" t="n">
+      <c r="E1300" s="5" t="str">
         <f aca="false">IF((F1300+G1300)&gt;0,ROUND((F1300+G1300)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F1300" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G1300" s="5"/>
     </row>
@@ -32845,12 +32845,12 @@
         <v>44</v>
       </c>
       <c r="D1301" s="9"/>
-      <c r="E1301" s="5" t="n">
+      <c r="E1301" s="5" t="str">
         <f aca="false">IF((F1301+G1301)&gt;0,ROUND((F1301+G1301)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F1301" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G1301" s="5"/>
     </row>
@@ -32865,12 +32865,12 @@
         <v>44</v>
       </c>
       <c r="D1302" s="9"/>
-      <c r="E1302" s="5" t="n">
+      <c r="E1302" s="5" t="str">
         <f aca="false">IF((F1302+G1302)&gt;0,ROUND((F1302+G1302)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1302" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1302" s="5"/>
     </row>
@@ -32885,12 +32885,12 @@
         <v>44</v>
       </c>
       <c r="D1303" s="9"/>
-      <c r="E1303" s="5" t="n">
+      <c r="E1303" s="5" t="str">
         <f aca="false">IF((F1303+G1303)&gt;0,ROUND((F1303+G1303)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1303" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1303" s="5"/>
     </row>
@@ -32967,10 +32967,10 @@
       <c r="D1307" s="9"/>
       <c r="E1307" s="5" t="n">
         <f aca="false">IF((F1307+G1307)&gt;0,ROUND((F1307+G1307)/30,2),"")</f>
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="F1307" s="5" t="n">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="G1307" s="5"/>
     </row>
@@ -33105,12 +33105,12 @@
         <v>44</v>
       </c>
       <c r="D1314" s="9"/>
-      <c r="E1314" s="5" t="n">
+      <c r="E1314" s="5" t="str">
         <f aca="false">IF((F1314+G1314)&gt;0,ROUND((F1314+G1314)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1314" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1314" s="5"/>
     </row>
@@ -33125,12 +33125,12 @@
         <v>44</v>
       </c>
       <c r="D1315" s="9"/>
-      <c r="E1315" s="5" t="n">
+      <c r="E1315" s="5" t="str">
         <f aca="false">IF((F1315+G1315)&gt;0,ROUND((F1315+G1315)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1315" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1315" s="5"/>
     </row>
@@ -34107,12 +34107,12 @@
         <v>75</v>
       </c>
       <c r="D1364" s="9"/>
-      <c r="E1364" s="5" t="n">
+      <c r="E1364" s="5" t="str">
         <f aca="false">IF((F1364+G1364)&gt;0,ROUND((F1364+G1364)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1364" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1364" s="5"/>
     </row>
@@ -34147,12 +34147,12 @@
         <v>75</v>
       </c>
       <c r="D1366" s="9"/>
-      <c r="E1366" s="5" t="n">
+      <c r="E1366" s="5" t="str">
         <f aca="false">IF((F1366+G1366)&gt;0,ROUND((F1366+G1366)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1366" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1366" s="5"/>
     </row>
@@ -34167,12 +34167,12 @@
         <v>75</v>
       </c>
       <c r="D1367" s="9"/>
-      <c r="E1367" s="5" t="n">
+      <c r="E1367" s="5" t="str">
         <f aca="false">IF((F1367+G1367)&gt;0,ROUND((F1367+G1367)/30,2),"")</f>
-        <v>6.67</v>
+        <v/>
       </c>
       <c r="F1367" s="5" t="n">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G1367" s="5"/>
     </row>
@@ -34247,12 +34247,12 @@
         <v>75</v>
       </c>
       <c r="D1371" s="9"/>
-      <c r="E1371" s="5" t="n">
+      <c r="E1371" s="5" t="str">
         <f aca="false">IF((F1371+G1371)&gt;0,ROUND((F1371+G1371)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1371" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1371" s="5"/>
     </row>
@@ -34287,12 +34287,12 @@
         <v>75</v>
       </c>
       <c r="D1373" s="9"/>
-      <c r="E1373" s="5" t="n">
+      <c r="E1373" s="5" t="str">
         <f aca="false">IF((F1373+G1373)&gt;0,ROUND((F1373+G1373)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1373" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1373" s="5"/>
     </row>
@@ -34367,12 +34367,12 @@
         <v>75</v>
       </c>
       <c r="D1377" s="9"/>
-      <c r="E1377" s="5" t="n">
+      <c r="E1377" s="5" t="str">
         <f aca="false">IF((F1377+G1377)&gt;0,ROUND((F1377+G1377)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1377" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1377" s="5"/>
     </row>
@@ -34389,10 +34389,10 @@
       <c r="D1378" s="9"/>
       <c r="E1378" s="5" t="n">
         <f aca="false">IF((F1378+G1378)&gt;0,ROUND((F1378+G1378)/30,2),"")</f>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="F1378" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G1378" s="5"/>
     </row>
@@ -34409,10 +34409,10 @@
       <c r="D1379" s="9"/>
       <c r="E1379" s="5" t="n">
         <f aca="false">IF((F1379+G1379)&gt;0,ROUND((F1379+G1379)/30,2),"")</f>
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="F1379" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G1379" s="5"/>
     </row>
@@ -34449,12 +34449,12 @@
         <v>75</v>
       </c>
       <c r="D1381" s="9"/>
-      <c r="E1381" s="5" t="n">
+      <c r="E1381" s="5" t="str">
         <f aca="false">IF((F1381+G1381)&gt;0,ROUND((F1381+G1381)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F1381" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G1381" s="5"/>
     </row>
@@ -34469,12 +34469,12 @@
         <v>75</v>
       </c>
       <c r="D1382" s="9"/>
-      <c r="E1382" s="5" t="n">
+      <c r="E1382" s="5" t="str">
         <f aca="false">IF((F1382+G1382)&gt;0,ROUND((F1382+G1382)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1382" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1382" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -16620,12 +16620,12 @@
       <c r="D534" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E534" s="5" t="n">
+      <c r="E534" s="5" t="str">
         <f aca="false">IF((F534+G534)&gt;0,ROUND((F534+G534)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F534" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G534" s="5"/>
     </row>
@@ -16818,12 +16818,12 @@
       <c r="D543" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E543" s="5" t="n">
+      <c r="E543" s="5" t="str">
         <f aca="false">IF((F543+G543)&gt;0,ROUND((F543+G543)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F543" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G543" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -5778,10 +5778,10 @@
       </c>
       <c r="E41" s="5" t="n">
         <f aca="false">IF((F41+G41)&gt;0,ROUND((F41+G41)/30,2),"")</f>
-        <v>23.33</v>
+        <v>16.67</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="G41" s="5"/>
     </row>
@@ -7915,10 +7915,10 @@
       </c>
       <c r="E138" s="5" t="n">
         <f aca="false">IF((F138+G138)&gt;0,ROUND((F138+G138)/30,2),"")</f>
-        <v>100</v>
+        <v>33.33</v>
       </c>
       <c r="F138" s="5" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="G138" s="5"/>
     </row>
@@ -8775,10 +8775,10 @@
       </c>
       <c r="E177" s="5" t="n">
         <f aca="false">IF((F177+G177)&gt;0,ROUND((F177+G177)/30,2),"")</f>
-        <v>66.67</v>
+        <v>33.33</v>
       </c>
       <c r="F177" s="5" t="n">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="G177" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -23312,10 +23312,10 @@
       </c>
       <c r="E838" s="5" t="n">
         <f aca="false">IF((F838+G838)&gt;0,ROUND((F838+G838)/30,2),"")</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F838" s="5" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G838" s="5"/>
     </row>
@@ -23638,14 +23638,14 @@
         <v>75</v>
       </c>
       <c r="D853" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E853" s="5" t="n">
         <f aca="false">IF((F853+G853)&gt;0,ROUND((F853+G853)/30,2),"")</f>
-        <v>6.67</v>
+        <v>4</v>
       </c>
       <c r="F853" s="5" t="n">
-        <v>200</v>
+        <v>120</v>
       </c>
       <c r="G853" s="5"/>
     </row>
@@ -23730,10 +23730,10 @@
       </c>
       <c r="E857" s="5" t="n">
         <f aca="false">IF((F857+G857)&gt;0,ROUND((F857+G857)/30,2),"")</f>
-        <v>3.33</v>
+        <v>1.67</v>
       </c>
       <c r="F857" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G857" s="5"/>
     </row>
@@ -23838,10 +23838,7 @@
       <c r="D862" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E862" s="5" t="str">
-        <f aca="false">IF((F862+G862)&gt;0,ROUND((F862+G862)/30,2),"")</f>
-        <v/>
-      </c>
+      <c r="E862" s="5"/>
       <c r="F862" s="5" t="n">
         <v>0</v>
       </c>
@@ -24012,14 +24009,14 @@
         <v>75</v>
       </c>
       <c r="D870" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E870" s="5" t="n">
         <f aca="false">IF((F870+G870)&gt;0,ROUND((F870+G870)/30,2),"")</f>
-        <v>6.67</v>
+        <v>3.33</v>
       </c>
       <c r="F870" s="5" t="n">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G870" s="5"/>
     </row>
@@ -24500,10 +24497,10 @@
       </c>
       <c r="E892" s="5" t="n">
         <f aca="false">IF((F892+G892)&gt;0,ROUND((F892+G892)/30,2),"")</f>
-        <v>3.33</v>
+        <v>1.67</v>
       </c>
       <c r="F892" s="5" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="G892" s="5"/>
     </row>
@@ -24566,10 +24563,10 @@
       </c>
       <c r="E895" s="5" t="n">
         <f aca="false">IF((F895+G895)&gt;0,ROUND((F895+G895)/30,2),"")</f>
-        <v>5</v>
+        <v>3.33</v>
       </c>
       <c r="F895" s="5" t="n">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="G895" s="5"/>
     </row>
@@ -34511,10 +34508,10 @@
       <c r="D1384" s="9"/>
       <c r="E1384" s="5" t="n">
         <f aca="false">IF((F1384+G1384)&gt;0,ROUND((F1384+G1384)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="F1384" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G1384" s="5"/>
     </row>
@@ -34531,10 +34528,10 @@
       <c r="D1385" s="9"/>
       <c r="E1385" s="5" t="n">
         <f aca="false">IF((F1385+G1385)&gt;0,ROUND((F1385+G1385)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F1385" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G1385" s="5"/>
     </row>
@@ -34791,12 +34788,12 @@
         <v>75</v>
       </c>
       <c r="D1398" s="9"/>
-      <c r="E1398" s="5" t="n">
+      <c r="E1398" s="5" t="str">
         <f aca="false">IF((F1398+G1398)&gt;0,ROUND((F1398+G1398)/30,2),"")</f>
-        <v>1</v>
+        <v/>
       </c>
       <c r="F1398" s="5" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G1398" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -8137,10 +8137,10 @@
       </c>
       <c r="E148" s="5" t="n">
         <f aca="false">IF((F148+G148)&gt;0,ROUND((F148+G148)/30,2),"")</f>
-        <v>33.33</v>
+        <v>50</v>
       </c>
       <c r="F148" s="5" t="n">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="G148" s="5"/>
     </row>
@@ -8159,10 +8159,10 @@
       </c>
       <c r="E149" s="5" t="n">
         <f aca="false">IF((F149+G149)&gt;0,ROUND((F149+G149)/30,2),"")</f>
-        <v>11.67</v>
+        <v>33.33</v>
       </c>
       <c r="F149" s="5" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="G149" s="5"/>
     </row>
@@ -21222,10 +21222,10 @@
       </c>
       <c r="E743" s="5" t="n">
         <f aca="false">IF((F743+G743)&gt;0,ROUND((F743+G743)/30,2),"")</f>
-        <v>13.33</v>
+        <v>16.67</v>
       </c>
       <c r="F743" s="5" t="n">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="G743" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -7203,10 +7203,10 @@
       </c>
       <c r="E106" s="5" t="n">
         <f aca="false">IF((F106+G106)&gt;0,ROUND((F106+G106)/30,2),"")</f>
-        <v>20</v>
+        <v>23.33</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="G106" s="5"/>
     </row>
@@ -7423,10 +7423,10 @@
       </c>
       <c r="E116" s="5" t="n">
         <f aca="false">IF((F116+G116)&gt;0,ROUND((F116+G116)/30,2),"")</f>
-        <v>26.67</v>
+        <v>30</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>800</v>
+        <v>900</v>
       </c>
       <c r="G116" s="5"/>
     </row>
@@ -7445,10 +7445,10 @@
       </c>
       <c r="E117" s="5" t="n">
         <f aca="false">IF((F117+G117)&gt;0,ROUND((F117+G117)/30,2),"")</f>
-        <v>6.67</v>
+        <v>8.33</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="G117" s="5"/>
     </row>
@@ -16336,10 +16336,10 @@
       </c>
       <c r="E521" s="5" t="n">
         <f aca="false">IF((F521+G521)&gt;0,ROUND((F521+G521)/30,2),"")</f>
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="F521" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G521" s="5"/>
     </row>
@@ -16358,10 +16358,10 @@
       </c>
       <c r="E522" s="5" t="n">
         <f aca="false">IF((F522+G522)&gt;0,ROUND((F522+G522)/30,2),"")</f>
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="F522" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G522" s="5"/>
     </row>
@@ -16424,10 +16424,10 @@
       </c>
       <c r="E525" s="5" t="n">
         <f aca="false">IF((F525+G525)&gt;0,ROUND((F525+G525)/30,2),"")</f>
-        <v>3.33</v>
+        <v>5</v>
       </c>
       <c r="F525" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G525" s="5"/>
     </row>
@@ -16512,10 +16512,10 @@
       </c>
       <c r="E529" s="5" t="n">
         <f aca="false">IF((F529+G529)&gt;0,ROUND((F529+G529)/30,2),"")</f>
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="F529" s="5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G529" s="5"/>
     </row>
@@ -16600,10 +16600,10 @@
       </c>
       <c r="E533" s="5" t="n">
         <f aca="false">IF((F533+G533)&gt;0,ROUND((F533+G533)/30,2),"")</f>
-        <v>1.67</v>
+        <v>2.33</v>
       </c>
       <c r="F533" s="5" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="G533" s="5"/>
     </row>
@@ -16996,10 +16996,10 @@
       </c>
       <c r="E551" s="5" t="n">
         <f aca="false">IF((F551+G551)&gt;0,ROUND((F551+G551)/30,2),"")</f>
-        <v>5</v>
+        <v>1.67</v>
       </c>
       <c r="F551" s="5" t="n">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G551" s="5"/>
     </row>
@@ -17194,10 +17194,10 @@
       </c>
       <c r="E560" s="5" t="n">
         <f aca="false">IF((F560+G560)&gt;0,ROUND((F560+G560)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F560" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G560" s="5"/>
     </row>
@@ -17260,10 +17260,10 @@
       </c>
       <c r="E563" s="5" t="n">
         <f aca="false">IF((F563+G563)&gt;0,ROUND((F563+G563)/30,2),"")</f>
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="F563" s="5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G563" s="5"/>
     </row>
@@ -17282,10 +17282,10 @@
       </c>
       <c r="E564" s="5" t="n">
         <f aca="false">IF((F564+G564)&gt;0,ROUND((F564+G564)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F564" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G564" s="5"/>
     </row>
@@ -17612,10 +17612,10 @@
       </c>
       <c r="E579" s="5" t="n">
         <f aca="false">IF((F579+G579)&gt;0,ROUND((F579+G579)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F579" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G579" s="5"/>
     </row>
@@ -17788,10 +17788,10 @@
       </c>
       <c r="E587" s="5" t="n">
         <f aca="false">IF((F587+G587)&gt;0,ROUND((F587+G587)/30,2),"")</f>
-        <v>1.67</v>
+        <v>0.33</v>
       </c>
       <c r="F587" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G587" s="5"/>
     </row>
@@ -31398,10 +31398,10 @@
       <c r="D1229" s="9"/>
       <c r="E1229" s="5" t="n">
         <f aca="false">IF((F1229+G1229)&gt;0,ROUND((F1229+G1229)/30,2),"")</f>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="F1229" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G1229" s="5"/>
     </row>
@@ -31862,10 +31862,10 @@
       <c r="D1252" s="9"/>
       <c r="E1252" s="5" t="n">
         <f aca="false">IF((F1252+G1252)&gt;0,ROUND((F1252+G1252)/30,2),"")</f>
-        <v>1.67</v>
+        <v>0.17</v>
       </c>
       <c r="F1252" s="5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="G1252" s="5"/>
     </row>
@@ -32102,10 +32102,10 @@
       <c r="D1264" s="9"/>
       <c r="E1264" s="5" t="n">
         <f aca="false">IF((F1264+G1264)&gt;0,ROUND((F1264+G1264)/30,2),"")</f>
-        <v>1.67</v>
+        <v>0.33</v>
       </c>
       <c r="F1264" s="5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G1264" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -5262,10 +5262,10 @@
       </c>
       <c r="E18" s="5" t="n">
         <f aca="false">IF((F18+G18)&gt;0,ROUND((F18+G18)/30,2),"")</f>
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="G18" s="5"/>
     </row>
@@ -5284,12 +5284,14 @@
       </c>
       <c r="E19" s="5" t="n">
         <f aca="false">IF((F19+G19)&gt;0,ROUND((F19+G19)/30,2),"")</f>
-        <v>50</v>
+        <v>66.67</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G19" s="5"/>
+        <v>1900</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5" t="n">
@@ -5372,12 +5374,14 @@
       </c>
       <c r="E23" s="5" t="n">
         <f aca="false">IF((F23+G23)&gt;0,ROUND((F23+G23)/30,2),"")</f>
-        <v>33.33</v>
+        <v>34.33</v>
       </c>
       <c r="F23" s="5" t="n">
         <v>1000</v>
       </c>
-      <c r="G23" s="5"/>
+      <c r="G23" s="5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5" t="n">
@@ -5419,9 +5423,11 @@
         <v>23.33</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="G25" s="5"/>
+        <v>500</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5" t="n">
@@ -7184,9 +7190,11 @@
         <v>20</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>600</v>
-      </c>
-      <c r="G105" s="5"/>
+        <v>100</v>
+      </c>
+      <c r="G105" s="5" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="5" t="n">
@@ -7206,9 +7214,11 @@
         <v>23.33</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>700</v>
-      </c>
-      <c r="G106" s="5"/>
+        <v>500</v>
+      </c>
+      <c r="G106" s="5" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="5" t="n">
@@ -7272,9 +7282,11 @@
         <v>6.67</v>
       </c>
       <c r="F109" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="G109" s="5"/>
+        <v>150</v>
+      </c>
+      <c r="G109" s="5" t="n">
+        <v>50</v>
+      </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="5" t="n">
@@ -7357,12 +7369,14 @@
       </c>
       <c r="E113" s="5" t="n">
         <f aca="false">IF((F113+G113)&gt;0,ROUND((F113+G113)/30,2),"")</f>
-        <v>6.67</v>
+        <v>8.33</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="G113" s="5"/>
+        <v>150</v>
+      </c>
+      <c r="G113" s="5" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="5" t="n">
@@ -8643,10 +8657,10 @@
       </c>
       <c r="E171" s="5" t="n">
         <f aca="false">IF((F171+G171)&gt;0,ROUND((F171+G171)/30,2),"")</f>
-        <v>16.67</v>
+        <v>66.67</v>
       </c>
       <c r="F171" s="5" t="n">
-        <v>500</v>
+        <v>2000</v>
       </c>
       <c r="G171" s="5"/>
     </row>
@@ -9149,10 +9163,10 @@
       </c>
       <c r="E194" s="5" t="n">
         <f aca="false">IF((F194+G194)&gt;0,ROUND((F194+G194)/30,2),"")</f>
-        <v>33.33</v>
+        <v>66.67</v>
       </c>
       <c r="F194" s="5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G194" s="5"/>
     </row>
@@ -9171,10 +9185,10 @@
       </c>
       <c r="E195" s="5" t="n">
         <f aca="false">IF((F195+G195)&gt;0,ROUND((F195+G195)/30,2),"")</f>
-        <v>33.33</v>
+        <v>66.67</v>
       </c>
       <c r="F195" s="5" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="G195" s="5"/>
     </row>
@@ -9193,10 +9207,10 @@
       </c>
       <c r="E196" s="5" t="n">
         <f aca="false">IF((F196+G196)&gt;0,ROUND((F196+G196)/30,2),"")</f>
-        <v>20</v>
+        <v>66.67</v>
       </c>
       <c r="F196" s="5" t="n">
-        <v>600</v>
+        <v>2000</v>
       </c>
       <c r="G196" s="5"/>
     </row>
@@ -16383,9 +16397,11 @@
         <v>5</v>
       </c>
       <c r="F523" s="5" t="n">
-        <v>150</v>
-      </c>
-      <c r="G523" s="5"/>
+        <v>120</v>
+      </c>
+      <c r="G523" s="5" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="524" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A524" s="5" t="n">
@@ -17348,12 +17364,14 @@
       </c>
       <c r="E567" s="5" t="n">
         <f aca="false">IF((F567+G567)&gt;0,ROUND((F567+G567)/30,2),"")</f>
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="F567" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G567" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="G567" s="5" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="568" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A568" s="5" t="n">
@@ -18800,10 +18818,10 @@
       </c>
       <c r="E633" s="5" t="n">
         <f aca="false">IF((F633+G633)&gt;0,ROUND((F633+G633)/30,2),"")</f>
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="F633" s="5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G633" s="5"/>
     </row>
@@ -19264,10 +19282,10 @@
       </c>
       <c r="E654" s="5" t="n">
         <f aca="false">IF((F654+G654)&gt;0,ROUND((F654+G654)/30,2),"")</f>
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="F654" s="5" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G654" s="5"/>
     </row>
@@ -19440,10 +19458,10 @@
       </c>
       <c r="E662" s="5" t="n">
         <f aca="false">IF((F662+G662)&gt;0,ROUND((F662+G662)/30,2),"")</f>
-        <v>3.33</v>
+        <v>5</v>
       </c>
       <c r="F662" s="5" t="n">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="G662" s="5"/>
     </row>
@@ -19638,10 +19656,10 @@
       </c>
       <c r="E671" s="5" t="n">
         <f aca="false">IF((F671+G671)&gt;0,ROUND((F671+G671)/30,2),"")</f>
-        <v>1.67</v>
+        <v>8.33</v>
       </c>
       <c r="F671" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G671" s="5"/>
     </row>
@@ -19966,12 +19984,12 @@
       <c r="D686" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E686" s="5" t="n">
+      <c r="E686" s="5" t="str">
         <f aca="false">IF((F686+G686)&gt;0,ROUND((F686+G686)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F686" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G686" s="5"/>
     </row>
@@ -19990,10 +20008,10 @@
       </c>
       <c r="E687" s="5" t="n">
         <f aca="false">IF((F687+G687)&gt;0,ROUND((F687+G687)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F687" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G687" s="5"/>
     </row>
@@ -20034,10 +20052,10 @@
       </c>
       <c r="E689" s="5" t="n">
         <f aca="false">IF((F689+G689)&gt;0,ROUND((F689+G689)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F689" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G689" s="5"/>
     </row>
@@ -20100,10 +20118,10 @@
       </c>
       <c r="E692" s="5" t="n">
         <f aca="false">IF((F692+G692)&gt;0,ROUND((F692+G692)/30,2),"")</f>
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="F692" s="5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G692" s="5"/>
     </row>
@@ -20210,10 +20228,10 @@
       </c>
       <c r="E697" s="5" t="n">
         <f aca="false">IF((F697+G697)&gt;0,ROUND((F697+G697)/30,2),"")</f>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="F697" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G697" s="5"/>
     </row>
@@ -20738,10 +20756,10 @@
       </c>
       <c r="E721" s="5" t="n">
         <f aca="false">IF((F721+G721)&gt;0,ROUND((F721+G721)/30,2),"")</f>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="F721" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G721" s="5"/>
     </row>
@@ -20914,10 +20932,10 @@
       </c>
       <c r="E729" s="5" t="n">
         <f aca="false">IF((F729+G729)&gt;0,ROUND((F729+G729)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="F729" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G729" s="5"/>
     </row>
@@ -21044,12 +21062,12 @@
       <c r="D735" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E735" s="5" t="n">
+      <c r="E735" s="5" t="str">
         <f aca="false">IF((F735+G735)&gt;0,ROUND((F735+G735)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F735" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G735" s="5"/>
     </row>
@@ -23312,10 +23330,10 @@
       </c>
       <c r="E838" s="5" t="n">
         <f aca="false">IF((F838+G838)&gt;0,ROUND((F838+G838)/30,2),"")</f>
-        <v>4</v>
+        <v>3.33</v>
       </c>
       <c r="F838" s="5" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="G838" s="5"/>
     </row>
@@ -24013,10 +24031,10 @@
       </c>
       <c r="E870" s="5" t="n">
         <f aca="false">IF((F870+G870)&gt;0,ROUND((F870+G870)/30,2),"")</f>
-        <v>3.33</v>
+        <v>2</v>
       </c>
       <c r="F870" s="5" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="G870" s="5"/>
     </row>
@@ -25883,10 +25901,10 @@
       </c>
       <c r="E955" s="5" t="n">
         <f aca="false">IF((F955+G955)&gt;0,ROUND((F955+G955)/30,2),"")</f>
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="F955" s="5" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G955" s="5"/>
     </row>
@@ -25905,10 +25923,10 @@
       </c>
       <c r="E956" s="5" t="n">
         <f aca="false">IF((F956+G956)&gt;0,ROUND((F956+G956)/30,2),"")</f>
-        <v>1.67</v>
+        <v>6</v>
       </c>
       <c r="F956" s="5" t="n">
-        <v>50</v>
+        <v>180</v>
       </c>
       <c r="G956" s="5"/>
     </row>
@@ -25927,10 +25945,10 @@
       </c>
       <c r="E957" s="5" t="n">
         <f aca="false">IF((F957+G957)&gt;0,ROUND((F957+G957)/30,2),"")</f>
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="F957" s="5" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G957" s="5"/>
     </row>
@@ -25947,12 +25965,12 @@
       <c r="D958" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E958" s="5" t="n">
+      <c r="E958" s="5" t="str">
         <f aca="false">IF((F958+G958)&gt;0,ROUND((F958+G958)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F958" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G958" s="5"/>
     </row>
@@ -25993,10 +26011,10 @@
       </c>
       <c r="E960" s="5" t="n">
         <f aca="false">IF((F960+G960)&gt;0,ROUND((F960+G960)/30,2),"")</f>
-        <v>1.67</v>
+        <v>8.33</v>
       </c>
       <c r="F960" s="5" t="n">
-        <v>50</v>
+        <v>250</v>
       </c>
       <c r="G960" s="5"/>
     </row>
@@ -26015,10 +26033,10 @@
       </c>
       <c r="E961" s="5" t="n">
         <f aca="false">IF((F961+G961)&gt;0,ROUND((F961+G961)/30,2),"")</f>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="F961" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G961" s="5"/>
     </row>
@@ -26035,12 +26053,12 @@
       <c r="D962" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E962" s="5" t="n">
+      <c r="E962" s="5" t="str">
         <f aca="false">IF((F962+G962)&gt;0,ROUND((F962+G962)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F962" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G962" s="5"/>
     </row>
@@ -26059,10 +26077,10 @@
       </c>
       <c r="E963" s="5" t="n">
         <f aca="false">IF((F963+G963)&gt;0,ROUND((F963+G963)/30,2),"")</f>
-        <v>1.67</v>
+        <v>16.67</v>
       </c>
       <c r="F963" s="5" t="n">
-        <v>50</v>
+        <v>500</v>
       </c>
       <c r="G963" s="5"/>
     </row>
@@ -26081,10 +26099,10 @@
       </c>
       <c r="E964" s="5" t="n">
         <f aca="false">IF((F964+G964)&gt;0,ROUND((F964+G964)/30,2),"")</f>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="F964" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G964" s="5"/>
     </row>
@@ -26103,10 +26121,10 @@
       </c>
       <c r="E965" s="5" t="n">
         <f aca="false">IF((F965+G965)&gt;0,ROUND((F965+G965)/30,2),"")</f>
-        <v>3.33</v>
+        <v>16.67</v>
       </c>
       <c r="F965" s="5" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="G965" s="5"/>
     </row>
@@ -26125,10 +26143,10 @@
       </c>
       <c r="E966" s="5" t="n">
         <f aca="false">IF((F966+G966)&gt;0,ROUND((F966+G966)/30,2),"")</f>
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="F966" s="5" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G966" s="5"/>
     </row>
@@ -26147,10 +26165,10 @@
       </c>
       <c r="E967" s="5" t="n">
         <f aca="false">IF((F967+G967)&gt;0,ROUND((F967+G967)/30,2),"")</f>
-        <v>3.33</v>
+        <v>8.33</v>
       </c>
       <c r="F967" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G967" s="5"/>
     </row>
@@ -26167,12 +26185,12 @@
       <c r="D968" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E968" s="5" t="n">
+      <c r="E968" s="5" t="str">
         <f aca="false">IF((F968+G968)&gt;0,ROUND((F968+G968)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F968" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G968" s="5"/>
     </row>
@@ -26191,10 +26209,10 @@
       </c>
       <c r="E969" s="5" t="n">
         <f aca="false">IF((F969+G969)&gt;0,ROUND((F969+G969)/30,2),"")</f>
-        <v>3.33</v>
+        <v>6.67</v>
       </c>
       <c r="F969" s="5" t="n">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="G969" s="5"/>
     </row>
@@ -26213,10 +26231,10 @@
       </c>
       <c r="E970" s="5" t="n">
         <f aca="false">IF((F970+G970)&gt;0,ROUND((F970+G970)/30,2),"")</f>
-        <v>1.67</v>
+        <v>5</v>
       </c>
       <c r="F970" s="5" t="n">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="G970" s="5"/>
     </row>
@@ -26255,12 +26273,12 @@
       <c r="D972" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="E972" s="5" t="n">
+      <c r="E972" s="5" t="str">
         <f aca="false">IF((F972+G972)&gt;0,ROUND((F972+G972)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F972" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G972" s="5"/>
     </row>
@@ -26279,10 +26297,10 @@
       </c>
       <c r="E973" s="5" t="n">
         <f aca="false">IF((F973+G973)&gt;0,ROUND((F973+G973)/30,2),"")</f>
-        <v>1.67</v>
+        <v>3.33</v>
       </c>
       <c r="F973" s="5" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G973" s="5"/>
     </row>
@@ -33164,10 +33182,10 @@
       <c r="D1317" s="9"/>
       <c r="E1317" s="5" t="n">
         <f aca="false">IF((F1317+G1317)&gt;0,ROUND((F1317+G1317)/30,2),"")</f>
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="F1317" s="5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G1317" s="5"/>
     </row>
@@ -33202,12 +33220,12 @@
         <v>44</v>
       </c>
       <c r="D1319" s="9"/>
-      <c r="E1319" s="5" t="n">
+      <c r="E1319" s="5" t="str">
         <f aca="false">IF((F1319+G1319)&gt;0,ROUND((F1319+G1319)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1319" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1319" s="5"/>
     </row>
@@ -33222,12 +33240,12 @@
         <v>44</v>
       </c>
       <c r="D1320" s="9"/>
-      <c r="E1320" s="5" t="n">
+      <c r="E1320" s="5" t="str">
         <f aca="false">IF((F1320+G1320)&gt;0,ROUND((F1320+G1320)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F1320" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G1320" s="5"/>
     </row>
@@ -34226,10 +34244,10 @@
       <c r="D1370" s="9"/>
       <c r="E1370" s="5" t="n">
         <f aca="false">IF((F1370+G1370)&gt;0,ROUND((F1370+G1370)/30,2),"")</f>
-        <v>3.33</v>
+        <v>10</v>
       </c>
       <c r="F1370" s="5" t="n">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="G1370" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -6180,12 +6180,14 @@
       </c>
       <c r="E59" s="5" t="n">
         <f aca="false">IF((F59+G59)&gt;0,ROUND((F59+G59)/30,2),"")</f>
-        <v>300</v>
+        <v>366.67</v>
       </c>
       <c r="F59" s="5" t="n">
         <v>9000</v>
       </c>
-      <c r="G59" s="5"/>
+      <c r="G59" s="5" t="n">
+        <v>2000</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5" t="n">
@@ -7973,12 +7975,14 @@
       </c>
       <c r="E140" s="5" t="n">
         <f aca="false">IF((F140+G140)&gt;0,ROUND((F140+G140)/30,2),"")</f>
-        <v>50</v>
+        <v>33.33</v>
       </c>
       <c r="F140" s="5" t="n">
-        <v>1500</v>
-      </c>
-      <c r="G140" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="G140" s="5" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="5" t="n">
@@ -8635,10 +8639,10 @@
       </c>
       <c r="E170" s="5" t="n">
         <f aca="false">IF((F170+G170)&gt;0,ROUND((F170+G170)/30,2),"")</f>
-        <v>66.67</v>
+        <v>83.33</v>
       </c>
       <c r="F170" s="5" t="n">
-        <v>2000</v>
+        <v>2500</v>
       </c>
       <c r="G170" s="5"/>
     </row>
@@ -8855,12 +8859,14 @@
       </c>
       <c r="E180" s="5" t="n">
         <f aca="false">IF((F180+G180)&gt;0,ROUND((F180+G180)/30,2),"")</f>
-        <v>1.67</v>
+        <v>100</v>
       </c>
       <c r="F180" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G180" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="G180" s="5" t="n">
+        <v>3000</v>
+      </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="5" t="n">
@@ -12498,12 +12504,14 @@
       </c>
       <c r="E346" s="5" t="n">
         <f aca="false">IF((F346+G346)&gt;0,ROUND((F346+G346)/30,2),"")</f>
-        <v>1.67</v>
+        <v>4.33</v>
       </c>
       <c r="F346" s="5" t="n">
         <v>50</v>
       </c>
-      <c r="G346" s="5"/>
+      <c r="G346" s="5" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="347" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A347" s="5" t="n">
@@ -13820,12 +13828,14 @@
       </c>
       <c r="E406" s="5" t="n">
         <f aca="false">IF((F406+G406)&gt;0,ROUND((F406+G406)/30,2),"")</f>
-        <v>1.67</v>
+        <v>7.67</v>
       </c>
       <c r="F406" s="5" t="n">
-        <v>50</v>
-      </c>
-      <c r="G406" s="5"/>
+        <v>150</v>
+      </c>
+      <c r="G406" s="5" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="407" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A407" s="5" t="n">
@@ -18996,12 +19006,14 @@
       </c>
       <c r="E641" s="5" t="n">
         <f aca="false">IF((F641+G641)&gt;0,ROUND((F641+G641)/30,2),"")</f>
-        <v>6.67</v>
+        <v>10</v>
       </c>
       <c r="F641" s="5" t="n">
-        <v>200</v>
-      </c>
-      <c r="G641" s="5"/>
+        <v>0</v>
+      </c>
+      <c r="G641" s="5" t="n">
+        <v>300</v>
+      </c>
     </row>
     <row r="642" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A642" s="5" t="n">
@@ -34302,14 +34314,16 @@
         <v>75</v>
       </c>
       <c r="D1373" s="9"/>
-      <c r="E1373" s="5" t="str">
+      <c r="E1373" s="5" t="n">
         <f aca="false">IF((F1373+G1373)&gt;0,ROUND((F1373+G1373)/30,2),"")</f>
-        <v/>
+        <v>16.67</v>
       </c>
       <c r="F1373" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G1373" s="5"/>
+      <c r="G1373" s="5" t="n">
+        <v>500</v>
+      </c>
     </row>
     <row r="1374" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1374" s="5" t="n">

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -19052,10 +19052,10 @@
       </c>
       <c r="E643" s="5" t="n">
         <f aca="false">IF((F643+G643)&gt;0,ROUND((F643+G643)/30,2),"")</f>
-        <v>3.33</v>
+        <v>8.33</v>
       </c>
       <c r="F643" s="5" t="n">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="G643" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -5692,13 +5692,13 @@
       </c>
       <c r="E37" s="5" t="n">
         <f aca="false">IF((F37+G37)&gt;0,ROUND((F37+G37)/30,2),"")</f>
-        <v>33.33</v>
+        <v>203.33</v>
       </c>
       <c r="F37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>1000</v>
+        <v>6100</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -32672,12 +32672,12 @@
       <c r="D1291" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="E1291" s="5" t="n">
+      <c r="E1291" s="5" t="str">
         <f aca="false">IF((F1291+G1291)&gt;0,ROUND((F1291+G1291)/30,2),"")</f>
-        <v>203.33</v>
+        <v/>
       </c>
       <c r="F1291" s="5" t="n">
-        <v>6100</v>
+        <v>0</v>
       </c>
       <c r="G1291" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -698,79 +698,79 @@
     <t xml:space="preserve">Баласина-24</t>
   </si>
   <si>
+    <t xml:space="preserve">Баласина-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Баласина-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гладкий 12 (Немерный)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25-Пистон (танга)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ойна держатель №-32 (43х43)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гладкий 8 (Немерный)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пласт-40х20</t>
+  </si>
+  <si>
     <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-28</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Баласина-13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гладкий 12 (Немерный)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25-Пистон (танга)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ойна держатель №-32 (43х43)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Гладкий 8 (Немерный)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Пласт-40х20</t>
   </si>
   <si>
     <t xml:space="preserve">Пистон-38</t>
@@ -4932,10 +4932,10 @@
       </c>
       <c r="E3" s="5" t="n">
         <f aca="false">IF((F3+G3)&gt;0,ROUND((F3+G3)/30,2),"")</f>
-        <v>933.33</v>
+        <v>1000</v>
       </c>
       <c r="F3" s="5" t="n">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="G3" s="5"/>
     </row>
@@ -4954,10 +4954,10 @@
       </c>
       <c r="E4" s="5" t="n">
         <f aca="false">IF((F4+G4)&gt;0,ROUND((F4+G4)/30,2),"")</f>
-        <v>433.33</v>
+        <v>666.67</v>
       </c>
       <c r="F4" s="5" t="n">
-        <v>13000</v>
+        <v>20000</v>
       </c>
       <c r="G4" s="5"/>
     </row>
@@ -4976,10 +4976,10 @@
       </c>
       <c r="E5" s="5" t="n">
         <f aca="false">IF((F5+G5)&gt;0,ROUND((F5+G5)/30,2),"")</f>
-        <v>433.33</v>
+        <v>733.33</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>13000</v>
+        <v>22000</v>
       </c>
       <c r="G5" s="5"/>
     </row>
@@ -4998,10 +4998,10 @@
       </c>
       <c r="E6" s="5" t="n">
         <f aca="false">IF((F6+G6)&gt;0,ROUND((F6+G6)/30,2),"")</f>
-        <v>266.67</v>
+        <v>433.33</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>8000</v>
+        <v>13000</v>
       </c>
       <c r="G6" s="5"/>
     </row>
@@ -7821,10 +7821,10 @@
       </c>
       <c r="E133" s="5" t="n">
         <f aca="false">IF((F133+G133)&gt;0,ROUND((F133+G133)/30,2),"")</f>
-        <v>100</v>
+        <v>83.33</v>
       </c>
       <c r="F133" s="5" t="n">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="G133" s="5"/>
     </row>
@@ -7909,10 +7909,10 @@
       </c>
       <c r="E137" s="5" t="n">
         <f aca="false">IF((F137+G137)&gt;0,ROUND((F137+G137)/30,2),"")</f>
-        <v>23.33</v>
+        <v>33.33</v>
       </c>
       <c r="F137" s="5" t="n">
-        <v>700</v>
+        <v>1000</v>
       </c>
       <c r="G137" s="5"/>
     </row>
@@ -7951,12 +7951,12 @@
       <c r="D139" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E139" s="5" t="n">
+      <c r="E139" s="5" t="str">
         <f aca="false">IF((F139+G139)&gt;0,ROUND((F139+G139)/30,2),"")</f>
-        <v>13.33</v>
+        <v/>
       </c>
       <c r="F139" s="5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G139" s="5"/>
     </row>
@@ -8043,10 +8043,10 @@
       </c>
       <c r="E143" s="5" t="n">
         <f aca="false">IF((F143+G143)&gt;0,ROUND((F143+G143)/30,2),"")</f>
-        <v>16.67</v>
+        <v>15</v>
       </c>
       <c r="F143" s="5" t="n">
-        <v>500</v>
+        <v>450</v>
       </c>
       <c r="G143" s="5"/>
     </row>
@@ -9330,14 +9330,14 @@
         <v>11</v>
       </c>
       <c r="D202" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E202" s="5" t="n">
         <f aca="false">IF((F202+G202)&gt;0,ROUND((F202+G202)/30,2),"")</f>
-        <v>25</v>
+        <v>166.67</v>
       </c>
       <c r="F202" s="5" t="n">
-        <v>750</v>
+        <v>5000</v>
       </c>
       <c r="G202" s="5"/>
     </row>
@@ -9346,20 +9346,20 @@
         <v>202</v>
       </c>
       <c r="B203" s="5" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C203" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D203" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E203" s="5" t="n">
         <f aca="false">IF((F203+G203)&gt;0,ROUND((F203+G203)/30,2),"")</f>
-        <v>23.33</v>
+        <v>166.67</v>
       </c>
       <c r="F203" s="5" t="n">
-        <v>700</v>
+        <v>5000</v>
       </c>
       <c r="G203" s="5"/>
     </row>
@@ -9368,20 +9368,20 @@
         <v>203</v>
       </c>
       <c r="B204" s="5" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C204" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D204" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E204" s="5" t="n">
         <f aca="false">IF((F204+G204)&gt;0,ROUND((F204+G204)/30,2),"")</f>
-        <v>25</v>
+        <v>13.33</v>
       </c>
       <c r="F204" s="5" t="n">
-        <v>750</v>
+        <v>400</v>
       </c>
       <c r="G204" s="5"/>
     </row>
@@ -9390,20 +9390,20 @@
         <v>204</v>
       </c>
       <c r="B205" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C205" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D205" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E205" s="5" t="n">
         <f aca="false">IF((F205+G205)&gt;0,ROUND((F205+G205)/30,2),"")</f>
-        <v>166.67</v>
+        <v>266.67</v>
       </c>
       <c r="F205" s="5" t="n">
-        <v>5000</v>
+        <v>8000</v>
       </c>
       <c r="G205" s="5"/>
     </row>
@@ -9412,20 +9412,20 @@
         <v>205</v>
       </c>
       <c r="B206" s="5" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C206" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D206" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E206" s="5" t="n">
         <f aca="false">IF((F206+G206)&gt;0,ROUND((F206+G206)/30,2),"")</f>
-        <v>23.33</v>
+        <v>166.67</v>
       </c>
       <c r="F206" s="5" t="n">
-        <v>700</v>
+        <v>5000</v>
       </c>
       <c r="G206" s="5"/>
     </row>
@@ -9434,13 +9434,13 @@
         <v>206</v>
       </c>
       <c r="B207" s="5" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C207" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D207" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E207" s="5" t="n">
         <f aca="false">IF((F207+G207)&gt;0,ROUND((F207+G207)/30,2),"")</f>
@@ -9456,20 +9456,20 @@
         <v>207</v>
       </c>
       <c r="B208" s="5" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C208" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D208" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E208" s="5" t="n">
         <f aca="false">IF((F208+G208)&gt;0,ROUND((F208+G208)/30,2),"")</f>
-        <v>63.33</v>
+        <v>166.67</v>
       </c>
       <c r="F208" s="5" t="n">
-        <v>1900</v>
+        <v>5000</v>
       </c>
       <c r="G208" s="5"/>
     </row>
@@ -9478,20 +9478,20 @@
         <v>208</v>
       </c>
       <c r="B209" s="5" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C209" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D209" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E209" s="5" t="n">
         <f aca="false">IF((F209+G209)&gt;0,ROUND((F209+G209)/30,2),"")</f>
-        <v>5</v>
+        <v>166.67</v>
       </c>
       <c r="F209" s="5" t="n">
-        <v>150</v>
+        <v>5000</v>
       </c>
       <c r="G209" s="5"/>
     </row>
@@ -9500,20 +9500,20 @@
         <v>209</v>
       </c>
       <c r="B210" s="5" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C210" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D210" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E210" s="5" t="n">
         <f aca="false">IF((F210+G210)&gt;0,ROUND((F210+G210)/30,2),"")</f>
-        <v>3.33</v>
+        <v>133.33</v>
       </c>
       <c r="F210" s="5" t="n">
-        <v>100</v>
+        <v>4000</v>
       </c>
       <c r="G210" s="5"/>
     </row>
@@ -9522,20 +9522,20 @@
         <v>210</v>
       </c>
       <c r="B211" s="5" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C211" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D211" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E211" s="5" t="n">
         <f aca="false">IF((F211+G211)&gt;0,ROUND((F211+G211)/30,2),"")</f>
-        <v>33.33</v>
+        <v>433.33</v>
       </c>
       <c r="F211" s="5" t="n">
-        <v>1000</v>
+        <v>13000</v>
       </c>
       <c r="G211" s="5"/>
     </row>
@@ -9544,20 +9544,20 @@
         <v>211</v>
       </c>
       <c r="B212" s="5" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C212" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D212" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E212" s="5" t="n">
         <f aca="false">IF((F212+G212)&gt;0,ROUND((F212+G212)/30,2),"")</f>
-        <v>1.67</v>
+        <v>233.33</v>
       </c>
       <c r="F212" s="5" t="n">
-        <v>50</v>
+        <v>7000</v>
       </c>
       <c r="G212" s="5"/>
     </row>
@@ -9566,20 +9566,20 @@
         <v>212</v>
       </c>
       <c r="B213" s="5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C213" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D213" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E213" s="5" t="n">
         <f aca="false">IF((F213+G213)&gt;0,ROUND((F213+G213)/30,2),"")</f>
-        <v>31.67</v>
+        <v>166.67</v>
       </c>
       <c r="F213" s="5" t="n">
-        <v>950</v>
+        <v>5000</v>
       </c>
       <c r="G213" s="5"/>
     </row>
@@ -9588,20 +9588,20 @@
         <v>213</v>
       </c>
       <c r="B214" s="5" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C214" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D214" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E214" s="5" t="n">
         <f aca="false">IF((F214+G214)&gt;0,ROUND((F214+G214)/30,2),"")</f>
-        <v>1.67</v>
+        <v>13.33</v>
       </c>
       <c r="F214" s="5" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="G214" s="5"/>
     </row>
@@ -9610,20 +9610,20 @@
         <v>214</v>
       </c>
       <c r="B215" s="5" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C215" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D215" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E215" s="5" t="n">
         <f aca="false">IF((F215+G215)&gt;0,ROUND((F215+G215)/30,2),"")</f>
-        <v>3.33</v>
+        <v>233.33</v>
       </c>
       <c r="F215" s="5" t="n">
-        <v>100</v>
+        <v>7000</v>
       </c>
       <c r="G215" s="5"/>
     </row>
@@ -9632,20 +9632,20 @@
         <v>215</v>
       </c>
       <c r="B216" s="5" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C216" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D216" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E216" s="5" t="n">
         <f aca="false">IF((F216+G216)&gt;0,ROUND((F216+G216)/30,2),"")</f>
-        <v>1.67</v>
+        <v>13.33</v>
       </c>
       <c r="F216" s="5" t="n">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="G216" s="5"/>
     </row>
@@ -9654,20 +9654,20 @@
         <v>216</v>
       </c>
       <c r="B217" s="5" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C217" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D217" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E217" s="5" t="n">
         <f aca="false">IF((F217+G217)&gt;0,ROUND((F217+G217)/30,2),"")</f>
-        <v>1.67</v>
+        <v>166.67</v>
       </c>
       <c r="F217" s="5" t="n">
-        <v>50</v>
+        <v>5000</v>
       </c>
       <c r="G217" s="5"/>
     </row>
@@ -9676,20 +9676,20 @@
         <v>217</v>
       </c>
       <c r="B218" s="5" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C218" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D218" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E218" s="5" t="n">
         <f aca="false">IF((F218+G218)&gt;0,ROUND((F218+G218)/30,2),"")</f>
-        <v>26.67</v>
+        <v>133.33</v>
       </c>
       <c r="F218" s="5" t="n">
-        <v>800</v>
+        <v>4000</v>
       </c>
       <c r="G218" s="5"/>
     </row>
@@ -9698,20 +9698,20 @@
         <v>218</v>
       </c>
       <c r="B219" s="5" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C219" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D219" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E219" s="5" t="n">
         <f aca="false">IF((F219+G219)&gt;0,ROUND((F219+G219)/30,2),"")</f>
-        <v>16.67</v>
+        <v>166.67</v>
       </c>
       <c r="F219" s="5" t="n">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="G219" s="5"/>
     </row>
@@ -9720,20 +9720,20 @@
         <v>219</v>
       </c>
       <c r="B220" s="5" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C220" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D220" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E220" s="5" t="n">
         <f aca="false">IF((F220+G220)&gt;0,ROUND((F220+G220)/30,2),"")</f>
-        <v>5</v>
+        <v>166.67</v>
       </c>
       <c r="F220" s="5" t="n">
-        <v>150</v>
+        <v>5000</v>
       </c>
       <c r="G220" s="5"/>
     </row>
@@ -9742,20 +9742,20 @@
         <v>220</v>
       </c>
       <c r="B221" s="5" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C221" s="5" t="s">
         <v>11</v>
       </c>
       <c r="D221" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E221" s="5" t="n">
         <f aca="false">IF((F221+G221)&gt;0,ROUND((F221+G221)/30,2),"")</f>
-        <v>1.67</v>
+        <v>10</v>
       </c>
       <c r="F221" s="5" t="n">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="G221" s="5"/>
     </row>
@@ -9764,13 +9764,13 @@
         <v>221</v>
       </c>
       <c r="B222" s="5" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C222" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D222" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E222" s="5" t="n">
         <f aca="false">IF((F222+G222)&gt;0,ROUND((F222+G222)/30,2),"")</f>
@@ -9786,13 +9786,13 @@
         <v>222</v>
       </c>
       <c r="B223" s="5" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C223" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D223" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E223" s="5" t="n">
         <f aca="false">IF((F223+G223)&gt;0,ROUND((F223+G223)/30,2),"")</f>
@@ -9808,13 +9808,13 @@
         <v>223</v>
       </c>
       <c r="B224" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C224" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D224" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E224" s="5" t="n">
         <f aca="false">IF((F224+G224)&gt;0,ROUND((F224+G224)/30,2),"")</f>
@@ -9830,13 +9830,13 @@
         <v>224</v>
       </c>
       <c r="B225" s="5" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C225" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D225" s="8" t="s">
-        <v>224</v>
+        <v>12</v>
       </c>
       <c r="E225" s="5" t="n">
         <f aca="false">IF((F225+G225)&gt;0,ROUND((F225+G225)/30,2),"")</f>
@@ -9852,13 +9852,13 @@
         <v>225</v>
       </c>
       <c r="B226" s="5" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C226" s="5" t="s">
         <v>17</v>
       </c>
       <c r="D226" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E226" s="5" t="n">
         <f aca="false">IF((F226+G226)&gt;0,ROUND((F226+G226)/30,2),"")</f>
@@ -9880,7 +9880,7 @@
         <v>17</v>
       </c>
       <c r="D227" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E227" s="5" t="n">
         <f aca="false">IF((F227+G227)&gt;0,ROUND((F227+G227)/30,2),"")</f>
@@ -9902,7 +9902,7 @@
         <v>17</v>
       </c>
       <c r="D228" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E228" s="5" t="str">
         <f aca="false">IF((F228+G228)&gt;0,ROUND((F228+G228)/30,2),"")</f>
@@ -9924,7 +9924,7 @@
         <v>17</v>
       </c>
       <c r="D229" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E229" s="5" t="n">
         <f aca="false">IF((F229+G229)&gt;0,ROUND((F229+G229)/30,2),"")</f>
@@ -9946,7 +9946,7 @@
         <v>17</v>
       </c>
       <c r="D230" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E230" s="5" t="n">
         <f aca="false">IF((F230+G230)&gt;0,ROUND((F230+G230)/30,2),"")</f>
@@ -9968,7 +9968,7 @@
         <v>17</v>
       </c>
       <c r="D231" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E231" s="5" t="n">
         <f aca="false">IF((F231+G231)&gt;0,ROUND((F231+G231)/30,2),"")</f>
@@ -9990,7 +9990,7 @@
         <v>17</v>
       </c>
       <c r="D232" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E232" s="5" t="n">
         <f aca="false">IF((F232+G232)&gt;0,ROUND((F232+G232)/30,2),"")</f>
@@ -10012,7 +10012,7 @@
         <v>17</v>
       </c>
       <c r="D233" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E233" s="5" t="n">
         <f aca="false">IF((F233+G233)&gt;0,ROUND((F233+G233)/30,2),"")</f>
@@ -10034,7 +10034,7 @@
         <v>17</v>
       </c>
       <c r="D234" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E234" s="5" t="n">
         <f aca="false">IF((F234+G234)&gt;0,ROUND((F234+G234)/30,2),"")</f>
@@ -10056,7 +10056,7 @@
         <v>17</v>
       </c>
       <c r="D235" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E235" s="5" t="n">
         <f aca="false">IF((F235+G235)&gt;0,ROUND((F235+G235)/30,2),"")</f>
@@ -10078,7 +10078,7 @@
         <v>17</v>
       </c>
       <c r="D236" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E236" s="5" t="n">
         <f aca="false">IF((F236+G236)&gt;0,ROUND((F236+G236)/30,2),"")</f>
@@ -10100,7 +10100,7 @@
         <v>17</v>
       </c>
       <c r="D237" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E237" s="5" t="str">
         <f aca="false">IF((F237+G237)&gt;0,ROUND((F237+G237)/30,2),"")</f>
@@ -10122,7 +10122,7 @@
         <v>17</v>
       </c>
       <c r="D238" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E238" s="5" t="n">
         <f aca="false">IF((F238+G238)&gt;0,ROUND((F238+G238)/30,2),"")</f>
@@ -10144,7 +10144,7 @@
         <v>17</v>
       </c>
       <c r="D239" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E239" s="5" t="n">
         <f aca="false">IF((F239+G239)&gt;0,ROUND((F239+G239)/30,2),"")</f>
@@ -10166,7 +10166,7 @@
         <v>17</v>
       </c>
       <c r="D240" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E240" s="5" t="n">
         <f aca="false">IF((F240+G240)&gt;0,ROUND((F240+G240)/30,2),"")</f>
@@ -10188,7 +10188,7 @@
         <v>17</v>
       </c>
       <c r="D241" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E241" s="5" t="n">
         <f aca="false">IF((F241+G241)&gt;0,ROUND((F241+G241)/30,2),"")</f>
@@ -10210,7 +10210,7 @@
         <v>17</v>
       </c>
       <c r="D242" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E242" s="5" t="n">
         <f aca="false">IF((F242+G242)&gt;0,ROUND((F242+G242)/30,2),"")</f>
@@ -10232,7 +10232,7 @@
         <v>17</v>
       </c>
       <c r="D243" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E243" s="5" t="n">
         <f aca="false">IF((F243+G243)&gt;0,ROUND((F243+G243)/30,2),"")</f>
@@ -10254,7 +10254,7 @@
         <v>17</v>
       </c>
       <c r="D244" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E244" s="5" t="n">
         <f aca="false">IF((F244+G244)&gt;0,ROUND((F244+G244)/30,2),"")</f>
@@ -10276,7 +10276,7 @@
         <v>17</v>
       </c>
       <c r="D245" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E245" s="5" t="n">
         <f aca="false">IF((F245+G245)&gt;0,ROUND((F245+G245)/30,2),"")</f>
@@ -10298,7 +10298,7 @@
         <v>17</v>
       </c>
       <c r="D246" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E246" s="5" t="n">
         <f aca="false">IF((F246+G246)&gt;0,ROUND((F246+G246)/30,2),"")</f>
@@ -10320,7 +10320,7 @@
         <v>17</v>
       </c>
       <c r="D247" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E247" s="5" t="n">
         <f aca="false">IF((F247+G247)&gt;0,ROUND((F247+G247)/30,2),"")</f>
@@ -10342,7 +10342,7 @@
         <v>17</v>
       </c>
       <c r="D248" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E248" s="5" t="n">
         <f aca="false">IF((F248+G248)&gt;0,ROUND((F248+G248)/30,2),"")</f>
@@ -10364,7 +10364,7 @@
         <v>17</v>
       </c>
       <c r="D249" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E249" s="5" t="n">
         <f aca="false">IF((F249+G249)&gt;0,ROUND((F249+G249)/30,2),"")</f>
@@ -10386,7 +10386,7 @@
         <v>17</v>
       </c>
       <c r="D250" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E250" s="5" t="n">
         <f aca="false">IF((F250+G250)&gt;0,ROUND((F250+G250)/30,2),"")</f>
@@ -10408,7 +10408,7 @@
         <v>17</v>
       </c>
       <c r="D251" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E251" s="5" t="n">
         <f aca="false">IF((F251+G251)&gt;0,ROUND((F251+G251)/30,2),"")</f>
@@ -10430,7 +10430,7 @@
         <v>17</v>
       </c>
       <c r="D252" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E252" s="5" t="str">
         <f aca="false">IF((F252+G252)&gt;0,ROUND((F252+G252)/30,2),"")</f>
@@ -10452,7 +10452,7 @@
         <v>17</v>
       </c>
       <c r="D253" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E253" s="5" t="n">
         <f aca="false">IF((F253+G253)&gt;0,ROUND((F253+G253)/30,2),"")</f>
@@ -10474,7 +10474,7 @@
         <v>17</v>
       </c>
       <c r="D254" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E254" s="5" t="n">
         <f aca="false">IF((F254+G254)&gt;0,ROUND((F254+G254)/30,2),"")</f>
@@ -10496,7 +10496,7 @@
         <v>17</v>
       </c>
       <c r="D255" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E255" s="5" t="n">
         <f aca="false">IF((F255+G255)&gt;0,ROUND((F255+G255)/30,2),"")</f>
@@ -10518,7 +10518,7 @@
         <v>17</v>
       </c>
       <c r="D256" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E256" s="5" t="n">
         <f aca="false">IF((F256+G256)&gt;0,ROUND((F256+G256)/30,2),"")</f>
@@ -10540,7 +10540,7 @@
         <v>17</v>
       </c>
       <c r="D257" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E257" s="5" t="n">
         <f aca="false">IF((F257+G257)&gt;0,ROUND((F257+G257)/30,2),"")</f>
@@ -10562,7 +10562,7 @@
         <v>17</v>
       </c>
       <c r="D258" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E258" s="5" t="n">
         <f aca="false">IF((F258+G258)&gt;0,ROUND((F258+G258)/30,2),"")</f>
@@ -10584,7 +10584,7 @@
         <v>17</v>
       </c>
       <c r="D259" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E259" s="5" t="n">
         <f aca="false">IF((F259+G259)&gt;0,ROUND((F259+G259)/30,2),"")</f>
@@ -10628,7 +10628,7 @@
         <v>17</v>
       </c>
       <c r="D261" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E261" s="5" t="n">
         <f aca="false">IF((F261+G261)&gt;0,ROUND((F261+G261)/30,2),"")</f>
@@ -10650,7 +10650,7 @@
         <v>17</v>
       </c>
       <c r="D262" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E262" s="5" t="n">
         <f aca="false">IF((F262+G262)&gt;0,ROUND((F262+G262)/30,2),"")</f>
@@ -10674,7 +10674,7 @@
         <v>17</v>
       </c>
       <c r="D263" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E263" s="5" t="n">
         <f aca="false">IF((F263+G263)&gt;0,ROUND((F263+G263)/30,2),"")</f>
@@ -10696,7 +10696,7 @@
         <v>17</v>
       </c>
       <c r="D264" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E264" s="5" t="n">
         <f aca="false">IF((F264+G264)&gt;0,ROUND((F264+G264)/30,2),"")</f>
@@ -10718,7 +10718,7 @@
         <v>17</v>
       </c>
       <c r="D265" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E265" s="5" t="str">
         <f aca="false">IF((F265+G265)&gt;0,ROUND((F265+G265)/30,2),"")</f>
@@ -10740,7 +10740,7 @@
         <v>17</v>
       </c>
       <c r="D266" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E266" s="5" t="n">
         <f aca="false">IF((F266+G266)&gt;0,ROUND((F266+G266)/30,2),"")</f>
@@ -10762,7 +10762,7 @@
         <v>17</v>
       </c>
       <c r="D267" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E267" s="5" t="str">
         <f aca="false">IF((F267+G267)&gt;0,ROUND((F267+G267)/30,2),"")</f>
@@ -10784,7 +10784,7 @@
         <v>17</v>
       </c>
       <c r="D268" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E268" s="5" t="n">
         <f aca="false">IF((F268+G268)&gt;0,ROUND((F268+G268)/30,2),"")</f>
@@ -10806,7 +10806,7 @@
         <v>17</v>
       </c>
       <c r="D269" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E269" s="5" t="n">
         <f aca="false">IF((F269+G269)&gt;0,ROUND((F269+G269)/30,2),"")</f>
@@ -10828,7 +10828,7 @@
         <v>17</v>
       </c>
       <c r="D270" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E270" s="5" t="n">
         <f aca="false">IF((F270+G270)&gt;0,ROUND((F270+G270)/30,2),"")</f>
@@ -10850,7 +10850,7 @@
         <v>17</v>
       </c>
       <c r="D271" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E271" s="5" t="n">
         <f aca="false">IF((F271+G271)&gt;0,ROUND((F271+G271)/30,2),"")</f>
@@ -10872,7 +10872,7 @@
         <v>17</v>
       </c>
       <c r="D272" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E272" s="5" t="str">
         <f aca="false">IF((F272+G272)&gt;0,ROUND((F272+G272)/30,2),"")</f>
@@ -10894,7 +10894,7 @@
         <v>17</v>
       </c>
       <c r="D273" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E273" s="5" t="str">
         <f aca="false">IF((F273+G273)&gt;0,ROUND((F273+G273)/30,2),"")</f>
@@ -10916,7 +10916,7 @@
         <v>17</v>
       </c>
       <c r="D274" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E274" s="5" t="str">
         <f aca="false">IF((F274+G274)&gt;0,ROUND((F274+G274)/30,2),"")</f>
@@ -10938,7 +10938,7 @@
         <v>17</v>
       </c>
       <c r="D275" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E275" s="5" t="n">
         <f aca="false">IF((F275+G275)&gt;0,ROUND((F275+G275)/30,2),"")</f>
@@ -10960,7 +10960,7 @@
         <v>17</v>
       </c>
       <c r="D276" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E276" s="5" t="n">
         <f aca="false">IF((F276+G276)&gt;0,ROUND((F276+G276)/30,2),"")</f>
@@ -10982,7 +10982,7 @@
         <v>17</v>
       </c>
       <c r="D277" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E277" s="5" t="str">
         <f aca="false">IF((F277+G277)&gt;0,ROUND((F277+G277)/30,2),"")</f>
@@ -11004,7 +11004,7 @@
         <v>17</v>
       </c>
       <c r="D278" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E278" s="5" t="n">
         <f aca="false">IF((F278+G278)&gt;0,ROUND((F278+G278)/30,2),"")</f>
@@ -11026,7 +11026,7 @@
         <v>17</v>
       </c>
       <c r="D279" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E279" s="5" t="n">
         <f aca="false">IF((F279+G279)&gt;0,ROUND((F279+G279)/30,2),"")</f>
@@ -11070,7 +11070,7 @@
         <v>17</v>
       </c>
       <c r="D281" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E281" s="5" t="str">
         <f aca="false">IF((F281+G281)&gt;0,ROUND((F281+G281)/30,2),"")</f>
@@ -11092,7 +11092,7 @@
         <v>17</v>
       </c>
       <c r="D282" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E282" s="5" t="n">
         <f aca="false">IF((F282+G282)&gt;0,ROUND((F282+G282)/30,2),"")</f>
@@ -11114,7 +11114,7 @@
         <v>17</v>
       </c>
       <c r="D283" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E283" s="5" t="n">
         <f aca="false">IF((F283+G283)&gt;0,ROUND((F283+G283)/30,2),"")</f>
@@ -11158,7 +11158,7 @@
         <v>17</v>
       </c>
       <c r="D285" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E285" s="5" t="n">
         <f aca="false">IF((F285+G285)&gt;0,ROUND((F285+G285)/30,2),"")</f>
@@ -11180,7 +11180,7 @@
         <v>17</v>
       </c>
       <c r="D286" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E286" s="5" t="str">
         <f aca="false">IF((F286+G286)&gt;0,ROUND((F286+G286)/30,2),"")</f>
@@ -11202,7 +11202,7 @@
         <v>17</v>
       </c>
       <c r="D287" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E287" s="5" t="n">
         <f aca="false">IF((F287+G287)&gt;0,ROUND((F287+G287)/30,2),"")</f>
@@ -11224,7 +11224,7 @@
         <v>17</v>
       </c>
       <c r="D288" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E288" s="5" t="str">
         <f aca="false">IF((F288+G288)&gt;0,ROUND((F288+G288)/30,2),"")</f>
@@ -11246,7 +11246,7 @@
         <v>17</v>
       </c>
       <c r="D289" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E289" s="5" t="n">
         <f aca="false">IF((F289+G289)&gt;0,ROUND((F289+G289)/30,2),"")</f>
@@ -11268,7 +11268,7 @@
         <v>17</v>
       </c>
       <c r="D290" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E290" s="5" t="str">
         <f aca="false">IF((F290+G290)&gt;0,ROUND((F290+G290)/30,2),"")</f>
@@ -11290,7 +11290,7 @@
         <v>17</v>
       </c>
       <c r="D291" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E291" s="5" t="str">
         <f aca="false">IF((F291+G291)&gt;0,ROUND((F291+G291)/30,2),"")</f>
@@ -11334,7 +11334,7 @@
         <v>17</v>
       </c>
       <c r="D293" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E293" s="5" t="n">
         <f aca="false">IF((F293+G293)&gt;0,ROUND((F293+G293)/30,2),"")</f>
@@ -11378,16 +11378,18 @@
         <v>17</v>
       </c>
       <c r="D295" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E295" s="5" t="n">
         <f aca="false">IF((F295+G295)&gt;0,ROUND((F295+G295)/30,2),"")</f>
         <v>38.33</v>
       </c>
       <c r="F295" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G295" s="5" t="n">
         <v>1150</v>
       </c>
-      <c r="G295" s="5"/>
     </row>
     <row r="296" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A296" s="5" t="n">
@@ -11400,7 +11402,7 @@
         <v>17</v>
       </c>
       <c r="D296" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E296" s="5" t="n">
         <f aca="false">IF((F296+G296)&gt;0,ROUND((F296+G296)/30,2),"")</f>
@@ -11422,7 +11424,7 @@
         <v>17</v>
       </c>
       <c r="D297" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E297" s="5" t="n">
         <f aca="false">IF((F297+G297)&gt;0,ROUND((F297+G297)/30,2),"")</f>
@@ -11444,7 +11446,7 @@
         <v>17</v>
       </c>
       <c r="D298" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E298" s="5" t="n">
         <f aca="false">IF((F298+G298)&gt;0,ROUND((F298+G298)/30,2),"")</f>
@@ -11466,7 +11468,7 @@
         <v>17</v>
       </c>
       <c r="D299" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E299" s="5" t="n">
         <f aca="false">IF((F299+G299)&gt;0,ROUND((F299+G299)/30,2),"")</f>
@@ -11488,7 +11490,7 @@
         <v>17</v>
       </c>
       <c r="D300" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E300" s="5" t="n">
         <f aca="false">IF((F300+G300)&gt;0,ROUND((F300+G300)/30,2),"")</f>
@@ -11532,7 +11534,7 @@
         <v>17</v>
       </c>
       <c r="D302" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E302" s="5" t="n">
         <f aca="false">IF((F302+G302)&gt;0,ROUND((F302+G302)/30,2),"")</f>
@@ -11554,7 +11556,7 @@
         <v>17</v>
       </c>
       <c r="D303" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E303" s="5" t="n">
         <f aca="false">IF((F303+G303)&gt;0,ROUND((F303+G303)/30,2),"")</f>
@@ -11576,7 +11578,7 @@
         <v>17</v>
       </c>
       <c r="D304" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E304" s="5" t="n">
         <f aca="false">IF((F304+G304)&gt;0,ROUND((F304+G304)/30,2),"")</f>
@@ -11598,7 +11600,7 @@
         <v>17</v>
       </c>
       <c r="D305" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E305" s="5" t="n">
         <f aca="false">IF((F305+G305)&gt;0,ROUND((F305+G305)/30,2),"")</f>
@@ -11620,7 +11622,7 @@
         <v>17</v>
       </c>
       <c r="D306" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E306" s="5" t="str">
         <f aca="false">IF((F306+G306)&gt;0,ROUND((F306+G306)/30,2),"")</f>
@@ -11664,7 +11666,7 @@
         <v>17</v>
       </c>
       <c r="D308" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E308" s="5" t="n">
         <f aca="false">IF((F308+G308)&gt;0,ROUND((F308+G308)/30,2),"")</f>
@@ -11686,7 +11688,7 @@
         <v>17</v>
       </c>
       <c r="D309" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E309" s="5" t="n">
         <f aca="false">IF((F309+G309)&gt;0,ROUND((F309+G309)/30,2),"")</f>
@@ -11708,7 +11710,7 @@
         <v>17</v>
       </c>
       <c r="D310" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E310" s="5" t="n">
         <f aca="false">IF((F310+G310)&gt;0,ROUND((F310+G310)/30,2),"")</f>
@@ -11730,7 +11732,7 @@
         <v>17</v>
       </c>
       <c r="D311" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E311" s="5" t="n">
         <f aca="false">IF((F311+G311)&gt;0,ROUND((F311+G311)/30,2),"")</f>
@@ -11752,7 +11754,7 @@
         <v>17</v>
       </c>
       <c r="D312" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E312" s="5" t="n">
         <f aca="false">IF((F312+G312)&gt;0,ROUND((F312+G312)/30,2),"")</f>
@@ -11774,7 +11776,7 @@
         <v>17</v>
       </c>
       <c r="D313" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E313" s="5" t="n">
         <f aca="false">IF((F313+G313)&gt;0,ROUND((F313+G313)/30,2),"")</f>
@@ -11796,7 +11798,7 @@
         <v>17</v>
       </c>
       <c r="D314" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E314" s="5" t="n">
         <f aca="false">IF((F314+G314)&gt;0,ROUND((F314+G314)/30,2),"")</f>
@@ -11818,7 +11820,7 @@
         <v>17</v>
       </c>
       <c r="D315" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E315" s="5" t="n">
         <f aca="false">IF((F315+G315)&gt;0,ROUND((F315+G315)/30,2),"")</f>
@@ -11840,7 +11842,7 @@
         <v>17</v>
       </c>
       <c r="D316" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E316" s="5" t="n">
         <f aca="false">IF((F316+G316)&gt;0,ROUND((F316+G316)/30,2),"")</f>
@@ -11862,7 +11864,7 @@
         <v>17</v>
       </c>
       <c r="D317" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E317" s="5" t="n">
         <f aca="false">IF((F317+G317)&gt;0,ROUND((F317+G317)/30,2),"")</f>
@@ -11884,7 +11886,7 @@
         <v>17</v>
       </c>
       <c r="D318" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E318" s="5" t="n">
         <f aca="false">IF((F318+G318)&gt;0,ROUND((F318+G318)/30,2),"")</f>
@@ -11906,7 +11908,7 @@
         <v>17</v>
       </c>
       <c r="D319" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E319" s="5" t="n">
         <f aca="false">IF((F319+G319)&gt;0,ROUND((F319+G319)/30,2),"")</f>
@@ -11928,7 +11930,7 @@
         <v>17</v>
       </c>
       <c r="D320" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E320" s="5" t="n">
         <f aca="false">IF((F320+G320)&gt;0,ROUND((F320+G320)/30,2),"")</f>
@@ -11950,7 +11952,7 @@
         <v>17</v>
       </c>
       <c r="D321" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E321" s="5" t="n">
         <f aca="false">IF((F321+G321)&gt;0,ROUND((F321+G321)/30,2),"")</f>
@@ -11972,7 +11974,7 @@
         <v>17</v>
       </c>
       <c r="D322" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E322" s="5" t="n">
         <f aca="false">IF((F322+G322)&gt;0,ROUND((F322+G322)/30,2),"")</f>
@@ -11994,7 +11996,7 @@
         <v>17</v>
       </c>
       <c r="D323" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E323" s="5" t="n">
         <f aca="false">IF((F323+G323)&gt;0,ROUND((F323+G323)/30,2),"")</f>
@@ -12016,7 +12018,7 @@
         <v>17</v>
       </c>
       <c r="D324" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E324" s="5" t="n">
         <f aca="false">IF((F324+G324)&gt;0,ROUND((F324+G324)/30,2),"")</f>
@@ -12038,7 +12040,7 @@
         <v>17</v>
       </c>
       <c r="D325" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E325" s="5" t="str">
         <f aca="false">IF((F325+G325)&gt;0,ROUND((F325+G325)/30,2),"")</f>
@@ -12060,7 +12062,7 @@
         <v>17</v>
       </c>
       <c r="D326" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E326" s="5" t="n">
         <f aca="false">IF((F326+G326)&gt;0,ROUND((F326+G326)/30,2),"")</f>
@@ -12082,7 +12084,7 @@
         <v>17</v>
       </c>
       <c r="D327" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E327" s="5" t="str">
         <f aca="false">IF((F327+G327)&gt;0,ROUND((F327+G327)/30,2),"")</f>
@@ -12104,7 +12106,7 @@
         <v>17</v>
       </c>
       <c r="D328" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E328" s="5" t="n">
         <f aca="false">IF((F328+G328)&gt;0,ROUND((F328+G328)/30,2),"")</f>
@@ -12126,7 +12128,7 @@
         <v>17</v>
       </c>
       <c r="D329" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E329" s="5" t="str">
         <f aca="false">IF((F329+G329)&gt;0,ROUND((F329+G329)/30,2),"")</f>
@@ -12148,7 +12150,7 @@
         <v>17</v>
       </c>
       <c r="D330" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E330" s="5" t="n">
         <f aca="false">IF((F330+G330)&gt;0,ROUND((F330+G330)/30,2),"")</f>
@@ -12170,7 +12172,7 @@
         <v>17</v>
       </c>
       <c r="D331" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E331" s="5" t="n">
         <f aca="false">IF((F331+G331)&gt;0,ROUND((F331+G331)/30,2),"")</f>
@@ -12192,7 +12194,7 @@
         <v>17</v>
       </c>
       <c r="D332" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E332" s="5" t="n">
         <f aca="false">IF((F332+G332)&gt;0,ROUND((F332+G332)/30,2),"")</f>
@@ -12214,7 +12216,7 @@
         <v>17</v>
       </c>
       <c r="D333" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E333" s="5" t="n">
         <f aca="false">IF((F333+G333)&gt;0,ROUND((F333+G333)/30,2),"")</f>
@@ -12236,7 +12238,7 @@
         <v>17</v>
       </c>
       <c r="D334" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E334" s="5" t="n">
         <f aca="false">IF((F334+G334)&gt;0,ROUND((F334+G334)/30,2),"")</f>
@@ -12258,7 +12260,7 @@
         <v>17</v>
       </c>
       <c r="D335" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E335" s="5" t="n">
         <f aca="false">IF((F335+G335)&gt;0,ROUND((F335+G335)/30,2),"")</f>
@@ -12280,7 +12282,7 @@
         <v>17</v>
       </c>
       <c r="D336" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E336" s="5" t="n">
         <f aca="false">IF((F336+G336)&gt;0,ROUND((F336+G336)/30,2),"")</f>
@@ -12302,7 +12304,7 @@
         <v>17</v>
       </c>
       <c r="D337" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E337" s="5" t="n">
         <f aca="false">IF((F337+G337)&gt;0,ROUND((F337+G337)/30,2),"")</f>
@@ -12324,7 +12326,7 @@
         <v>17</v>
       </c>
       <c r="D338" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E338" s="5" t="n">
         <f aca="false">IF((F338+G338)&gt;0,ROUND((F338+G338)/30,2),"")</f>
@@ -12346,7 +12348,7 @@
         <v>17</v>
       </c>
       <c r="D339" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E339" s="5" t="n">
         <f aca="false">IF((F339+G339)&gt;0,ROUND((F339+G339)/30,2),"")</f>
@@ -12390,7 +12392,7 @@
         <v>17</v>
       </c>
       <c r="D341" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E341" s="5" t="n">
         <f aca="false">IF((F341+G341)&gt;0,ROUND((F341+G341)/30,2),"")</f>
@@ -12412,7 +12414,7 @@
         <v>17</v>
       </c>
       <c r="D342" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E342" s="5" t="n">
         <f aca="false">IF((F342+G342)&gt;0,ROUND((F342+G342)/30,2),"")</f>
@@ -12434,7 +12436,7 @@
         <v>17</v>
       </c>
       <c r="D343" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E343" s="5" t="n">
         <f aca="false">IF((F343+G343)&gt;0,ROUND((F343+G343)/30,2),"")</f>
@@ -12456,7 +12458,7 @@
         <v>17</v>
       </c>
       <c r="D344" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E344" s="5" t="n">
         <f aca="false">IF((F344+G344)&gt;0,ROUND((F344+G344)/30,2),"")</f>
@@ -12478,7 +12480,7 @@
         <v>17</v>
       </c>
       <c r="D345" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E345" s="5" t="n">
         <f aca="false">IF((F345+G345)&gt;0,ROUND((F345+G345)/30,2),"")</f>
@@ -12500,7 +12502,7 @@
         <v>17</v>
       </c>
       <c r="D346" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E346" s="5" t="n">
         <f aca="false">IF((F346+G346)&gt;0,ROUND((F346+G346)/30,2),"")</f>
@@ -12524,7 +12526,7 @@
         <v>17</v>
       </c>
       <c r="D347" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E347" s="5" t="n">
         <f aca="false">IF((F347+G347)&gt;0,ROUND((F347+G347)/30,2),"")</f>
@@ -12546,7 +12548,7 @@
         <v>17</v>
       </c>
       <c r="D348" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E348" s="5" t="n">
         <f aca="false">IF((F348+G348)&gt;0,ROUND((F348+G348)/30,2),"")</f>
@@ -12568,7 +12570,7 @@
         <v>17</v>
       </c>
       <c r="D349" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E349" s="5" t="str">
         <f aca="false">IF((F349+G349)&gt;0,ROUND((F349+G349)/30,2),"")</f>
@@ -12590,7 +12592,7 @@
         <v>17</v>
       </c>
       <c r="D350" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E350" s="5" t="n">
         <f aca="false">IF((F350+G350)&gt;0,ROUND((F350+G350)/30,2),"")</f>
@@ -12612,7 +12614,7 @@
         <v>17</v>
       </c>
       <c r="D351" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E351" s="5" t="str">
         <f aca="false">IF((F351+G351)&gt;0,ROUND((F351+G351)/30,2),"")</f>
@@ -12634,7 +12636,7 @@
         <v>17</v>
       </c>
       <c r="D352" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E352" s="5" t="n">
         <f aca="false">IF((F352+G352)&gt;0,ROUND((F352+G352)/30,2),"")</f>
@@ -12656,7 +12658,7 @@
         <v>17</v>
       </c>
       <c r="D353" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E353" s="5" t="n">
         <f aca="false">IF((F353+G353)&gt;0,ROUND((F353+G353)/30,2),"")</f>
@@ -12678,7 +12680,7 @@
         <v>17</v>
       </c>
       <c r="D354" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E354" s="5" t="str">
         <f aca="false">IF((F354+G354)&gt;0,ROUND((F354+G354)/30,2),"")</f>
@@ -12700,7 +12702,7 @@
         <v>17</v>
       </c>
       <c r="D355" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E355" s="5" t="n">
         <f aca="false">IF((F355+G355)&gt;0,ROUND((F355+G355)/30,2),"")</f>
@@ -12722,7 +12724,7 @@
         <v>17</v>
       </c>
       <c r="D356" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E356" s="5" t="str">
         <f aca="false">IF((F356+G356)&gt;0,ROUND((F356+G356)/30,2),"")</f>
@@ -12744,7 +12746,7 @@
         <v>17</v>
       </c>
       <c r="D357" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E357" s="5" t="n">
         <f aca="false">IF((F357+G357)&gt;0,ROUND((F357+G357)/30,2),"")</f>
@@ -12766,7 +12768,7 @@
         <v>17</v>
       </c>
       <c r="D358" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E358" s="5" t="n">
         <f aca="false">IF((F358+G358)&gt;0,ROUND((F358+G358)/30,2),"")</f>
@@ -12790,7 +12792,7 @@
         <v>17</v>
       </c>
       <c r="D359" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E359" s="5" t="n">
         <f aca="false">IF((F359+G359)&gt;0,ROUND((F359+G359)/30,2),"")</f>
@@ -12812,7 +12814,7 @@
         <v>17</v>
       </c>
       <c r="D360" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E360" s="5" t="n">
         <f aca="false">IF((F360+G360)&gt;0,ROUND((F360+G360)/30,2),"")</f>
@@ -12834,7 +12836,7 @@
         <v>17</v>
       </c>
       <c r="D361" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E361" s="5" t="n">
         <f aca="false">IF((F361+G361)&gt;0,ROUND((F361+G361)/30,2),"")</f>
@@ -12856,7 +12858,7 @@
         <v>17</v>
       </c>
       <c r="D362" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E362" s="5" t="n">
         <f aca="false">IF((F362+G362)&gt;0,ROUND((F362+G362)/30,2),"")</f>
@@ -12878,7 +12880,7 @@
         <v>17</v>
       </c>
       <c r="D363" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E363" s="5" t="n">
         <f aca="false">IF((F363+G363)&gt;0,ROUND((F363+G363)/30,2),"")</f>
@@ -12900,7 +12902,7 @@
         <v>17</v>
       </c>
       <c r="D364" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E364" s="5" t="n">
         <f aca="false">IF((F364+G364)&gt;0,ROUND((F364+G364)/30,2),"")</f>
@@ -12922,7 +12924,7 @@
         <v>17</v>
       </c>
       <c r="D365" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E365" s="5" t="n">
         <f aca="false">IF((F365+G365)&gt;0,ROUND((F365+G365)/30,2),"")</f>
@@ -12944,7 +12946,7 @@
         <v>17</v>
       </c>
       <c r="D366" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E366" s="5" t="n">
         <f aca="false">IF((F366+G366)&gt;0,ROUND((F366+G366)/30,2),"")</f>
@@ -12966,7 +12968,7 @@
         <v>17</v>
       </c>
       <c r="D367" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E367" s="5" t="str">
         <f aca="false">IF((F367+G367)&gt;0,ROUND((F367+G367)/30,2),"")</f>
@@ -12988,7 +12990,7 @@
         <v>17</v>
       </c>
       <c r="D368" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E368" s="5" t="n">
         <f aca="false">IF((F368+G368)&gt;0,ROUND((F368+G368)/30,2),"")</f>
@@ -13010,7 +13012,7 @@
         <v>17</v>
       </c>
       <c r="D369" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E369" s="5" t="n">
         <f aca="false">IF((F369+G369)&gt;0,ROUND((F369+G369)/30,2),"")</f>
@@ -13032,7 +13034,7 @@
         <v>17</v>
       </c>
       <c r="D370" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E370" s="5" t="n">
         <f aca="false">IF((F370+G370)&gt;0,ROUND((F370+G370)/30,2),"")</f>
@@ -13054,7 +13056,7 @@
         <v>17</v>
       </c>
       <c r="D371" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E371" s="5" t="n">
         <f aca="false">IF((F371+G371)&gt;0,ROUND((F371+G371)/30,2),"")</f>
@@ -13076,7 +13078,7 @@
         <v>17</v>
       </c>
       <c r="D372" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E372" s="5" t="n">
         <f aca="false">IF((F372+G372)&gt;0,ROUND((F372+G372)/30,2),"")</f>
@@ -13098,7 +13100,7 @@
         <v>17</v>
       </c>
       <c r="D373" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E373" s="5" t="n">
         <f aca="false">IF((F373+G373)&gt;0,ROUND((F373+G373)/30,2),"")</f>
@@ -13120,7 +13122,7 @@
         <v>17</v>
       </c>
       <c r="D374" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E374" s="5" t="n">
         <f aca="false">IF((F374+G374)&gt;0,ROUND((F374+G374)/30,2),"")</f>
@@ -13142,7 +13144,7 @@
         <v>17</v>
       </c>
       <c r="D375" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E375" s="5" t="str">
         <f aca="false">IF((F375+G375)&gt;0,ROUND((F375+G375)/30,2),"")</f>
@@ -13164,7 +13166,7 @@
         <v>17</v>
       </c>
       <c r="D376" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E376" s="5" t="n">
         <f aca="false">IF((F376+G376)&gt;0,ROUND((F376+G376)/30,2),"")</f>
@@ -13186,7 +13188,7 @@
         <v>17</v>
       </c>
       <c r="D377" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E377" s="5" t="n">
         <f aca="false">IF((F377+G377)&gt;0,ROUND((F377+G377)/30,2),"")</f>
@@ -13208,7 +13210,7 @@
         <v>17</v>
       </c>
       <c r="D378" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E378" s="5" t="n">
         <f aca="false">IF((F378+G378)&gt;0,ROUND((F378+G378)/30,2),"")</f>
@@ -13230,7 +13232,7 @@
         <v>17</v>
       </c>
       <c r="D379" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E379" s="5" t="n">
         <f aca="false">IF((F379+G379)&gt;0,ROUND((F379+G379)/30,2),"")</f>
@@ -13252,7 +13254,7 @@
         <v>17</v>
       </c>
       <c r="D380" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E380" s="5" t="str">
         <f aca="false">IF((F380+G380)&gt;0,ROUND((F380+G380)/30,2),"")</f>
@@ -13274,14 +13276,14 @@
         <v>17</v>
       </c>
       <c r="D381" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E381" s="5" t="n">
         <f aca="false">IF((F381+G381)&gt;0,ROUND((F381+G381)/30,2),"")</f>
-        <v>1.67</v>
+        <v>6.67</v>
       </c>
       <c r="F381" s="5" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="G381" s="5"/>
     </row>
@@ -13296,7 +13298,7 @@
         <v>17</v>
       </c>
       <c r="D382" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E382" s="5" t="n">
         <f aca="false">IF((F382+G382)&gt;0,ROUND((F382+G382)/30,2),"")</f>
@@ -13318,7 +13320,7 @@
         <v>17</v>
       </c>
       <c r="D383" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E383" s="5" t="n">
         <f aca="false">IF((F383+G383)&gt;0,ROUND((F383+G383)/30,2),"")</f>
@@ -13340,7 +13342,7 @@
         <v>17</v>
       </c>
       <c r="D384" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E384" s="5" t="n">
         <f aca="false">IF((F384+G384)&gt;0,ROUND((F384+G384)/30,2),"")</f>
@@ -13362,7 +13364,7 @@
         <v>17</v>
       </c>
       <c r="D385" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E385" s="5" t="n">
         <f aca="false">IF((F385+G385)&gt;0,ROUND((F385+G385)/30,2),"")</f>
@@ -13384,7 +13386,7 @@
         <v>17</v>
       </c>
       <c r="D386" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E386" s="5" t="n">
         <f aca="false">IF((F386+G386)&gt;0,ROUND((F386+G386)/30,2),"")</f>
@@ -13406,7 +13408,7 @@
         <v>17</v>
       </c>
       <c r="D387" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E387" s="5" t="n">
         <f aca="false">IF((F387+G387)&gt;0,ROUND((F387+G387)/30,2),"")</f>
@@ -13428,7 +13430,7 @@
         <v>17</v>
       </c>
       <c r="D388" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E388" s="5" t="str">
         <f aca="false">IF((F388+G388)&gt;0,ROUND((F388+G388)/30,2),"")</f>
@@ -13450,7 +13452,7 @@
         <v>17</v>
       </c>
       <c r="D389" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E389" s="5" t="str">
         <f aca="false">IF((F389+G389)&gt;0,ROUND((F389+G389)/30,2),"")</f>
@@ -13472,7 +13474,7 @@
         <v>17</v>
       </c>
       <c r="D390" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E390" s="5" t="n">
         <f aca="false">IF((F390+G390)&gt;0,ROUND((F390+G390)/30,2),"")</f>
@@ -13494,7 +13496,7 @@
         <v>17</v>
       </c>
       <c r="D391" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E391" s="5" t="str">
         <f aca="false">IF((F391+G391)&gt;0,ROUND((F391+G391)/30,2),"")</f>
@@ -13516,7 +13518,7 @@
         <v>17</v>
       </c>
       <c r="D392" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E392" s="5" t="n">
         <f aca="false">IF((F392+G392)&gt;0,ROUND((F392+G392)/30,2),"")</f>
@@ -13538,7 +13540,7 @@
         <v>17</v>
       </c>
       <c r="D393" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E393" s="5" t="n">
         <f aca="false">IF((F393+G393)&gt;0,ROUND((F393+G393)/30,2),"")</f>
@@ -13560,7 +13562,7 @@
         <v>17</v>
       </c>
       <c r="D394" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E394" s="5" t="str">
         <f aca="false">IF((F394+G394)&gt;0,ROUND((F394+G394)/30,2),"")</f>
@@ -13582,7 +13584,7 @@
         <v>17</v>
       </c>
       <c r="D395" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E395" s="5" t="n">
         <f aca="false">IF((F395+G395)&gt;0,ROUND((F395+G395)/30,2),"")</f>
@@ -13604,7 +13606,7 @@
         <v>17</v>
       </c>
       <c r="D396" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E396" s="5" t="str">
         <f aca="false">IF((F396+G396)&gt;0,ROUND((F396+G396)/30,2),"")</f>
@@ -13626,7 +13628,7 @@
         <v>17</v>
       </c>
       <c r="D397" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E397" s="5" t="n">
         <f aca="false">IF((F397+G397)&gt;0,ROUND((F397+G397)/30,2),"")</f>
@@ -13648,7 +13650,7 @@
         <v>17</v>
       </c>
       <c r="D398" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E398" s="5" t="n">
         <f aca="false">IF((F398+G398)&gt;0,ROUND((F398+G398)/30,2),"")</f>
@@ -13670,7 +13672,7 @@
         <v>17</v>
       </c>
       <c r="D399" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E399" s="5" t="n">
         <f aca="false">IF((F399+G399)&gt;0,ROUND((F399+G399)/30,2),"")</f>
@@ -13692,7 +13694,7 @@
         <v>17</v>
       </c>
       <c r="D400" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E400" s="5" t="str">
         <f aca="false">IF((F400+G400)&gt;0,ROUND((F400+G400)/30,2),"")</f>
@@ -13714,7 +13716,7 @@
         <v>17</v>
       </c>
       <c r="D401" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E401" s="5" t="str">
         <f aca="false">IF((F401+G401)&gt;0,ROUND((F401+G401)/30,2),"")</f>
@@ -13736,7 +13738,7 @@
         <v>17</v>
       </c>
       <c r="D402" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E402" s="5" t="n">
         <f aca="false">IF((F402+G402)&gt;0,ROUND((F402+G402)/30,2),"")</f>
@@ -13758,7 +13760,7 @@
         <v>17</v>
       </c>
       <c r="D403" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E403" s="5" t="n">
         <f aca="false">IF((F403+G403)&gt;0,ROUND((F403+G403)/30,2),"")</f>
@@ -13780,7 +13782,7 @@
         <v>17</v>
       </c>
       <c r="D404" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E404" s="5" t="n">
         <f aca="false">IF((F404+G404)&gt;0,ROUND((F404+G404)/30,2),"")</f>
@@ -13802,7 +13804,7 @@
         <v>17</v>
       </c>
       <c r="D405" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E405" s="5" t="n">
         <f aca="false">IF((F405+G405)&gt;0,ROUND((F405+G405)/30,2),"")</f>
@@ -13824,7 +13826,7 @@
         <v>17</v>
       </c>
       <c r="D406" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E406" s="5" t="n">
         <f aca="false">IF((F406+G406)&gt;0,ROUND((F406+G406)/30,2),"")</f>
@@ -13848,7 +13850,7 @@
         <v>17</v>
       </c>
       <c r="D407" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E407" s="5" t="n">
         <f aca="false">IF((F407+G407)&gt;0,ROUND((F407+G407)/30,2),"")</f>
@@ -13870,7 +13872,7 @@
         <v>17</v>
       </c>
       <c r="D408" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E408" s="5" t="n">
         <f aca="false">IF((F408+G408)&gt;0,ROUND((F408+G408)/30,2),"")</f>
@@ -13892,7 +13894,7 @@
         <v>17</v>
       </c>
       <c r="D409" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E409" s="5" t="n">
         <f aca="false">IF((F409+G409)&gt;0,ROUND((F409+G409)/30,2),"")</f>
@@ -13914,7 +13916,7 @@
         <v>17</v>
       </c>
       <c r="D410" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E410" s="5" t="n">
         <f aca="false">IF((F410+G410)&gt;0,ROUND((F410+G410)/30,2),"")</f>
@@ -13936,7 +13938,7 @@
         <v>17</v>
       </c>
       <c r="D411" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E411" s="5" t="n">
         <f aca="false">IF((F411+G411)&gt;0,ROUND((F411+G411)/30,2),"")</f>
@@ -13958,7 +13960,7 @@
         <v>17</v>
       </c>
       <c r="D412" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E412" s="5" t="n">
         <f aca="false">IF((F412+G412)&gt;0,ROUND((F412+G412)/30,2),"")</f>
@@ -13980,7 +13982,7 @@
         <v>17</v>
       </c>
       <c r="D413" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E413" s="5" t="str">
         <f aca="false">IF((F413+G413)&gt;0,ROUND((F413+G413)/30,2),"")</f>
@@ -14002,7 +14004,7 @@
         <v>17</v>
       </c>
       <c r="D414" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E414" s="5" t="n">
         <f aca="false">IF((F414+G414)&gt;0,ROUND((F414+G414)/30,2),"")</f>
@@ -14024,7 +14026,7 @@
         <v>17</v>
       </c>
       <c r="D415" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E415" s="5" t="n">
         <f aca="false">IF((F415+G415)&gt;0,ROUND((F415+G415)/30,2),"")</f>
@@ -14046,7 +14048,7 @@
         <v>17</v>
       </c>
       <c r="D416" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E416" s="5" t="n">
         <f aca="false">IF((F416+G416)&gt;0,ROUND((F416+G416)/30,2),"")</f>
@@ -14068,7 +14070,7 @@
         <v>17</v>
       </c>
       <c r="D417" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E417" s="5" t="n">
         <f aca="false">IF((F417+G417)&gt;0,ROUND((F417+G417)/30,2),"")</f>
@@ -14090,7 +14092,7 @@
         <v>17</v>
       </c>
       <c r="D418" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E418" s="5" t="n">
         <f aca="false">IF((F418+G418)&gt;0,ROUND((F418+G418)/30,2),"")</f>
@@ -14112,7 +14114,7 @@
         <v>17</v>
       </c>
       <c r="D419" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E419" s="5" t="n">
         <f aca="false">IF((F419+G419)&gt;0,ROUND((F419+G419)/30,2),"")</f>
@@ -14134,7 +14136,7 @@
         <v>17</v>
       </c>
       <c r="D420" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E420" s="5" t="n">
         <f aca="false">IF((F420+G420)&gt;0,ROUND((F420+G420)/30,2),"")</f>
@@ -14156,7 +14158,7 @@
         <v>17</v>
       </c>
       <c r="D421" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E421" s="5" t="n">
         <f aca="false">IF((F421+G421)&gt;0,ROUND((F421+G421)/30,2),"")</f>
@@ -14178,7 +14180,7 @@
         <v>17</v>
       </c>
       <c r="D422" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E422" s="5" t="n">
         <f aca="false">IF((F422+G422)&gt;0,ROUND((F422+G422)/30,2),"")</f>
@@ -14200,7 +14202,7 @@
         <v>17</v>
       </c>
       <c r="D423" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E423" s="5" t="n">
         <f aca="false">IF((F423+G423)&gt;0,ROUND((F423+G423)/30,2),"")</f>
@@ -14222,7 +14224,7 @@
         <v>17</v>
       </c>
       <c r="D424" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E424" s="5" t="n">
         <f aca="false">IF((F424+G424)&gt;0,ROUND((F424+G424)/30,2),"")</f>
@@ -14244,7 +14246,7 @@
         <v>17</v>
       </c>
       <c r="D425" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E425" s="5" t="n">
         <f aca="false">IF((F425+G425)&gt;0,ROUND((F425+G425)/30,2),"")</f>
@@ -14266,7 +14268,7 @@
         <v>17</v>
       </c>
       <c r="D426" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E426" s="5" t="n">
         <f aca="false">IF((F426+G426)&gt;0,ROUND((F426+G426)/30,2),"")</f>
@@ -14288,7 +14290,7 @@
         <v>17</v>
       </c>
       <c r="D427" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E427" s="5" t="n">
         <f aca="false">IF((F427+G427)&gt;0,ROUND((F427+G427)/30,2),"")</f>
@@ -14310,7 +14312,7 @@
         <v>17</v>
       </c>
       <c r="D428" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E428" s="5" t="n">
         <f aca="false">IF((F428+G428)&gt;0,ROUND((F428+G428)/30,2),"")</f>
@@ -14332,7 +14334,7 @@
         <v>17</v>
       </c>
       <c r="D429" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E429" s="5" t="str">
         <f aca="false">IF((F429+G429)&gt;0,ROUND((F429+G429)/30,2),"")</f>
@@ -14354,7 +14356,7 @@
         <v>17</v>
       </c>
       <c r="D430" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E430" s="5" t="n">
         <f aca="false">IF((F430+G430)&gt;0,ROUND((F430+G430)/30,2),"")</f>
@@ -14376,7 +14378,7 @@
         <v>17</v>
       </c>
       <c r="D431" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E431" s="5" t="n">
         <f aca="false">IF((F431+G431)&gt;0,ROUND((F431+G431)/30,2),"")</f>
@@ -14398,7 +14400,7 @@
         <v>17</v>
       </c>
       <c r="D432" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E432" s="5" t="n">
         <f aca="false">IF((F432+G432)&gt;0,ROUND((F432+G432)/30,2),"")</f>
@@ -14420,7 +14422,7 @@
         <v>17</v>
       </c>
       <c r="D433" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E433" s="5" t="n">
         <f aca="false">IF((F433+G433)&gt;0,ROUND((F433+G433)/30,2),"")</f>
@@ -14442,7 +14444,7 @@
         <v>17</v>
       </c>
       <c r="D434" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E434" s="5" t="n">
         <f aca="false">IF((F434+G434)&gt;0,ROUND((F434+G434)/30,2),"")</f>
@@ -14464,7 +14466,7 @@
         <v>17</v>
       </c>
       <c r="D435" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E435" s="5" t="n">
         <f aca="false">IF((F435+G435)&gt;0,ROUND((F435+G435)/30,2),"")</f>
@@ -14486,7 +14488,7 @@
         <v>17</v>
       </c>
       <c r="D436" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E436" s="5" t="n">
         <f aca="false">IF((F436+G436)&gt;0,ROUND((F436+G436)/30,2),"")</f>
@@ -14508,7 +14510,7 @@
         <v>17</v>
       </c>
       <c r="D437" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E437" s="5" t="n">
         <f aca="false">IF((F437+G437)&gt;0,ROUND((F437+G437)/30,2),"")</f>
@@ -14530,7 +14532,7 @@
         <v>17</v>
       </c>
       <c r="D438" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E438" s="5" t="n">
         <f aca="false">IF((F438+G438)&gt;0,ROUND((F438+G438)/30,2),"")</f>
@@ -14552,7 +14554,7 @@
         <v>17</v>
       </c>
       <c r="D439" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E439" s="5" t="n">
         <f aca="false">IF((F439+G439)&gt;0,ROUND((F439+G439)/30,2),"")</f>
@@ -14574,7 +14576,7 @@
         <v>17</v>
       </c>
       <c r="D440" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E440" s="5" t="str">
         <f aca="false">IF((F440+G440)&gt;0,ROUND((F440+G440)/30,2),"")</f>
@@ -14596,7 +14598,7 @@
         <v>17</v>
       </c>
       <c r="D441" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E441" s="5" t="n">
         <f aca="false">IF((F441+G441)&gt;0,ROUND((F441+G441)/30,2),"")</f>
@@ -14618,7 +14620,7 @@
         <v>17</v>
       </c>
       <c r="D442" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E442" s="5" t="n">
         <f aca="false">IF((F442+G442)&gt;0,ROUND((F442+G442)/30,2),"")</f>
@@ -14640,7 +14642,7 @@
         <v>17</v>
       </c>
       <c r="D443" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E443" s="5" t="n">
         <f aca="false">IF((F443+G443)&gt;0,ROUND((F443+G443)/30,2),"")</f>
@@ -14662,7 +14664,7 @@
         <v>17</v>
       </c>
       <c r="D444" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E444" s="5" t="n">
         <f aca="false">IF((F444+G444)&gt;0,ROUND((F444+G444)/30,2),"")</f>
@@ -14684,7 +14686,7 @@
         <v>17</v>
       </c>
       <c r="D445" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E445" s="5" t="n">
         <f aca="false">IF((F445+G445)&gt;0,ROUND((F445+G445)/30,2),"")</f>
@@ -14706,7 +14708,7 @@
         <v>17</v>
       </c>
       <c r="D446" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E446" s="5" t="n">
         <f aca="false">IF((F446+G446)&gt;0,ROUND((F446+G446)/30,2),"")</f>
@@ -14728,7 +14730,7 @@
         <v>17</v>
       </c>
       <c r="D447" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E447" s="5" t="n">
         <f aca="false">IF((F447+G447)&gt;0,ROUND((F447+G447)/30,2),"")</f>
@@ -14750,7 +14752,7 @@
         <v>17</v>
       </c>
       <c r="D448" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E448" s="5" t="n">
         <f aca="false">IF((F448+G448)&gt;0,ROUND((F448+G448)/30,2),"")</f>
@@ -14772,7 +14774,7 @@
         <v>17</v>
       </c>
       <c r="D449" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E449" s="5" t="n">
         <f aca="false">IF((F449+G449)&gt;0,ROUND((F449+G449)/30,2),"")</f>
@@ -14794,7 +14796,7 @@
         <v>17</v>
       </c>
       <c r="D450" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E450" s="5" t="n">
         <f aca="false">IF((F450+G450)&gt;0,ROUND((F450+G450)/30,2),"")</f>
@@ -14816,7 +14818,7 @@
         <v>17</v>
       </c>
       <c r="D451" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E451" s="5" t="n">
         <f aca="false">IF((F451+G451)&gt;0,ROUND((F451+G451)/30,2),"")</f>
@@ -14838,7 +14840,7 @@
         <v>17</v>
       </c>
       <c r="D452" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E452" s="5" t="n">
         <f aca="false">IF((F452+G452)&gt;0,ROUND((F452+G452)/30,2),"")</f>
@@ -14860,7 +14862,7 @@
         <v>17</v>
       </c>
       <c r="D453" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E453" s="5" t="n">
         <f aca="false">IF((F453+G453)&gt;0,ROUND((F453+G453)/30,2),"")</f>
@@ -14882,7 +14884,7 @@
         <v>17</v>
       </c>
       <c r="D454" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E454" s="5" t="n">
         <f aca="false">IF((F454+G454)&gt;0,ROUND((F454+G454)/30,2),"")</f>
@@ -14904,7 +14906,7 @@
         <v>17</v>
       </c>
       <c r="D455" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E455" s="5" t="n">
         <f aca="false">IF((F455+G455)&gt;0,ROUND((F455+G455)/30,2),"")</f>
@@ -14926,7 +14928,7 @@
         <v>17</v>
       </c>
       <c r="D456" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E456" s="5" t="n">
         <f aca="false">IF((F456+G456)&gt;0,ROUND((F456+G456)/30,2),"")</f>
@@ -14948,7 +14950,7 @@
         <v>17</v>
       </c>
       <c r="D457" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E457" s="5" t="n">
         <f aca="false">IF((F457+G457)&gt;0,ROUND((F457+G457)/30,2),"")</f>
@@ -14970,7 +14972,7 @@
         <v>17</v>
       </c>
       <c r="D458" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E458" s="5" t="n">
         <f aca="false">IF((F458+G458)&gt;0,ROUND((F458+G458)/30,2),"")</f>
@@ -14992,7 +14994,7 @@
         <v>17</v>
       </c>
       <c r="D459" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E459" s="5" t="str">
         <f aca="false">IF((F459+G459)&gt;0,ROUND((F459+G459)/30,2),"")</f>
@@ -15014,7 +15016,7 @@
         <v>17</v>
       </c>
       <c r="D460" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E460" s="5" t="n">
         <f aca="false">IF((F460+G460)&gt;0,ROUND((F460+G460)/30,2),"")</f>
@@ -15036,7 +15038,7 @@
         <v>17</v>
       </c>
       <c r="D461" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E461" s="5" t="n">
         <f aca="false">IF((F461+G461)&gt;0,ROUND((F461+G461)/30,2),"")</f>
@@ -15058,7 +15060,7 @@
         <v>17</v>
       </c>
       <c r="D462" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E462" s="5" t="n">
         <f aca="false">IF((F462+G462)&gt;0,ROUND((F462+G462)/30,2),"")</f>
@@ -15080,7 +15082,7 @@
         <v>17</v>
       </c>
       <c r="D463" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E463" s="5" t="n">
         <f aca="false">IF((F463+G463)&gt;0,ROUND((F463+G463)/30,2),"")</f>
@@ -15102,7 +15104,7 @@
         <v>17</v>
       </c>
       <c r="D464" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E464" s="5" t="n">
         <f aca="false">IF((F464+G464)&gt;0,ROUND((F464+G464)/30,2),"")</f>
@@ -15124,7 +15126,7 @@
         <v>17</v>
       </c>
       <c r="D465" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E465" s="5" t="n">
         <f aca="false">IF((F465+G465)&gt;0,ROUND((F465+G465)/30,2),"")</f>
@@ -15146,14 +15148,14 @@
         <v>17</v>
       </c>
       <c r="D466" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E466" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="E466" s="5" t="str">
         <f aca="false">IF((F466+G466)&gt;0,ROUND((F466+G466)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F466" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G466" s="5"/>
     </row>
@@ -15168,7 +15170,7 @@
         <v>17</v>
       </c>
       <c r="D467" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E467" s="5" t="n">
         <f aca="false">IF((F467+G467)&gt;0,ROUND((F467+G467)/30,2),"")</f>
@@ -15190,7 +15192,7 @@
         <v>17</v>
       </c>
       <c r="D468" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E468" s="5" t="n">
         <f aca="false">IF((F468+G468)&gt;0,ROUND((F468+G468)/30,2),"")</f>
@@ -15212,7 +15214,7 @@
         <v>17</v>
       </c>
       <c r="D469" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E469" s="5" t="n">
         <f aca="false">IF((F469+G469)&gt;0,ROUND((F469+G469)/30,2),"")</f>
@@ -15234,7 +15236,7 @@
         <v>17</v>
       </c>
       <c r="D470" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E470" s="5" t="n">
         <f aca="false">IF((F470+G470)&gt;0,ROUND((F470+G470)/30,2),"")</f>
@@ -15256,7 +15258,7 @@
         <v>17</v>
       </c>
       <c r="D471" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E471" s="5" t="n">
         <f aca="false">IF((F471+G471)&gt;0,ROUND((F471+G471)/30,2),"")</f>
@@ -15278,7 +15280,7 @@
         <v>17</v>
       </c>
       <c r="D472" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E472" s="5" t="n">
         <f aca="false">IF((F472+G472)&gt;0,ROUND((F472+G472)/30,2),"")</f>
@@ -15300,7 +15302,7 @@
         <v>17</v>
       </c>
       <c r="D473" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E473" s="5" t="str">
         <f aca="false">IF((F473+G473)&gt;0,ROUND((F473+G473)/30,2),"")</f>
@@ -15322,7 +15324,7 @@
         <v>17</v>
       </c>
       <c r="D474" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E474" s="5" t="str">
         <f aca="false">IF((F474+G474)&gt;0,ROUND((F474+G474)/30,2),"")</f>
@@ -15344,7 +15346,7 @@
         <v>17</v>
       </c>
       <c r="D475" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E475" s="5" t="n">
         <f aca="false">IF((F475+G475)&gt;0,ROUND((F475+G475)/30,2),"")</f>
@@ -15366,7 +15368,7 @@
         <v>17</v>
       </c>
       <c r="D476" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E476" s="5" t="n">
         <f aca="false">IF((F476+G476)&gt;0,ROUND((F476+G476)/30,2),"")</f>
@@ -15388,7 +15390,7 @@
         <v>17</v>
       </c>
       <c r="D477" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E477" s="5" t="n">
         <f aca="false">IF((F477+G477)&gt;0,ROUND((F477+G477)/30,2),"")</f>
@@ -15410,7 +15412,7 @@
         <v>17</v>
       </c>
       <c r="D478" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E478" s="5" t="n">
         <f aca="false">IF((F478+G478)&gt;0,ROUND((F478+G478)/30,2),"")</f>
@@ -15432,7 +15434,7 @@
         <v>17</v>
       </c>
       <c r="D479" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E479" s="5" t="n">
         <f aca="false">IF((F479+G479)&gt;0,ROUND((F479+G479)/30,2),"")</f>
@@ -15454,7 +15456,7 @@
         <v>17</v>
       </c>
       <c r="D480" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E480" s="5" t="n">
         <f aca="false">IF((F480+G480)&gt;0,ROUND((F480+G480)/30,2),"")</f>
@@ -15476,7 +15478,7 @@
         <v>17</v>
       </c>
       <c r="D481" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E481" s="5" t="n">
         <f aca="false">IF((F481+G481)&gt;0,ROUND((F481+G481)/30,2),"")</f>
@@ -15498,7 +15500,7 @@
         <v>17</v>
       </c>
       <c r="D482" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E482" s="5" t="n">
         <f aca="false">IF((F482+G482)&gt;0,ROUND((F482+G482)/30,2),"")</f>
@@ -15520,7 +15522,7 @@
         <v>17</v>
       </c>
       <c r="D483" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E483" s="5" t="n">
         <f aca="false">IF((F483+G483)&gt;0,ROUND((F483+G483)/30,2),"")</f>
@@ -15542,7 +15544,7 @@
         <v>17</v>
       </c>
       <c r="D484" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E484" s="5" t="n">
         <f aca="false">IF((F484+G484)&gt;0,ROUND((F484+G484)/30,2),"")</f>
@@ -15564,7 +15566,7 @@
         <v>17</v>
       </c>
       <c r="D485" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E485" s="5" t="n">
         <f aca="false">IF((F485+G485)&gt;0,ROUND((F485+G485)/30,2),"")</f>
@@ -15586,7 +15588,7 @@
         <v>17</v>
       </c>
       <c r="D486" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E486" s="5" t="n">
         <f aca="false">IF((F486+G486)&gt;0,ROUND((F486+G486)/30,2),"")</f>
@@ -15608,7 +15610,7 @@
         <v>17</v>
       </c>
       <c r="D487" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E487" s="5" t="n">
         <f aca="false">IF((F487+G487)&gt;0,ROUND((F487+G487)/30,2),"")</f>
@@ -15630,7 +15632,7 @@
         <v>17</v>
       </c>
       <c r="D488" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E488" s="5" t="n">
         <f aca="false">IF((F488+G488)&gt;0,ROUND((F488+G488)/30,2),"")</f>
@@ -15652,7 +15654,7 @@
         <v>17</v>
       </c>
       <c r="D489" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E489" s="5" t="n">
         <f aca="false">IF((F489+G489)&gt;0,ROUND((F489+G489)/30,2),"")</f>
@@ -15674,7 +15676,7 @@
         <v>17</v>
       </c>
       <c r="D490" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E490" s="5" t="n">
         <f aca="false">IF((F490+G490)&gt;0,ROUND((F490+G490)/30,2),"")</f>
@@ -15696,7 +15698,7 @@
         <v>17</v>
       </c>
       <c r="D491" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E491" s="5" t="str">
         <f aca="false">IF((F491+G491)&gt;0,ROUND((F491+G491)/30,2),"")</f>
@@ -15718,7 +15720,7 @@
         <v>17</v>
       </c>
       <c r="D492" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E492" s="5" t="str">
         <f aca="false">IF((F492+G492)&gt;0,ROUND((F492+G492)/30,2),"")</f>
@@ -15740,7 +15742,7 @@
         <v>17</v>
       </c>
       <c r="D493" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E493" s="5" t="n">
         <f aca="false">IF((F493+G493)&gt;0,ROUND((F493+G493)/30,2),"")</f>
@@ -15762,7 +15764,7 @@
         <v>17</v>
       </c>
       <c r="D494" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E494" s="5" t="n">
         <f aca="false">IF((F494+G494)&gt;0,ROUND((F494+G494)/30,2),"")</f>
@@ -15784,7 +15786,7 @@
         <v>17</v>
       </c>
       <c r="D495" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E495" s="5" t="n">
         <f aca="false">IF((F495+G495)&gt;0,ROUND((F495+G495)/30,2),"")</f>
@@ -15806,7 +15808,7 @@
         <v>17</v>
       </c>
       <c r="D496" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E496" s="5" t="str">
         <f aca="false">IF((F496+G496)&gt;0,ROUND((F496+G496)/30,2),"")</f>
@@ -15828,7 +15830,7 @@
         <v>17</v>
       </c>
       <c r="D497" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E497" s="5" t="n">
         <f aca="false">IF((F497+G497)&gt;0,ROUND((F497+G497)/30,2),"")</f>
@@ -15850,7 +15852,7 @@
         <v>17</v>
       </c>
       <c r="D498" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E498" s="5" t="n">
         <f aca="false">IF((F498+G498)&gt;0,ROUND((F498+G498)/30,2),"")</f>
@@ -15872,7 +15874,7 @@
         <v>17</v>
       </c>
       <c r="D499" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E499" s="5" t="n">
         <f aca="false">IF((F499+G499)&gt;0,ROUND((F499+G499)/30,2),"")</f>
@@ -15894,7 +15896,7 @@
         <v>17</v>
       </c>
       <c r="D500" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E500" s="5" t="n">
         <f aca="false">IF((F500+G500)&gt;0,ROUND((F500+G500)/30,2),"")</f>
@@ -15916,7 +15918,7 @@
         <v>17</v>
       </c>
       <c r="D501" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E501" s="5" t="n">
         <f aca="false">IF((F501+G501)&gt;0,ROUND((F501+G501)/30,2),"")</f>
@@ -15938,7 +15940,7 @@
         <v>17</v>
       </c>
       <c r="D502" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E502" s="5" t="n">
         <f aca="false">IF((F502+G502)&gt;0,ROUND((F502+G502)/30,2),"")</f>
@@ -15960,7 +15962,7 @@
         <v>17</v>
       </c>
       <c r="D503" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E503" s="5" t="n">
         <f aca="false">IF((F503+G503)&gt;0,ROUND((F503+G503)/30,2),"")</f>
@@ -15982,7 +15984,7 @@
         <v>17</v>
       </c>
       <c r="D504" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E504" s="5" t="n">
         <f aca="false">IF((F504+G504)&gt;0,ROUND((F504+G504)/30,2),"")</f>
@@ -16004,7 +16006,7 @@
         <v>17</v>
       </c>
       <c r="D505" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E505" s="5" t="n">
         <f aca="false">IF((F505+G505)&gt;0,ROUND((F505+G505)/30,2),"")</f>
@@ -16026,7 +16028,7 @@
         <v>17</v>
       </c>
       <c r="D506" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E506" s="5" t="n">
         <f aca="false">IF((F506+G506)&gt;0,ROUND((F506+G506)/30,2),"")</f>
@@ -16048,7 +16050,7 @@
         <v>17</v>
       </c>
       <c r="D507" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E507" s="5" t="n">
         <f aca="false">IF((F507+G507)&gt;0,ROUND((F507+G507)/30,2),"")</f>
@@ -16070,7 +16072,7 @@
         <v>17</v>
       </c>
       <c r="D508" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E508" s="5" t="n">
         <f aca="false">IF((F508+G508)&gt;0,ROUND((F508+G508)/30,2),"")</f>
@@ -16092,7 +16094,7 @@
         <v>17</v>
       </c>
       <c r="D509" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E509" s="5" t="n">
         <f aca="false">IF((F509+G509)&gt;0,ROUND((F509+G509)/30,2),"")</f>
@@ -16114,7 +16116,7 @@
         <v>17</v>
       </c>
       <c r="D510" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E510" s="5" t="n">
         <f aca="false">IF((F510+G510)&gt;0,ROUND((F510+G510)/30,2),"")</f>
@@ -16136,7 +16138,7 @@
         <v>28</v>
       </c>
       <c r="D511" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E511" s="5" t="n">
         <f aca="false">IF((F511+G511)&gt;0,ROUND((F511+G511)/30,2),"")</f>
@@ -16158,7 +16160,7 @@
         <v>28</v>
       </c>
       <c r="D512" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E512" s="5" t="n">
         <f aca="false">IF((F512+G512)&gt;0,ROUND((F512+G512)/30,2),"")</f>
@@ -16180,7 +16182,7 @@
         <v>28</v>
       </c>
       <c r="D513" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E513" s="5" t="n">
         <f aca="false">IF((F513+G513)&gt;0,ROUND((F513+G513)/30,2),"")</f>
@@ -16202,7 +16204,7 @@
         <v>28</v>
       </c>
       <c r="D514" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E514" s="5" t="n">
         <f aca="false">IF((F514+G514)&gt;0,ROUND((F514+G514)/30,2),"")</f>
@@ -16224,7 +16226,7 @@
         <v>28</v>
       </c>
       <c r="D515" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E515" s="5" t="n">
         <f aca="false">IF((F515+G515)&gt;0,ROUND((F515+G515)/30,2),"")</f>
@@ -16246,7 +16248,7 @@
         <v>28</v>
       </c>
       <c r="D516" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E516" s="5" t="n">
         <f aca="false">IF((F516+G516)&gt;0,ROUND((F516+G516)/30,2),"")</f>
@@ -16268,7 +16270,7 @@
         <v>28</v>
       </c>
       <c r="D517" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E517" s="5" t="n">
         <f aca="false">IF((F517+G517)&gt;0,ROUND((F517+G517)/30,2),"")</f>
@@ -16290,7 +16292,7 @@
         <v>28</v>
       </c>
       <c r="D518" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E518" s="5" t="n">
         <f aca="false">IF((F518+G518)&gt;0,ROUND((F518+G518)/30,2),"")</f>
@@ -16312,7 +16314,7 @@
         <v>28</v>
       </c>
       <c r="D519" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E519" s="5" t="n">
         <f aca="false">IF((F519+G519)&gt;0,ROUND((F519+G519)/30,2),"")</f>
@@ -16334,7 +16336,7 @@
         <v>28</v>
       </c>
       <c r="D520" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E520" s="5" t="n">
         <f aca="false">IF((F520+G520)&gt;0,ROUND((F520+G520)/30,2),"")</f>
@@ -16356,7 +16358,7 @@
         <v>30</v>
       </c>
       <c r="D521" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E521" s="5" t="n">
         <f aca="false">IF((F521+G521)&gt;0,ROUND((F521+G521)/30,2),"")</f>
@@ -16378,7 +16380,7 @@
         <v>30</v>
       </c>
       <c r="D522" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E522" s="5" t="n">
         <f aca="false">IF((F522+G522)&gt;0,ROUND((F522+G522)/30,2),"")</f>
@@ -16400,7 +16402,7 @@
         <v>30</v>
       </c>
       <c r="D523" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E523" s="5" t="n">
         <f aca="false">IF((F523+G523)&gt;0,ROUND((F523+G523)/30,2),"")</f>
@@ -16424,7 +16426,7 @@
         <v>30</v>
       </c>
       <c r="D524" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E524" s="5" t="n">
         <f aca="false">IF((F524+G524)&gt;0,ROUND((F524+G524)/30,2),"")</f>
@@ -16446,7 +16448,7 @@
         <v>30</v>
       </c>
       <c r="D525" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E525" s="5" t="n">
         <f aca="false">IF((F525+G525)&gt;0,ROUND((F525+G525)/30,2),"")</f>
@@ -16468,7 +16470,7 @@
         <v>30</v>
       </c>
       <c r="D526" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E526" s="5" t="n">
         <f aca="false">IF((F526+G526)&gt;0,ROUND((F526+G526)/30,2),"")</f>
@@ -16490,7 +16492,7 @@
         <v>30</v>
       </c>
       <c r="D527" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E527" s="5" t="n">
         <f aca="false">IF((F527+G527)&gt;0,ROUND((F527+G527)/30,2),"")</f>
@@ -16512,7 +16514,7 @@
         <v>30</v>
       </c>
       <c r="D528" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E528" s="5" t="n">
         <f aca="false">IF((F528+G528)&gt;0,ROUND((F528+G528)/30,2),"")</f>
@@ -16534,7 +16536,7 @@
         <v>30</v>
       </c>
       <c r="D529" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E529" s="5" t="n">
         <f aca="false">IF((F529+G529)&gt;0,ROUND((F529+G529)/30,2),"")</f>
@@ -16556,7 +16558,7 @@
         <v>30</v>
       </c>
       <c r="D530" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E530" s="5" t="n">
         <f aca="false">IF((F530+G530)&gt;0,ROUND((F530+G530)/30,2),"")</f>
@@ -16578,7 +16580,7 @@
         <v>30</v>
       </c>
       <c r="D531" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E531" s="5" t="n">
         <f aca="false">IF((F531+G531)&gt;0,ROUND((F531+G531)/30,2),"")</f>
@@ -16600,7 +16602,7 @@
         <v>30</v>
       </c>
       <c r="D532" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E532" s="5" t="n">
         <f aca="false">IF((F532+G532)&gt;0,ROUND((F532+G532)/30,2),"")</f>
@@ -16622,7 +16624,7 @@
         <v>30</v>
       </c>
       <c r="D533" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E533" s="5" t="n">
         <f aca="false">IF((F533+G533)&gt;0,ROUND((F533+G533)/30,2),"")</f>
@@ -16644,7 +16646,7 @@
         <v>30</v>
       </c>
       <c r="D534" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E534" s="5" t="str">
         <f aca="false">IF((F534+G534)&gt;0,ROUND((F534+G534)/30,2),"")</f>
@@ -16666,7 +16668,7 @@
         <v>30</v>
       </c>
       <c r="D535" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E535" s="5" t="n">
         <f aca="false">IF((F535+G535)&gt;0,ROUND((F535+G535)/30,2),"")</f>
@@ -16688,7 +16690,7 @@
         <v>30</v>
       </c>
       <c r="D536" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E536" s="5" t="n">
         <f aca="false">IF((F536+G536)&gt;0,ROUND((F536+G536)/30,2),"")</f>
@@ -16710,7 +16712,7 @@
         <v>30</v>
       </c>
       <c r="D537" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E537" s="5" t="n">
         <f aca="false">IF((F537+G537)&gt;0,ROUND((F537+G537)/30,2),"")</f>
@@ -16732,7 +16734,7 @@
         <v>30</v>
       </c>
       <c r="D538" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E538" s="5" t="str">
         <f aca="false">IF((F538+G538)&gt;0,ROUND((F538+G538)/30,2),"")</f>
@@ -16754,7 +16756,7 @@
         <v>30</v>
       </c>
       <c r="D539" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E539" s="5" t="n">
         <f aca="false">IF((F539+G539)&gt;0,ROUND((F539+G539)/30,2),"")</f>
@@ -16776,7 +16778,7 @@
         <v>30</v>
       </c>
       <c r="D540" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E540" s="5" t="n">
         <f aca="false">IF((F540+G540)&gt;0,ROUND((F540+G540)/30,2),"")</f>
@@ -16798,7 +16800,7 @@
         <v>30</v>
       </c>
       <c r="D541" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E541" s="5" t="n">
         <f aca="false">IF((F541+G541)&gt;0,ROUND((F541+G541)/30,2),"")</f>
@@ -16820,7 +16822,7 @@
         <v>30</v>
       </c>
       <c r="D542" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E542" s="5" t="n">
         <f aca="false">IF((F542+G542)&gt;0,ROUND((F542+G542)/30,2),"")</f>
@@ -16842,7 +16844,7 @@
         <v>30</v>
       </c>
       <c r="D543" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E543" s="5" t="str">
         <f aca="false">IF((F543+G543)&gt;0,ROUND((F543+G543)/30,2),"")</f>
@@ -16864,7 +16866,7 @@
         <v>30</v>
       </c>
       <c r="D544" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E544" s="5" t="n">
         <f aca="false">IF((F544+G544)&gt;0,ROUND((F544+G544)/30,2),"")</f>
@@ -16886,7 +16888,7 @@
         <v>30</v>
       </c>
       <c r="D545" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E545" s="5" t="n">
         <f aca="false">IF((F545+G545)&gt;0,ROUND((F545+G545)/30,2),"")</f>
@@ -16908,7 +16910,7 @@
         <v>30</v>
       </c>
       <c r="D546" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E546" s="5" t="n">
         <f aca="false">IF((F546+G546)&gt;0,ROUND((F546+G546)/30,2),"")</f>
@@ -16930,7 +16932,7 @@
         <v>30</v>
       </c>
       <c r="D547" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E547" s="5" t="n">
         <f aca="false">IF((F547+G547)&gt;0,ROUND((F547+G547)/30,2),"")</f>
@@ -16952,7 +16954,7 @@
         <v>30</v>
       </c>
       <c r="D548" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E548" s="5" t="n">
         <f aca="false">IF((F548+G548)&gt;0,ROUND((F548+G548)/30,2),"")</f>
@@ -16974,7 +16976,7 @@
         <v>30</v>
       </c>
       <c r="D549" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E549" s="5" t="n">
         <f aca="false">IF((F549+G549)&gt;0,ROUND((F549+G549)/30,2),"")</f>
@@ -16996,7 +16998,7 @@
         <v>30</v>
       </c>
       <c r="D550" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E550" s="5" t="n">
         <f aca="false">IF((F550+G550)&gt;0,ROUND((F550+G550)/30,2),"")</f>
@@ -17018,7 +17020,7 @@
         <v>30</v>
       </c>
       <c r="D551" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E551" s="5" t="n">
         <f aca="false">IF((F551+G551)&gt;0,ROUND((F551+G551)/30,2),"")</f>
@@ -17040,7 +17042,7 @@
         <v>30</v>
       </c>
       <c r="D552" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E552" s="5" t="n">
         <f aca="false">IF((F552+G552)&gt;0,ROUND((F552+G552)/30,2),"")</f>
@@ -17062,7 +17064,7 @@
         <v>30</v>
       </c>
       <c r="D553" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E553" s="5" t="n">
         <f aca="false">IF((F553+G553)&gt;0,ROUND((F553+G553)/30,2),"")</f>
@@ -17084,7 +17086,7 @@
         <v>30</v>
       </c>
       <c r="D554" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E554" s="5" t="n">
         <f aca="false">IF((F554+G554)&gt;0,ROUND((F554+G554)/30,2),"")</f>
@@ -17106,7 +17108,7 @@
         <v>30</v>
       </c>
       <c r="D555" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E555" s="5" t="n">
         <f aca="false">IF((F555+G555)&gt;0,ROUND((F555+G555)/30,2),"")</f>
@@ -17128,7 +17130,7 @@
         <v>30</v>
       </c>
       <c r="D556" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E556" s="5" t="str">
         <f aca="false">IF((F556+G556)&gt;0,ROUND((F556+G556)/30,2),"")</f>
@@ -17150,7 +17152,7 @@
         <v>30</v>
       </c>
       <c r="D557" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E557" s="5" t="n">
         <f aca="false">IF((F557+G557)&gt;0,ROUND((F557+G557)/30,2),"")</f>
@@ -17172,7 +17174,7 @@
         <v>30</v>
       </c>
       <c r="D558" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E558" s="5" t="n">
         <f aca="false">IF((F558+G558)&gt;0,ROUND((F558+G558)/30,2),"")</f>
@@ -17194,7 +17196,7 @@
         <v>30</v>
       </c>
       <c r="D559" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E559" s="5" t="n">
         <f aca="false">IF((F559+G559)&gt;0,ROUND((F559+G559)/30,2),"")</f>
@@ -17216,7 +17218,7 @@
         <v>30</v>
       </c>
       <c r="D560" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E560" s="5" t="n">
         <f aca="false">IF((F560+G560)&gt;0,ROUND((F560+G560)/30,2),"")</f>
@@ -17238,7 +17240,7 @@
         <v>30</v>
       </c>
       <c r="D561" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E561" s="5" t="str">
         <f aca="false">IF((F561+G561)&gt;0,ROUND((F561+G561)/30,2),"")</f>
@@ -17260,7 +17262,7 @@
         <v>30</v>
       </c>
       <c r="D562" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E562" s="5" t="str">
         <f aca="false">IF((F562+G562)&gt;0,ROUND((F562+G562)/30,2),"")</f>
@@ -17282,7 +17284,7 @@
         <v>30</v>
       </c>
       <c r="D563" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E563" s="5" t="n">
         <f aca="false">IF((F563+G563)&gt;0,ROUND((F563+G563)/30,2),"")</f>
@@ -17304,7 +17306,7 @@
         <v>30</v>
       </c>
       <c r="D564" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E564" s="5" t="n">
         <f aca="false">IF((F564+G564)&gt;0,ROUND((F564+G564)/30,2),"")</f>
@@ -17326,7 +17328,7 @@
         <v>30</v>
       </c>
       <c r="D565" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E565" s="5" t="str">
         <f aca="false">IF((F565+G565)&gt;0,ROUND((F565+G565)/30,2),"")</f>
@@ -17348,7 +17350,7 @@
         <v>30</v>
       </c>
       <c r="D566" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E566" s="5" t="n">
         <f aca="false">IF((F566+G566)&gt;0,ROUND((F566+G566)/30,2),"")</f>
@@ -17370,7 +17372,7 @@
         <v>30</v>
       </c>
       <c r="D567" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E567" s="5" t="n">
         <f aca="false">IF((F567+G567)&gt;0,ROUND((F567+G567)/30,2),"")</f>
@@ -17394,7 +17396,7 @@
         <v>30</v>
       </c>
       <c r="D568" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E568" s="5" t="str">
         <f aca="false">IF((F568+G568)&gt;0,ROUND((F568+G568)/30,2),"")</f>
@@ -17416,7 +17418,7 @@
         <v>30</v>
       </c>
       <c r="D569" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E569" s="5" t="n">
         <f aca="false">IF((F569+G569)&gt;0,ROUND((F569+G569)/30,2),"")</f>
@@ -17438,7 +17440,7 @@
         <v>30</v>
       </c>
       <c r="D570" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E570" s="5" t="str">
         <f aca="false">IF((F570+G570)&gt;0,ROUND((F570+G570)/30,2),"")</f>
@@ -17460,7 +17462,7 @@
         <v>30</v>
       </c>
       <c r="D571" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E571" s="5" t="str">
         <f aca="false">IF((F571+G571)&gt;0,ROUND((F571+G571)/30,2),"")</f>
@@ -17482,7 +17484,7 @@
         <v>30</v>
       </c>
       <c r="D572" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E572" s="5" t="str">
         <f aca="false">IF((F572+G572)&gt;0,ROUND((F572+G572)/30,2),"")</f>
@@ -17504,7 +17506,7 @@
         <v>30</v>
       </c>
       <c r="D573" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E573" s="5" t="str">
         <f aca="false">IF((F573+G573)&gt;0,ROUND((F573+G573)/30,2),"")</f>
@@ -17526,7 +17528,7 @@
         <v>30</v>
       </c>
       <c r="D574" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E574" s="5" t="n">
         <f aca="false">IF((F574+G574)&gt;0,ROUND((F574+G574)/30,2),"")</f>
@@ -17548,7 +17550,7 @@
         <v>30</v>
       </c>
       <c r="D575" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E575" s="5" t="n">
         <f aca="false">IF((F575+G575)&gt;0,ROUND((F575+G575)/30,2),"")</f>
@@ -17570,7 +17572,7 @@
         <v>30</v>
       </c>
       <c r="D576" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E576" s="5" t="n">
         <f aca="false">IF((F576+G576)&gt;0,ROUND((F576+G576)/30,2),"")</f>
@@ -17592,7 +17594,7 @@
         <v>30</v>
       </c>
       <c r="D577" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E577" s="5" t="n">
         <f aca="false">IF((F577+G577)&gt;0,ROUND((F577+G577)/30,2),"")</f>
@@ -17614,7 +17616,7 @@
         <v>30</v>
       </c>
       <c r="D578" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E578" s="5" t="n">
         <f aca="false">IF((F578+G578)&gt;0,ROUND((F578+G578)/30,2),"")</f>
@@ -17636,7 +17638,7 @@
         <v>30</v>
       </c>
       <c r="D579" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E579" s="5" t="n">
         <f aca="false">IF((F579+G579)&gt;0,ROUND((F579+G579)/30,2),"")</f>
@@ -17658,7 +17660,7 @@
         <v>30</v>
       </c>
       <c r="D580" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E580" s="5" t="n">
         <f aca="false">IF((F580+G580)&gt;0,ROUND((F580+G580)/30,2),"")</f>
@@ -17680,7 +17682,7 @@
         <v>30</v>
       </c>
       <c r="D581" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E581" s="5" t="n">
         <f aca="false">IF((F581+G581)&gt;0,ROUND((F581+G581)/30,2),"")</f>
@@ -17702,7 +17704,7 @@
         <v>30</v>
       </c>
       <c r="D582" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E582" s="5" t="n">
         <f aca="false">IF((F582+G582)&gt;0,ROUND((F582+G582)/30,2),"")</f>
@@ -17724,7 +17726,7 @@
         <v>30</v>
       </c>
       <c r="D583" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E583" s="5" t="n">
         <f aca="false">IF((F583+G583)&gt;0,ROUND((F583+G583)/30,2),"")</f>
@@ -17746,7 +17748,7 @@
         <v>30</v>
       </c>
       <c r="D584" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E584" s="5" t="n">
         <f aca="false">IF((F584+G584)&gt;0,ROUND((F584+G584)/30,2),"")</f>
@@ -17768,7 +17770,7 @@
         <v>30</v>
       </c>
       <c r="D585" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E585" s="5" t="str">
         <f aca="false">IF((F585+G585)&gt;0,ROUND((F585+G585)/30,2),"")</f>
@@ -17790,7 +17792,7 @@
         <v>30</v>
       </c>
       <c r="D586" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E586" s="5" t="n">
         <f aca="false">IF((F586+G586)&gt;0,ROUND((F586+G586)/30,2),"")</f>
@@ -17812,7 +17814,7 @@
         <v>30</v>
       </c>
       <c r="D587" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E587" s="5" t="n">
         <f aca="false">IF((F587+G587)&gt;0,ROUND((F587+G587)/30,2),"")</f>
@@ -17834,7 +17836,7 @@
         <v>30</v>
       </c>
       <c r="D588" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E588" s="5" t="n">
         <f aca="false">IF((F588+G588)&gt;0,ROUND((F588+G588)/30,2),"")</f>
@@ -17856,7 +17858,7 @@
         <v>41</v>
       </c>
       <c r="D589" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E589" s="5" t="n">
         <f aca="false">IF((F589+G589)&gt;0,ROUND((F589+G589)/30,2),"")</f>
@@ -17878,7 +17880,7 @@
         <v>41</v>
       </c>
       <c r="D590" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E590" s="5" t="n">
         <f aca="false">IF((F590+G590)&gt;0,ROUND((F590+G590)/30,2),"")</f>
@@ -17900,7 +17902,7 @@
         <v>41</v>
       </c>
       <c r="D591" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E591" s="5" t="n">
         <f aca="false">IF((F591+G591)&gt;0,ROUND((F591+G591)/30,2),"")</f>
@@ -17922,7 +17924,7 @@
         <v>41</v>
       </c>
       <c r="D592" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E592" s="5" t="n">
         <f aca="false">IF((F592+G592)&gt;0,ROUND((F592+G592)/30,2),"")</f>
@@ -17944,7 +17946,7 @@
         <v>41</v>
       </c>
       <c r="D593" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E593" s="5" t="n">
         <f aca="false">IF((F593+G593)&gt;0,ROUND((F593+G593)/30,2),"")</f>
@@ -17966,7 +17968,7 @@
         <v>41</v>
       </c>
       <c r="D594" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E594" s="5" t="n">
         <f aca="false">IF((F594+G594)&gt;0,ROUND((F594+G594)/30,2),"")</f>
@@ -17988,7 +17990,7 @@
         <v>41</v>
       </c>
       <c r="D595" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E595" s="5" t="n">
         <f aca="false">IF((F595+G595)&gt;0,ROUND((F595+G595)/30,2),"")</f>
@@ -18010,7 +18012,7 @@
         <v>41</v>
       </c>
       <c r="D596" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E596" s="5" t="n">
         <f aca="false">IF((F596+G596)&gt;0,ROUND((F596+G596)/30,2),"")</f>
@@ -18032,7 +18034,7 @@
         <v>41</v>
       </c>
       <c r="D597" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E597" s="5" t="n">
         <f aca="false">IF((F597+G597)&gt;0,ROUND((F597+G597)/30,2),"")</f>
@@ -18054,7 +18056,7 @@
         <v>41</v>
       </c>
       <c r="D598" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E598" s="5" t="n">
         <f aca="false">IF((F598+G598)&gt;0,ROUND((F598+G598)/30,2),"")</f>
@@ -18076,7 +18078,7 @@
         <v>41</v>
       </c>
       <c r="D599" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E599" s="5" t="n">
         <f aca="false">IF((F599+G599)&gt;0,ROUND((F599+G599)/30,2),"")</f>
@@ -18098,7 +18100,7 @@
         <v>41</v>
       </c>
       <c r="D600" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E600" s="5" t="n">
         <f aca="false">IF((F600+G600)&gt;0,ROUND((F600+G600)/30,2),"")</f>
@@ -18120,7 +18122,7 @@
         <v>41</v>
       </c>
       <c r="D601" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E601" s="5" t="n">
         <f aca="false">IF((F601+G601)&gt;0,ROUND((F601+G601)/30,2),"")</f>
@@ -18142,7 +18144,7 @@
         <v>41</v>
       </c>
       <c r="D602" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E602" s="5" t="n">
         <f aca="false">IF((F602+G602)&gt;0,ROUND((F602+G602)/30,2),"")</f>
@@ -18164,7 +18166,7 @@
         <v>41</v>
       </c>
       <c r="D603" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E603" s="5" t="n">
         <f aca="false">IF((F603+G603)&gt;0,ROUND((F603+G603)/30,2),"")</f>
@@ -18186,7 +18188,7 @@
         <v>41</v>
       </c>
       <c r="D604" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E604" s="5" t="n">
         <f aca="false">IF((F604+G604)&gt;0,ROUND((F604+G604)/30,2),"")</f>
@@ -18208,7 +18210,7 @@
         <v>41</v>
       </c>
       <c r="D605" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E605" s="5" t="n">
         <f aca="false">IF((F605+G605)&gt;0,ROUND((F605+G605)/30,2),"")</f>
@@ -18230,7 +18232,7 @@
         <v>41</v>
       </c>
       <c r="D606" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E606" s="5" t="n">
         <f aca="false">IF((F606+G606)&gt;0,ROUND((F606+G606)/30,2),"")</f>
@@ -18252,7 +18254,7 @@
         <v>41</v>
       </c>
       <c r="D607" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E607" s="5" t="n">
         <f aca="false">IF((F607+G607)&gt;0,ROUND((F607+G607)/30,2),"")</f>
@@ -18274,7 +18276,7 @@
         <v>41</v>
       </c>
       <c r="D608" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E608" s="5" t="n">
         <f aca="false">IF((F608+G608)&gt;0,ROUND((F608+G608)/30,2),"")</f>
@@ -18296,7 +18298,7 @@
         <v>41</v>
       </c>
       <c r="D609" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E609" s="5" t="n">
         <f aca="false">IF((F609+G609)&gt;0,ROUND((F609+G609)/30,2),"")</f>
@@ -18318,7 +18320,7 @@
         <v>41</v>
       </c>
       <c r="D610" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E610" s="5" t="n">
         <f aca="false">IF((F610+G610)&gt;0,ROUND((F610+G610)/30,2),"")</f>
@@ -18340,7 +18342,7 @@
         <v>41</v>
       </c>
       <c r="D611" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E611" s="5" t="n">
         <f aca="false">IF((F611+G611)&gt;0,ROUND((F611+G611)/30,2),"")</f>
@@ -18362,7 +18364,7 @@
         <v>41</v>
       </c>
       <c r="D612" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E612" s="5" t="n">
         <f aca="false">IF((F612+G612)&gt;0,ROUND((F612+G612)/30,2),"")</f>
@@ -18384,7 +18386,7 @@
         <v>44</v>
       </c>
       <c r="D613" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E613" s="5" t="n">
         <f aca="false">IF((F613+G613)&gt;0,ROUND((F613+G613)/30,2),"")</f>
@@ -18406,7 +18408,7 @@
         <v>44</v>
       </c>
       <c r="D614" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E614" s="5" t="n">
         <f aca="false">IF((F614+G614)&gt;0,ROUND((F614+G614)/30,2),"")</f>
@@ -18428,7 +18430,7 @@
         <v>44</v>
       </c>
       <c r="D615" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E615" s="5" t="str">
         <f aca="false">IF((F615+G615)&gt;0,ROUND((F615+G615)/30,2),"")</f>
@@ -18450,7 +18452,7 @@
         <v>44</v>
       </c>
       <c r="D616" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E616" s="5" t="n">
         <f aca="false">IF((F616+G616)&gt;0,ROUND((F616+G616)/30,2),"")</f>
@@ -18472,7 +18474,7 @@
         <v>44</v>
       </c>
       <c r="D617" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E617" s="5" t="n">
         <f aca="false">IF((F617+G617)&gt;0,ROUND((F617+G617)/30,2),"")</f>
@@ -18494,7 +18496,7 @@
         <v>44</v>
       </c>
       <c r="D618" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E618" s="5" t="n">
         <f aca="false">IF((F618+G618)&gt;0,ROUND((F618+G618)/30,2),"")</f>
@@ -18516,7 +18518,7 @@
         <v>44</v>
       </c>
       <c r="D619" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E619" s="5" t="n">
         <f aca="false">IF((F619+G619)&gt;0,ROUND((F619+G619)/30,2),"")</f>
@@ -18538,7 +18540,7 @@
         <v>44</v>
       </c>
       <c r="D620" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E620" s="5" t="str">
         <f aca="false">IF((F620+G620)&gt;0,ROUND((F620+G620)/30,2),"")</f>
@@ -18560,7 +18562,7 @@
         <v>44</v>
       </c>
       <c r="D621" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E621" s="5" t="str">
         <f aca="false">IF((F621+G621)&gt;0,ROUND((F621+G621)/30,2),"")</f>
@@ -18582,14 +18584,14 @@
         <v>44</v>
       </c>
       <c r="D622" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E622" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="E622" s="5" t="str">
         <f aca="false">IF((F622+G622)&gt;0,ROUND((F622+G622)/30,2),"")</f>
-        <v>13.33</v>
+        <v/>
       </c>
       <c r="F622" s="5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G622" s="5"/>
     </row>
@@ -18604,7 +18606,7 @@
         <v>44</v>
       </c>
       <c r="D623" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E623" s="5" t="str">
         <f aca="false">IF((F623+G623)&gt;0,ROUND((F623+G623)/30,2),"")</f>
@@ -18626,7 +18628,7 @@
         <v>44</v>
       </c>
       <c r="D624" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E624" s="5" t="str">
         <f aca="false">IF((F624+G624)&gt;0,ROUND((F624+G624)/30,2),"")</f>
@@ -18670,7 +18672,7 @@
         <v>44</v>
       </c>
       <c r="D626" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E626" s="5" t="n">
         <f aca="false">IF((F626+G626)&gt;0,ROUND((F626+G626)/30,2),"")</f>
@@ -18692,7 +18694,7 @@
         <v>44</v>
       </c>
       <c r="D627" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E627" s="5" t="n">
         <f aca="false">IF((F627+G627)&gt;0,ROUND((F627+G627)/30,2),"")</f>
@@ -18714,7 +18716,7 @@
         <v>44</v>
       </c>
       <c r="D628" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E628" s="5" t="n">
         <f aca="false">IF((F628+G628)&gt;0,ROUND((F628+G628)/30,2),"")</f>
@@ -18736,7 +18738,7 @@
         <v>44</v>
       </c>
       <c r="D629" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E629" s="5" t="str">
         <f aca="false">IF((F629+G629)&gt;0,ROUND((F629+G629)/30,2),"")</f>
@@ -18758,7 +18760,7 @@
         <v>44</v>
       </c>
       <c r="D630" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E630" s="5" t="str">
         <f aca="false">IF((F630+G630)&gt;0,ROUND((F630+G630)/30,2),"")</f>
@@ -18780,7 +18782,7 @@
         <v>44</v>
       </c>
       <c r="D631" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E631" s="5" t="n">
         <f aca="false">IF((F631+G631)&gt;0,ROUND((F631+G631)/30,2),"")</f>
@@ -18802,7 +18804,7 @@
         <v>44</v>
       </c>
       <c r="D632" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E632" s="5" t="n">
         <f aca="false">IF((F632+G632)&gt;0,ROUND((F632+G632)/30,2),"")</f>
@@ -18824,7 +18826,7 @@
         <v>44</v>
       </c>
       <c r="D633" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E633" s="5" t="n">
         <f aca="false">IF((F633+G633)&gt;0,ROUND((F633+G633)/30,2),"")</f>
@@ -18846,7 +18848,7 @@
         <v>44</v>
       </c>
       <c r="D634" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E634" s="5" t="n">
         <f aca="false">IF((F634+G634)&gt;0,ROUND((F634+G634)/30,2),"")</f>
@@ -18868,7 +18870,7 @@
         <v>44</v>
       </c>
       <c r="D635" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E635" s="5" t="n">
         <f aca="false">IF((F635+G635)&gt;0,ROUND((F635+G635)/30,2),"")</f>
@@ -18890,7 +18892,7 @@
         <v>44</v>
       </c>
       <c r="D636" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E636" s="5" t="n">
         <f aca="false">IF((F636+G636)&gt;0,ROUND((F636+G636)/30,2),"")</f>
@@ -18912,7 +18914,7 @@
         <v>44</v>
       </c>
       <c r="D637" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E637" s="5" t="n">
         <f aca="false">IF((F637+G637)&gt;0,ROUND((F637+G637)/30,2),"")</f>
@@ -18934,14 +18936,14 @@
         <v>44</v>
       </c>
       <c r="D638" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E638" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="E638" s="5" t="str">
         <f aca="false">IF((F638+G638)&gt;0,ROUND((F638+G638)/30,2),"")</f>
-        <v>13.33</v>
+        <v/>
       </c>
       <c r="F638" s="5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="G638" s="5"/>
     </row>
@@ -18956,7 +18958,7 @@
         <v>44</v>
       </c>
       <c r="D639" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E639" s="5" t="n">
         <f aca="false">IF((F639+G639)&gt;0,ROUND((F639+G639)/30,2),"")</f>
@@ -18978,7 +18980,7 @@
         <v>44</v>
       </c>
       <c r="D640" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E640" s="5" t="n">
         <f aca="false">IF((F640+G640)&gt;0,ROUND((F640+G640)/30,2),"")</f>
@@ -19002,7 +19004,7 @@
         <v>44</v>
       </c>
       <c r="D641" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E641" s="5" t="n">
         <f aca="false">IF((F641+G641)&gt;0,ROUND((F641+G641)/30,2),"")</f>
@@ -19026,7 +19028,7 @@
         <v>44</v>
       </c>
       <c r="D642" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E642" s="5" t="n">
         <f aca="false">IF((F642+G642)&gt;0,ROUND((F642+G642)/30,2),"")</f>
@@ -19048,7 +19050,7 @@
         <v>44</v>
       </c>
       <c r="D643" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E643" s="5" t="n">
         <f aca="false">IF((F643+G643)&gt;0,ROUND((F643+G643)/30,2),"")</f>
@@ -19070,14 +19072,14 @@
         <v>44</v>
       </c>
       <c r="D644" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E644" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="E644" s="5" t="str">
         <f aca="false">IF((F644+G644)&gt;0,ROUND((F644+G644)/30,2),"")</f>
-        <v>3.33</v>
+        <v/>
       </c>
       <c r="F644" s="5" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="G644" s="5"/>
     </row>
@@ -19092,7 +19094,7 @@
         <v>44</v>
       </c>
       <c r="D645" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E645" s="5" t="n">
         <f aca="false">IF((F645+G645)&gt;0,ROUND((F645+G645)/30,2),"")</f>
@@ -19114,7 +19116,7 @@
         <v>44</v>
       </c>
       <c r="D646" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E646" s="5" t="str">
         <f aca="false">IF((F646+G646)&gt;0,ROUND((F646+G646)/30,2),"")</f>
@@ -19136,7 +19138,7 @@
         <v>44</v>
       </c>
       <c r="D647" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E647" s="5" t="n">
         <f aca="false">IF((F647+G647)&gt;0,ROUND((F647+G647)/30,2),"")</f>
@@ -19158,7 +19160,7 @@
         <v>44</v>
       </c>
       <c r="D648" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E648" s="5" t="str">
         <f aca="false">IF((F648+G648)&gt;0,ROUND((F648+G648)/30,2),"")</f>
@@ -19180,7 +19182,7 @@
         <v>44</v>
       </c>
       <c r="D649" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E649" s="5" t="n">
         <f aca="false">IF((F649+G649)&gt;0,ROUND((F649+G649)/30,2),"")</f>
@@ -19202,7 +19204,7 @@
         <v>44</v>
       </c>
       <c r="D650" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E650" s="5" t="str">
         <f aca="false">IF((F650+G650)&gt;0,ROUND((F650+G650)/30,2),"")</f>
@@ -19224,7 +19226,7 @@
         <v>44</v>
       </c>
       <c r="D651" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E651" s="5" t="str">
         <f aca="false">IF((F651+G651)&gt;0,ROUND((F651+G651)/30,2),"")</f>
@@ -19246,14 +19248,14 @@
         <v>44</v>
       </c>
       <c r="D652" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E652" s="5" t="n">
         <f aca="false">IF((F652+G652)&gt;0,ROUND((F652+G652)/30,2),"")</f>
-        <v>16.67</v>
+        <v>8.33</v>
       </c>
       <c r="F652" s="5" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="G652" s="5"/>
     </row>
@@ -19268,7 +19270,7 @@
         <v>44</v>
       </c>
       <c r="D653" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E653" s="5" t="n">
         <f aca="false">IF((F653+G653)&gt;0,ROUND((F653+G653)/30,2),"")</f>
@@ -19290,7 +19292,7 @@
         <v>44</v>
       </c>
       <c r="D654" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E654" s="5" t="n">
         <f aca="false">IF((F654+G654)&gt;0,ROUND((F654+G654)/30,2),"")</f>
@@ -19312,7 +19314,7 @@
         <v>44</v>
       </c>
       <c r="D655" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E655" s="5" t="n">
         <f aca="false">IF((F655+G655)&gt;0,ROUND((F655+G655)/30,2),"")</f>
@@ -19334,7 +19336,7 @@
         <v>44</v>
       </c>
       <c r="D656" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E656" s="5" t="n">
         <f aca="false">IF((F656+G656)&gt;0,ROUND((F656+G656)/30,2),"")</f>
@@ -19356,7 +19358,7 @@
         <v>44</v>
       </c>
       <c r="D657" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E657" s="5" t="n">
         <f aca="false">IF((F657+G657)&gt;0,ROUND((F657+G657)/30,2),"")</f>
@@ -19378,7 +19380,7 @@
         <v>44</v>
       </c>
       <c r="D658" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E658" s="5" t="str">
         <f aca="false">IF((F658+G658)&gt;0,ROUND((F658+G658)/30,2),"")</f>
@@ -19400,7 +19402,7 @@
         <v>44</v>
       </c>
       <c r="D659" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E659" s="5" t="n">
         <f aca="false">IF((F659+G659)&gt;0,ROUND((F659+G659)/30,2),"")</f>
@@ -19422,7 +19424,7 @@
         <v>44</v>
       </c>
       <c r="D660" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E660" s="5" t="str">
         <f aca="false">IF((F660+G660)&gt;0,ROUND((F660+G660)/30,2),"")</f>
@@ -19444,7 +19446,7 @@
         <v>44</v>
       </c>
       <c r="D661" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E661" s="5" t="str">
         <f aca="false">IF((F661+G661)&gt;0,ROUND((F661+G661)/30,2),"")</f>
@@ -19466,7 +19468,7 @@
         <v>44</v>
       </c>
       <c r="D662" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E662" s="5" t="n">
         <f aca="false">IF((F662+G662)&gt;0,ROUND((F662+G662)/30,2),"")</f>
@@ -19488,7 +19490,7 @@
         <v>44</v>
       </c>
       <c r="D663" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E663" s="5" t="n">
         <f aca="false">IF((F663+G663)&gt;0,ROUND((F663+G663)/30,2),"")</f>
@@ -19510,7 +19512,7 @@
         <v>44</v>
       </c>
       <c r="D664" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E664" s="5" t="str">
         <f aca="false">IF((F664+G664)&gt;0,ROUND((F664+G664)/30,2),"")</f>
@@ -19532,7 +19534,7 @@
         <v>44</v>
       </c>
       <c r="D665" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E665" s="5" t="n">
         <f aca="false">IF((F665+G665)&gt;0,ROUND((F665+G665)/30,2),"")</f>
@@ -19554,7 +19556,7 @@
         <v>44</v>
       </c>
       <c r="D666" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E666" s="5" t="n">
         <f aca="false">IF((F666+G666)&gt;0,ROUND((F666+G666)/30,2),"")</f>
@@ -19576,7 +19578,7 @@
         <v>44</v>
       </c>
       <c r="D667" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E667" s="5" t="n">
         <f aca="false">IF((F667+G667)&gt;0,ROUND((F667+G667)/30,2),"")</f>
@@ -19598,7 +19600,7 @@
         <v>44</v>
       </c>
       <c r="D668" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E668" s="5" t="n">
         <f aca="false">IF((F668+G668)&gt;0,ROUND((F668+G668)/30,2),"")</f>
@@ -19620,7 +19622,7 @@
         <v>44</v>
       </c>
       <c r="D669" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E669" s="5" t="n">
         <f aca="false">IF((F669+G669)&gt;0,ROUND((F669+G669)/30,2),"")</f>
@@ -19642,7 +19644,7 @@
         <v>44</v>
       </c>
       <c r="D670" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E670" s="5" t="n">
         <f aca="false">IF((F670+G670)&gt;0,ROUND((F670+G670)/30,2),"")</f>
@@ -19664,7 +19666,7 @@
         <v>44</v>
       </c>
       <c r="D671" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E671" s="5" t="n">
         <f aca="false">IF((F671+G671)&gt;0,ROUND((F671+G671)/30,2),"")</f>
@@ -19686,7 +19688,7 @@
         <v>44</v>
       </c>
       <c r="D672" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E672" s="5" t="n">
         <f aca="false">IF((F672+G672)&gt;0,ROUND((F672+G672)/30,2),"")</f>
@@ -19708,7 +19710,7 @@
         <v>44</v>
       </c>
       <c r="D673" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E673" s="5" t="str">
         <f aca="false">IF((F673+G673)&gt;0,ROUND((F673+G673)/30,2),"")</f>
@@ -19730,7 +19732,7 @@
         <v>44</v>
       </c>
       <c r="D674" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E674" s="5" t="n">
         <f aca="false">IF((F674+G674)&gt;0,ROUND((F674+G674)/30,2),"")</f>
@@ -19752,7 +19754,7 @@
         <v>44</v>
       </c>
       <c r="D675" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E675" s="5" t="n">
         <f aca="false">IF((F675+G675)&gt;0,ROUND((F675+G675)/30,2),"")</f>
@@ -19774,7 +19776,7 @@
         <v>44</v>
       </c>
       <c r="D676" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E676" s="5" t="n">
         <f aca="false">IF((F676+G676)&gt;0,ROUND((F676+G676)/30,2),"")</f>
@@ -19796,7 +19798,7 @@
         <v>44</v>
       </c>
       <c r="D677" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E677" s="5" t="n">
         <f aca="false">IF((F677+G677)&gt;0,ROUND((F677+G677)/30,2),"")</f>
@@ -19818,7 +19820,7 @@
         <v>44</v>
       </c>
       <c r="D678" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E678" s="5" t="str">
         <f aca="false">IF((F678+G678)&gt;0,ROUND((F678+G678)/30,2),"")</f>
@@ -19840,7 +19842,7 @@
         <v>44</v>
       </c>
       <c r="D679" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E679" s="5" t="n">
         <f aca="false">IF((F679+G679)&gt;0,ROUND((F679+G679)/30,2),"")</f>
@@ -19862,7 +19864,7 @@
         <v>44</v>
       </c>
       <c r="D680" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E680" s="5" t="n">
         <f aca="false">IF((F680+G680)&gt;0,ROUND((F680+G680)/30,2),"")</f>
@@ -19884,7 +19886,7 @@
         <v>44</v>
       </c>
       <c r="D681" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E681" s="5" t="str">
         <f aca="false">IF((F681+G681)&gt;0,ROUND((F681+G681)/30,2),"")</f>
@@ -19906,7 +19908,7 @@
         <v>44</v>
       </c>
       <c r="D682" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E682" s="5" t="n">
         <f aca="false">IF((F682+G682)&gt;0,ROUND((F682+G682)/30,2),"")</f>
@@ -19928,7 +19930,7 @@
         <v>44</v>
       </c>
       <c r="D683" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E683" s="5" t="str">
         <f aca="false">IF((F683+G683)&gt;0,ROUND((F683+G683)/30,2),"")</f>
@@ -19950,7 +19952,7 @@
         <v>44</v>
       </c>
       <c r="D684" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E684" s="5" t="str">
         <f aca="false">IF((F684+G684)&gt;0,ROUND((F684+G684)/30,2),"")</f>
@@ -19972,7 +19974,7 @@
         <v>44</v>
       </c>
       <c r="D685" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E685" s="5" t="n">
         <f aca="false">IF((F685+G685)&gt;0,ROUND((F685+G685)/30,2),"")</f>
@@ -19994,7 +19996,7 @@
         <v>44</v>
       </c>
       <c r="D686" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E686" s="5" t="str">
         <f aca="false">IF((F686+G686)&gt;0,ROUND((F686+G686)/30,2),"")</f>
@@ -20016,7 +20018,7 @@
         <v>44</v>
       </c>
       <c r="D687" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E687" s="5" t="n">
         <f aca="false">IF((F687+G687)&gt;0,ROUND((F687+G687)/30,2),"")</f>
@@ -20038,7 +20040,7 @@
         <v>44</v>
       </c>
       <c r="D688" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E688" s="5" t="str">
         <f aca="false">IF((F688+G688)&gt;0,ROUND((F688+G688)/30,2),"")</f>
@@ -20060,7 +20062,7 @@
         <v>44</v>
       </c>
       <c r="D689" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E689" s="5" t="n">
         <f aca="false">IF((F689+G689)&gt;0,ROUND((F689+G689)/30,2),"")</f>
@@ -20082,7 +20084,7 @@
         <v>44</v>
       </c>
       <c r="D690" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E690" s="5" t="str">
         <f aca="false">IF((F690+G690)&gt;0,ROUND((F690+G690)/30,2),"")</f>
@@ -20104,7 +20106,7 @@
         <v>44</v>
       </c>
       <c r="D691" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E691" s="5" t="n">
         <f aca="false">IF((F691+G691)&gt;0,ROUND((F691+G691)/30,2),"")</f>
@@ -20126,7 +20128,7 @@
         <v>44</v>
       </c>
       <c r="D692" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E692" s="5" t="n">
         <f aca="false">IF((F692+G692)&gt;0,ROUND((F692+G692)/30,2),"")</f>
@@ -20148,7 +20150,7 @@
         <v>44</v>
       </c>
       <c r="D693" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E693" s="5" t="n">
         <f aca="false">IF((F693+G693)&gt;0,ROUND((F693+G693)/30,2),"")</f>
@@ -20170,7 +20172,7 @@
         <v>44</v>
       </c>
       <c r="D694" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E694" s="5" t="str">
         <f aca="false">IF((F694+G694)&gt;0,ROUND((F694+G694)/30,2),"")</f>
@@ -20192,7 +20194,7 @@
         <v>44</v>
       </c>
       <c r="D695" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E695" s="5" t="str">
         <f aca="false">IF((F695+G695)&gt;0,ROUND((F695+G695)/30,2),"")</f>
@@ -20214,7 +20216,7 @@
         <v>44</v>
       </c>
       <c r="D696" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E696" s="5" t="str">
         <f aca="false">IF((F696+G696)&gt;0,ROUND((F696+G696)/30,2),"")</f>
@@ -20236,7 +20238,7 @@
         <v>44</v>
       </c>
       <c r="D697" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E697" s="5" t="n">
         <f aca="false">IF((F697+G697)&gt;0,ROUND((F697+G697)/30,2),"")</f>
@@ -20258,7 +20260,7 @@
         <v>44</v>
       </c>
       <c r="D698" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E698" s="5" t="n">
         <f aca="false">IF((F698+G698)&gt;0,ROUND((F698+G698)/30,2),"")</f>
@@ -20280,7 +20282,7 @@
         <v>44</v>
       </c>
       <c r="D699" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E699" s="5" t="str">
         <f aca="false">IF((F699+G699)&gt;0,ROUND((F699+G699)/30,2),"")</f>
@@ -20302,7 +20304,7 @@
         <v>44</v>
       </c>
       <c r="D700" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E700" s="5" t="n">
         <f aca="false">IF((F700+G700)&gt;0,ROUND((F700+G700)/30,2),"")</f>
@@ -20324,7 +20326,7 @@
         <v>44</v>
       </c>
       <c r="D701" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E701" s="5" t="n">
         <f aca="false">IF((F701+G701)&gt;0,ROUND((F701+G701)/30,2),"")</f>
@@ -20346,7 +20348,7 @@
         <v>44</v>
       </c>
       <c r="D702" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E702" s="5" t="str">
         <f aca="false">IF((F702+G702)&gt;0,ROUND((F702+G702)/30,2),"")</f>
@@ -20368,7 +20370,7 @@
         <v>44</v>
       </c>
       <c r="D703" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E703" s="5" t="str">
         <f aca="false">IF((F703+G703)&gt;0,ROUND((F703+G703)/30,2),"")</f>
@@ -20390,7 +20392,7 @@
         <v>44</v>
       </c>
       <c r="D704" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E704" s="5" t="n">
         <f aca="false">IF((F704+G704)&gt;0,ROUND((F704+G704)/30,2),"")</f>
@@ -20412,7 +20414,7 @@
         <v>44</v>
       </c>
       <c r="D705" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E705" s="5" t="str">
         <f aca="false">IF((F705+G705)&gt;0,ROUND((F705+G705)/30,2),"")</f>
@@ -20434,7 +20436,7 @@
         <v>44</v>
       </c>
       <c r="D706" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E706" s="5" t="n">
         <f aca="false">IF((F706+G706)&gt;0,ROUND((F706+G706)/30,2),"")</f>
@@ -20456,7 +20458,7 @@
         <v>44</v>
       </c>
       <c r="D707" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E707" s="5" t="str">
         <f aca="false">IF((F707+G707)&gt;0,ROUND((F707+G707)/30,2),"")</f>
@@ -20478,7 +20480,7 @@
         <v>44</v>
       </c>
       <c r="D708" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E708" s="5" t="n">
         <f aca="false">IF((F708+G708)&gt;0,ROUND((F708+G708)/30,2),"")</f>
@@ -20500,7 +20502,7 @@
         <v>44</v>
       </c>
       <c r="D709" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E709" s="5" t="str">
         <f aca="false">IF((F709+G709)&gt;0,ROUND((F709+G709)/30,2),"")</f>
@@ -20522,7 +20524,7 @@
         <v>44</v>
       </c>
       <c r="D710" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E710" s="5" t="n">
         <f aca="false">IF((F710+G710)&gt;0,ROUND((F710+G710)/30,2),"")</f>
@@ -20544,7 +20546,7 @@
         <v>44</v>
       </c>
       <c r="D711" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E711" s="5" t="str">
         <f aca="false">IF((F711+G711)&gt;0,ROUND((F711+G711)/30,2),"")</f>
@@ -20566,7 +20568,7 @@
         <v>44</v>
       </c>
       <c r="D712" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E712" s="5" t="n">
         <f aca="false">IF((F712+G712)&gt;0,ROUND((F712+G712)/30,2),"")</f>
@@ -20588,7 +20590,7 @@
         <v>44</v>
       </c>
       <c r="D713" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E713" s="5" t="n">
         <f aca="false">IF((F713+G713)&gt;0,ROUND((F713+G713)/30,2),"")</f>
@@ -20610,7 +20612,7 @@
         <v>44</v>
       </c>
       <c r="D714" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E714" s="5" t="n">
         <f aca="false">IF((F714+G714)&gt;0,ROUND((F714+G714)/30,2),"")</f>
@@ -20632,7 +20634,7 @@
         <v>44</v>
       </c>
       <c r="D715" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E715" s="5" t="n">
         <f aca="false">IF((F715+G715)&gt;0,ROUND((F715+G715)/30,2),"")</f>
@@ -20654,7 +20656,7 @@
         <v>44</v>
       </c>
       <c r="D716" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E716" s="5" t="str">
         <f aca="false">IF((F716+G716)&gt;0,ROUND((F716+G716)/30,2),"")</f>
@@ -20676,7 +20678,7 @@
         <v>44</v>
       </c>
       <c r="D717" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E717" s="5" t="n">
         <f aca="false">IF((F717+G717)&gt;0,ROUND((F717+G717)/30,2),"")</f>
@@ -20698,7 +20700,7 @@
         <v>44</v>
       </c>
       <c r="D718" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E718" s="5" t="n">
         <f aca="false">IF((F718+G718)&gt;0,ROUND((F718+G718)/30,2),"")</f>
@@ -20720,7 +20722,7 @@
         <v>44</v>
       </c>
       <c r="D719" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E719" s="5" t="str">
         <f aca="false">IF((F719+G719)&gt;0,ROUND((F719+G719)/30,2),"")</f>
@@ -20742,7 +20744,7 @@
         <v>44</v>
       </c>
       <c r="D720" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E720" s="5" t="str">
         <f aca="false">IF((F720+G720)&gt;0,ROUND((F720+G720)/30,2),"")</f>
@@ -20764,7 +20766,7 @@
         <v>44</v>
       </c>
       <c r="D721" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E721" s="5" t="n">
         <f aca="false">IF((F721+G721)&gt;0,ROUND((F721+G721)/30,2),"")</f>
@@ -20786,7 +20788,7 @@
         <v>44</v>
       </c>
       <c r="D722" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E722" s="5" t="n">
         <f aca="false">IF((F722+G722)&gt;0,ROUND((F722+G722)/30,2),"")</f>
@@ -20808,7 +20810,7 @@
         <v>44</v>
       </c>
       <c r="D723" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E723" s="5" t="n">
         <f aca="false">IF((F723+G723)&gt;0,ROUND((F723+G723)/30,2),"")</f>
@@ -20830,7 +20832,7 @@
         <v>44</v>
       </c>
       <c r="D724" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E724" s="5" t="n">
         <f aca="false">IF((F724+G724)&gt;0,ROUND((F724+G724)/30,2),"")</f>
@@ -20852,7 +20854,7 @@
         <v>44</v>
       </c>
       <c r="D725" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E725" s="5" t="n">
         <f aca="false">IF((F725+G725)&gt;0,ROUND((F725+G725)/30,2),"")</f>
@@ -20874,7 +20876,7 @@
         <v>44</v>
       </c>
       <c r="D726" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E726" s="5" t="n">
         <f aca="false">IF((F726+G726)&gt;0,ROUND((F726+G726)/30,2),"")</f>
@@ -20896,7 +20898,7 @@
         <v>44</v>
       </c>
       <c r="D727" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E727" s="5" t="str">
         <f aca="false">IF((F727+G727)&gt;0,ROUND((F727+G727)/30,2),"")</f>
@@ -20918,7 +20920,7 @@
         <v>44</v>
       </c>
       <c r="D728" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E728" s="5" t="str">
         <f aca="false">IF((F728+G728)&gt;0,ROUND((F728+G728)/30,2),"")</f>
@@ -20940,7 +20942,7 @@
         <v>44</v>
       </c>
       <c r="D729" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E729" s="5" t="n">
         <f aca="false">IF((F729+G729)&gt;0,ROUND((F729+G729)/30,2),"")</f>
@@ -20962,7 +20964,7 @@
         <v>44</v>
       </c>
       <c r="D730" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E730" s="5" t="str">
         <f aca="false">IF((F730+G730)&gt;0,ROUND((F730+G730)/30,2),"")</f>
@@ -20984,7 +20986,7 @@
         <v>44</v>
       </c>
       <c r="D731" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E731" s="5" t="n">
         <f aca="false">IF((F731+G731)&gt;0,ROUND((F731+G731)/30,2),"")</f>
@@ -21006,7 +21008,7 @@
         <v>44</v>
       </c>
       <c r="D732" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E732" s="5" t="n">
         <f aca="false">IF((F732+G732)&gt;0,ROUND((F732+G732)/30,2),"")</f>
@@ -21028,7 +21030,7 @@
         <v>44</v>
       </c>
       <c r="D733" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E733" s="5" t="n">
         <f aca="false">IF((F733+G733)&gt;0,ROUND((F733+G733)/30,2),"")</f>
@@ -21050,7 +21052,7 @@
         <v>44</v>
       </c>
       <c r="D734" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E734" s="5" t="n">
         <f aca="false">IF((F734+G734)&gt;0,ROUND((F734+G734)/30,2),"")</f>
@@ -21072,7 +21074,7 @@
         <v>44</v>
       </c>
       <c r="D735" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E735" s="5" t="str">
         <f aca="false">IF((F735+G735)&gt;0,ROUND((F735+G735)/30,2),"")</f>
@@ -21094,7 +21096,7 @@
         <v>44</v>
       </c>
       <c r="D736" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E736" s="5" t="n">
         <f aca="false">IF((F736+G736)&gt;0,ROUND((F736+G736)/30,2),"")</f>
@@ -21116,7 +21118,7 @@
         <v>44</v>
       </c>
       <c r="D737" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E737" s="5" t="n">
         <f aca="false">IF((F737+G737)&gt;0,ROUND((F737+G737)/30,2),"")</f>
@@ -21138,7 +21140,7 @@
         <v>44</v>
       </c>
       <c r="D738" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E738" s="5" t="n">
         <f aca="false">IF((F738+G738)&gt;0,ROUND((F738+G738)/30,2),"")</f>
@@ -21160,7 +21162,7 @@
         <v>44</v>
       </c>
       <c r="D739" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E739" s="5" t="n">
         <f aca="false">IF((F739+G739)&gt;0,ROUND((F739+G739)/30,2),"")</f>
@@ -21182,7 +21184,7 @@
         <v>44</v>
       </c>
       <c r="D740" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E740" s="5" t="n">
         <f aca="false">IF((F740+G740)&gt;0,ROUND((F740+G740)/30,2),"")</f>
@@ -21204,7 +21206,7 @@
         <v>44</v>
       </c>
       <c r="D741" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E741" s="5" t="n">
         <f aca="false">IF((F741+G741)&gt;0,ROUND((F741+G741)/30,2),"")</f>
@@ -21226,7 +21228,7 @@
         <v>44</v>
       </c>
       <c r="D742" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E742" s="5" t="n">
         <f aca="false">IF((F742+G742)&gt;0,ROUND((F742+G742)/30,2),"")</f>
@@ -21248,7 +21250,7 @@
         <v>169</v>
       </c>
       <c r="D743" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E743" s="5" t="n">
         <f aca="false">IF((F743+G743)&gt;0,ROUND((F743+G743)/30,2),"")</f>
@@ -21270,7 +21272,7 @@
         <v>169</v>
       </c>
       <c r="D744" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E744" s="5" t="n">
         <f aca="false">IF((F744+G744)&gt;0,ROUND((F744+G744)/30,2),"")</f>
@@ -21292,7 +21294,7 @@
         <v>169</v>
       </c>
       <c r="D745" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E745" s="5" t="n">
         <f aca="false">IF((F745+G745)&gt;0,ROUND((F745+G745)/30,2),"")</f>
@@ -21314,7 +21316,7 @@
         <v>169</v>
       </c>
       <c r="D746" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E746" s="5" t="n">
         <f aca="false">IF((F746+G746)&gt;0,ROUND((F746+G746)/30,2),"")</f>
@@ -21336,7 +21338,7 @@
         <v>59</v>
       </c>
       <c r="D747" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E747" s="5" t="n">
         <f aca="false">IF((F747+G747)&gt;0,ROUND((F747+G747)/30,2),"")</f>
@@ -21358,7 +21360,7 @@
         <v>59</v>
       </c>
       <c r="D748" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E748" s="5" t="n">
         <f aca="false">IF((F748+G748)&gt;0,ROUND((F748+G748)/30,2),"")</f>
@@ -21380,7 +21382,7 @@
         <v>59</v>
       </c>
       <c r="D749" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E749" s="5" t="n">
         <f aca="false">IF((F749+G749)&gt;0,ROUND((F749+G749)/30,2),"")</f>
@@ -21402,7 +21404,7 @@
         <v>59</v>
       </c>
       <c r="D750" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E750" s="5" t="n">
         <f aca="false">IF((F750+G750)&gt;0,ROUND((F750+G750)/30,2),"")</f>
@@ -21424,7 +21426,7 @@
         <v>59</v>
       </c>
       <c r="D751" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E751" s="5" t="n">
         <f aca="false">IF((F751+G751)&gt;0,ROUND((F751+G751)/30,2),"")</f>
@@ -21446,7 +21448,7 @@
         <v>59</v>
       </c>
       <c r="D752" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E752" s="5" t="n">
         <f aca="false">IF((F752+G752)&gt;0,ROUND((F752+G752)/30,2),"")</f>
@@ -21468,7 +21470,7 @@
         <v>59</v>
       </c>
       <c r="D753" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E753" s="5" t="n">
         <f aca="false">IF((F753+G753)&gt;0,ROUND((F753+G753)/30,2),"")</f>
@@ -21490,7 +21492,7 @@
         <v>59</v>
       </c>
       <c r="D754" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E754" s="5" t="n">
         <f aca="false">IF((F754+G754)&gt;0,ROUND((F754+G754)/30,2),"")</f>
@@ -21512,7 +21514,7 @@
         <v>59</v>
       </c>
       <c r="D755" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E755" s="5" t="n">
         <f aca="false">IF((F755+G755)&gt;0,ROUND((F755+G755)/30,2),"")</f>
@@ -21534,7 +21536,7 @@
         <v>59</v>
       </c>
       <c r="D756" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E756" s="5" t="n">
         <f aca="false">IF((F756+G756)&gt;0,ROUND((F756+G756)/30,2),"")</f>
@@ -21556,7 +21558,7 @@
         <v>59</v>
       </c>
       <c r="D757" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E757" s="5" t="n">
         <f aca="false">IF((F757+G757)&gt;0,ROUND((F757+G757)/30,2),"")</f>
@@ -21578,7 +21580,7 @@
         <v>59</v>
       </c>
       <c r="D758" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E758" s="5" t="n">
         <f aca="false">IF((F758+G758)&gt;0,ROUND((F758+G758)/30,2),"")</f>
@@ -21600,7 +21602,7 @@
         <v>59</v>
       </c>
       <c r="D759" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E759" s="5" t="n">
         <f aca="false">IF((F759+G759)&gt;0,ROUND((F759+G759)/30,2),"")</f>
@@ -21622,7 +21624,7 @@
         <v>59</v>
       </c>
       <c r="D760" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E760" s="5" t="n">
         <f aca="false">IF((F760+G760)&gt;0,ROUND((F760+G760)/30,2),"")</f>
@@ -21644,7 +21646,7 @@
         <v>59</v>
       </c>
       <c r="D761" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E761" s="5" t="n">
         <f aca="false">IF((F761+G761)&gt;0,ROUND((F761+G761)/30,2),"")</f>
@@ -21666,7 +21668,7 @@
         <v>59</v>
       </c>
       <c r="D762" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E762" s="5" t="n">
         <f aca="false">IF((F762+G762)&gt;0,ROUND((F762+G762)/30,2),"")</f>
@@ -21688,7 +21690,7 @@
         <v>59</v>
       </c>
       <c r="D763" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E763" s="5" t="n">
         <f aca="false">IF((F763+G763)&gt;0,ROUND((F763+G763)/30,2),"")</f>
@@ -21710,7 +21712,7 @@
         <v>59</v>
       </c>
       <c r="D764" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E764" s="5" t="n">
         <f aca="false">IF((F764+G764)&gt;0,ROUND((F764+G764)/30,2),"")</f>
@@ -21732,7 +21734,7 @@
         <v>59</v>
       </c>
       <c r="D765" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E765" s="5" t="n">
         <f aca="false">IF((F765+G765)&gt;0,ROUND((F765+G765)/30,2),"")</f>
@@ -21754,7 +21756,7 @@
         <v>59</v>
       </c>
       <c r="D766" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E766" s="5" t="n">
         <f aca="false">IF((F766+G766)&gt;0,ROUND((F766+G766)/30,2),"")</f>
@@ -21776,7 +21778,7 @@
         <v>59</v>
       </c>
       <c r="D767" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E767" s="5" t="n">
         <f aca="false">IF((F767+G767)&gt;0,ROUND((F767+G767)/30,2),"")</f>
@@ -21798,7 +21800,7 @@
         <v>59</v>
       </c>
       <c r="D768" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E768" s="5" t="n">
         <f aca="false">IF((F768+G768)&gt;0,ROUND((F768+G768)/30,2),"")</f>
@@ -21820,7 +21822,7 @@
         <v>59</v>
       </c>
       <c r="D769" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E769" s="5" t="n">
         <f aca="false">IF((F769+G769)&gt;0,ROUND((F769+G769)/30,2),"")</f>
@@ -21842,7 +21844,7 @@
         <v>59</v>
       </c>
       <c r="D770" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E770" s="5" t="n">
         <f aca="false">IF((F770+G770)&gt;0,ROUND((F770+G770)/30,2),"")</f>
@@ -21864,7 +21866,7 @@
         <v>59</v>
       </c>
       <c r="D771" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E771" s="5" t="n">
         <f aca="false">IF((F771+G771)&gt;0,ROUND((F771+G771)/30,2),"")</f>
@@ -21886,7 +21888,7 @@
         <v>59</v>
       </c>
       <c r="D772" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E772" s="5" t="n">
         <f aca="false">IF((F772+G772)&gt;0,ROUND((F772+G772)/30,2),"")</f>
@@ -21908,7 +21910,7 @@
         <v>59</v>
       </c>
       <c r="D773" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E773" s="5" t="n">
         <f aca="false">IF((F773+G773)&gt;0,ROUND((F773+G773)/30,2),"")</f>
@@ -21930,7 +21932,7 @@
         <v>59</v>
       </c>
       <c r="D774" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E774" s="5" t="n">
         <f aca="false">IF((F774+G774)&gt;0,ROUND((F774+G774)/30,2),"")</f>
@@ -21952,7 +21954,7 @@
         <v>59</v>
       </c>
       <c r="D775" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E775" s="5" t="n">
         <f aca="false">IF((F775+G775)&gt;0,ROUND((F775+G775)/30,2),"")</f>
@@ -21974,7 +21976,7 @@
         <v>59</v>
       </c>
       <c r="D776" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E776" s="5" t="n">
         <f aca="false">IF((F776+G776)&gt;0,ROUND((F776+G776)/30,2),"")</f>
@@ -21996,7 +21998,7 @@
         <v>59</v>
       </c>
       <c r="D777" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E777" s="5" t="n">
         <f aca="false">IF((F777+G777)&gt;0,ROUND((F777+G777)/30,2),"")</f>
@@ -22018,7 +22020,7 @@
         <v>59</v>
       </c>
       <c r="D778" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E778" s="5" t="n">
         <f aca="false">IF((F778+G778)&gt;0,ROUND((F778+G778)/30,2),"")</f>
@@ -22040,7 +22042,7 @@
         <v>59</v>
       </c>
       <c r="D779" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E779" s="5" t="n">
         <f aca="false">IF((F779+G779)&gt;0,ROUND((F779+G779)/30,2),"")</f>
@@ -22062,7 +22064,7 @@
         <v>59</v>
       </c>
       <c r="D780" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E780" s="5" t="n">
         <f aca="false">IF((F780+G780)&gt;0,ROUND((F780+G780)/30,2),"")</f>
@@ -22084,7 +22086,7 @@
         <v>67</v>
       </c>
       <c r="D781" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E781" s="5" t="str">
         <f aca="false">IF((F781+G781)&gt;0,ROUND((F781+G781)/30,2),"")</f>
@@ -22106,7 +22108,7 @@
         <v>67</v>
       </c>
       <c r="D782" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E782" s="5" t="n">
         <f aca="false">IF((F782+G782)&gt;0,ROUND((F782+G782)/30,2),"")</f>
@@ -22128,7 +22130,7 @@
         <v>67</v>
       </c>
       <c r="D783" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E783" s="5" t="n">
         <f aca="false">IF((F783+G783)&gt;0,ROUND((F783+G783)/30,2),"")</f>
@@ -22150,7 +22152,7 @@
         <v>67</v>
       </c>
       <c r="D784" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E784" s="5" t="n">
         <f aca="false">IF((F784+G784)&gt;0,ROUND((F784+G784)/30,2),"")</f>
@@ -22172,7 +22174,7 @@
         <v>67</v>
       </c>
       <c r="D785" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E785" s="5" t="n">
         <f aca="false">IF((F785+G785)&gt;0,ROUND((F785+G785)/30,2),"")</f>
@@ -22194,7 +22196,7 @@
         <v>67</v>
       </c>
       <c r="D786" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E786" s="5" t="n">
         <f aca="false">IF((F786+G786)&gt;0,ROUND((F786+G786)/30,2),"")</f>
@@ -22216,7 +22218,7 @@
         <v>67</v>
       </c>
       <c r="D787" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E787" s="5" t="n">
         <f aca="false">IF((F787+G787)&gt;0,ROUND((F787+G787)/30,2),"")</f>
@@ -22238,7 +22240,7 @@
         <v>67</v>
       </c>
       <c r="D788" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E788" s="5" t="n">
         <f aca="false">IF((F788+G788)&gt;0,ROUND((F788+G788)/30,2),"")</f>
@@ -22260,7 +22262,7 @@
         <v>67</v>
       </c>
       <c r="D789" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E789" s="5" t="str">
         <f aca="false">IF((F789+G789)&gt;0,ROUND((F789+G789)/30,2),"")</f>
@@ -22282,7 +22284,7 @@
         <v>67</v>
       </c>
       <c r="D790" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E790" s="5" t="str">
         <f aca="false">IF((F790+G790)&gt;0,ROUND((F790+G790)/30,2),"")</f>
@@ -22304,7 +22306,7 @@
         <v>67</v>
       </c>
       <c r="D791" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E791" s="5" t="str">
         <f aca="false">IF((F791+G791)&gt;0,ROUND((F791+G791)/30,2),"")</f>
@@ -22326,7 +22328,7 @@
         <v>67</v>
       </c>
       <c r="D792" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E792" s="5" t="n">
         <f aca="false">IF((F792+G792)&gt;0,ROUND((F792+G792)/30,2),"")</f>
@@ -22348,7 +22350,7 @@
         <v>67</v>
       </c>
       <c r="D793" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E793" s="5" t="n">
         <f aca="false">IF((F793+G793)&gt;0,ROUND((F793+G793)/30,2),"")</f>
@@ -22370,7 +22372,7 @@
         <v>67</v>
       </c>
       <c r="D794" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E794" s="5" t="n">
         <f aca="false">IF((F794+G794)&gt;0,ROUND((F794+G794)/30,2),"")</f>
@@ -22392,7 +22394,7 @@
         <v>67</v>
       </c>
       <c r="D795" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E795" s="5" t="n">
         <f aca="false">IF((F795+G795)&gt;0,ROUND((F795+G795)/30,2),"")</f>
@@ -22414,7 +22416,7 @@
         <v>67</v>
       </c>
       <c r="D796" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E796" s="5" t="n">
         <f aca="false">IF((F796+G796)&gt;0,ROUND((F796+G796)/30,2),"")</f>
@@ -22436,7 +22438,7 @@
         <v>67</v>
       </c>
       <c r="D797" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E797" s="5" t="n">
         <f aca="false">IF((F797+G797)&gt;0,ROUND((F797+G797)/30,2),"")</f>
@@ -22458,7 +22460,7 @@
         <v>67</v>
       </c>
       <c r="D798" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E798" s="5" t="n">
         <f aca="false">IF((F798+G798)&gt;0,ROUND((F798+G798)/30,2),"")</f>
@@ -22480,7 +22482,7 @@
         <v>67</v>
       </c>
       <c r="D799" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E799" s="5" t="n">
         <f aca="false">IF((F799+G799)&gt;0,ROUND((F799+G799)/30,2),"")</f>
@@ -22502,7 +22504,7 @@
         <v>67</v>
       </c>
       <c r="D800" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E800" s="5" t="str">
         <f aca="false">IF((F800+G800)&gt;0,ROUND((F800+G800)/30,2),"")</f>
@@ -22524,7 +22526,7 @@
         <v>67</v>
       </c>
       <c r="D801" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E801" s="5" t="n">
         <f aca="false">IF((F801+G801)&gt;0,ROUND((F801+G801)/30,2),"")</f>
@@ -22546,7 +22548,7 @@
         <v>67</v>
       </c>
       <c r="D802" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E802" s="5" t="str">
         <f aca="false">IF((F802+G802)&gt;0,ROUND((F802+G802)/30,2),"")</f>
@@ -22568,7 +22570,7 @@
         <v>67</v>
       </c>
       <c r="D803" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E803" s="5" t="str">
         <f aca="false">IF((F803+G803)&gt;0,ROUND((F803+G803)/30,2),"")</f>
@@ -22590,7 +22592,7 @@
         <v>67</v>
       </c>
       <c r="D804" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E804" s="5" t="n">
         <f aca="false">IF((F804+G804)&gt;0,ROUND((F804+G804)/30,2),"")</f>
@@ -22612,7 +22614,7 @@
         <v>67</v>
       </c>
       <c r="D805" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E805" s="5" t="n">
         <f aca="false">IF((F805+G805)&gt;0,ROUND((F805+G805)/30,2),"")</f>
@@ -22634,7 +22636,7 @@
         <v>67</v>
       </c>
       <c r="D806" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E806" s="5" t="n">
         <f aca="false">IF((F806+G806)&gt;0,ROUND((F806+G806)/30,2),"")</f>
@@ -22656,7 +22658,7 @@
         <v>67</v>
       </c>
       <c r="D807" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E807" s="5" t="str">
         <f aca="false">IF((F807+G807)&gt;0,ROUND((F807+G807)/30,2),"")</f>
@@ -22678,7 +22680,7 @@
         <v>67</v>
       </c>
       <c r="D808" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E808" s="5" t="str">
         <f aca="false">IF((F808+G808)&gt;0,ROUND((F808+G808)/30,2),"")</f>
@@ -22700,7 +22702,7 @@
         <v>67</v>
       </c>
       <c r="D809" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E809" s="5" t="n">
         <f aca="false">IF((F809+G809)&gt;0,ROUND((F809+G809)/30,2),"")</f>
@@ -22722,7 +22724,7 @@
         <v>67</v>
       </c>
       <c r="D810" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E810" s="5" t="str">
         <f aca="false">IF((F810+G810)&gt;0,ROUND((F810+G810)/30,2),"")</f>
@@ -22744,7 +22746,7 @@
         <v>67</v>
       </c>
       <c r="D811" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E811" s="5" t="str">
         <f aca="false">IF((F811+G811)&gt;0,ROUND((F811+G811)/30,2),"")</f>
@@ -22766,7 +22768,7 @@
         <v>67</v>
       </c>
       <c r="D812" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E812" s="5" t="n">
         <f aca="false">IF((F812+G812)&gt;0,ROUND((F812+G812)/30,2),"")</f>
@@ -22788,7 +22790,7 @@
         <v>67</v>
       </c>
       <c r="D813" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E813" s="5" t="n">
         <f aca="false">IF((F813+G813)&gt;0,ROUND((F813+G813)/30,2),"")</f>
@@ -22810,7 +22812,7 @@
         <v>67</v>
       </c>
       <c r="D814" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E814" s="5" t="n">
         <f aca="false">IF((F814+G814)&gt;0,ROUND((F814+G814)/30,2),"")</f>
@@ -22832,7 +22834,7 @@
         <v>67</v>
       </c>
       <c r="D815" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E815" s="5" t="n">
         <f aca="false">IF((F815+G815)&gt;0,ROUND((F815+G815)/30,2),"")</f>
@@ -22854,7 +22856,7 @@
         <v>67</v>
       </c>
       <c r="D816" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E816" s="5" t="n">
         <f aca="false">IF((F816+G816)&gt;0,ROUND((F816+G816)/30,2),"")</f>
@@ -22876,7 +22878,7 @@
         <v>67</v>
       </c>
       <c r="D817" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E817" s="5" t="n">
         <f aca="false">IF((F817+G817)&gt;0,ROUND((F817+G817)/30,2),"")</f>
@@ -22898,7 +22900,7 @@
         <v>75</v>
       </c>
       <c r="D818" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E818" s="5" t="n">
         <f aca="false">IF((F818+G818)&gt;0,ROUND((F818+G818)/30,2),"")</f>
@@ -22920,14 +22922,14 @@
         <v>75</v>
       </c>
       <c r="D819" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E819" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="E819" s="5" t="str">
         <f aca="false">IF((F819+G819)&gt;0,ROUND((F819+G819)/30,2),"")</f>
-        <v>66.67</v>
+        <v/>
       </c>
       <c r="F819" s="5" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="G819" s="5"/>
     </row>
@@ -22942,7 +22944,7 @@
         <v>75</v>
       </c>
       <c r="D820" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E820" s="5" t="n">
         <f aca="false">IF((F820+G820)&gt;0,ROUND((F820+G820)/30,2),"")</f>
@@ -22964,7 +22966,7 @@
         <v>75</v>
       </c>
       <c r="D821" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E821" s="5" t="str">
         <f aca="false">IF((F821+G821)&gt;0,ROUND((F821+G821)/30,2),"")</f>
@@ -22986,7 +22988,7 @@
         <v>75</v>
       </c>
       <c r="D822" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E822" s="5" t="n">
         <f aca="false">IF((F822+G822)&gt;0,ROUND((F822+G822)/30,2),"")</f>
@@ -23008,7 +23010,7 @@
         <v>75</v>
       </c>
       <c r="D823" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E823" s="5" t="n">
         <f aca="false">IF((F823+G823)&gt;0,ROUND((F823+G823)/30,2),"")</f>
@@ -23030,7 +23032,7 @@
         <v>75</v>
       </c>
       <c r="D824" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E824" s="5" t="str">
         <f aca="false">IF((F824+G824)&gt;0,ROUND((F824+G824)/30,2),"")</f>
@@ -23052,7 +23054,7 @@
         <v>75</v>
       </c>
       <c r="D825" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E825" s="5" t="n">
         <f aca="false">IF((F825+G825)&gt;0,ROUND((F825+G825)/30,2),"")</f>
@@ -23074,7 +23076,7 @@
         <v>75</v>
       </c>
       <c r="D826" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E826" s="5" t="str">
         <f aca="false">IF((F826+G826)&gt;0,ROUND((F826+G826)/30,2),"")</f>
@@ -23096,14 +23098,14 @@
         <v>75</v>
       </c>
       <c r="D827" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E827" s="5" t="n">
         <f aca="false">IF((F827+G827)&gt;0,ROUND((F827+G827)/30,2),"")</f>
-        <v>66.67</v>
+        <v>40</v>
       </c>
       <c r="F827" s="5" t="n">
-        <v>2000</v>
+        <v>1200</v>
       </c>
       <c r="G827" s="5"/>
     </row>
@@ -23118,7 +23120,7 @@
         <v>75</v>
       </c>
       <c r="D828" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E828" s="5" t="n">
         <f aca="false">IF((F828+G828)&gt;0,ROUND((F828+G828)/30,2),"")</f>
@@ -23140,7 +23142,7 @@
         <v>75</v>
       </c>
       <c r="D829" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E829" s="5" t="n">
         <f aca="false">IF((F829+G829)&gt;0,ROUND((F829+G829)/30,2),"")</f>
@@ -23162,7 +23164,7 @@
         <v>75</v>
       </c>
       <c r="D830" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E830" s="5" t="n">
         <f aca="false">IF((F830+G830)&gt;0,ROUND((F830+G830)/30,2),"")</f>
@@ -23184,7 +23186,7 @@
         <v>75</v>
       </c>
       <c r="D831" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E831" s="5" t="str">
         <f aca="false">IF((F831+G831)&gt;0,ROUND((F831+G831)/30,2),"")</f>
@@ -23206,7 +23208,7 @@
         <v>75</v>
       </c>
       <c r="D832" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E832" s="5" t="n">
         <f aca="false">IF((F832+G832)&gt;0,ROUND((F832+G832)/30,2),"")</f>
@@ -23228,7 +23230,7 @@
         <v>75</v>
       </c>
       <c r="D833" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E833" s="5" t="str">
         <f aca="false">IF((F833+G833)&gt;0,ROUND((F833+G833)/30,2),"")</f>
@@ -23250,7 +23252,7 @@
         <v>75</v>
       </c>
       <c r="D834" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E834" s="5" t="n">
         <f aca="false">IF((F834+G834)&gt;0,ROUND((F834+G834)/30,2),"")</f>
@@ -23272,7 +23274,7 @@
         <v>75</v>
       </c>
       <c r="D835" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E835" s="5" t="n">
         <f aca="false">IF((F835+G835)&gt;0,ROUND((F835+G835)/30,2),"")</f>
@@ -23294,7 +23296,7 @@
         <v>75</v>
       </c>
       <c r="D836" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E836" s="5" t="n">
         <f aca="false">IF((F836+G836)&gt;0,ROUND((F836+G836)/30,2),"")</f>
@@ -23316,7 +23318,7 @@
         <v>75</v>
       </c>
       <c r="D837" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E837" s="5" t="n">
         <f aca="false">IF((F837+G837)&gt;0,ROUND((F837+G837)/30,2),"")</f>
@@ -23338,7 +23340,7 @@
         <v>75</v>
       </c>
       <c r="D838" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E838" s="5" t="n">
         <f aca="false">IF((F838+G838)&gt;0,ROUND((F838+G838)/30,2),"")</f>
@@ -23360,7 +23362,7 @@
         <v>75</v>
       </c>
       <c r="D839" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E839" s="5" t="n">
         <f aca="false">IF((F839+G839)&gt;0,ROUND((F839+G839)/30,2),"")</f>
@@ -23382,7 +23384,7 @@
         <v>75</v>
       </c>
       <c r="D840" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E840" s="5" t="str">
         <f aca="false">IF((F840+G840)&gt;0,ROUND((F840+G840)/30,2),"")</f>
@@ -23404,7 +23406,7 @@
         <v>75</v>
       </c>
       <c r="D841" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E841" s="5" t="n">
         <f aca="false">IF((F841+G841)&gt;0,ROUND((F841+G841)/30,2),"")</f>
@@ -23426,7 +23428,7 @@
         <v>75</v>
       </c>
       <c r="D842" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E842" s="5" t="n">
         <f aca="false">IF((F842+G842)&gt;0,ROUND((F842+G842)/30,2),"")</f>
@@ -23448,7 +23450,7 @@
         <v>75</v>
       </c>
       <c r="D843" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E843" s="5" t="n">
         <f aca="false">IF((F843+G843)&gt;0,ROUND((F843+G843)/30,2),"")</f>
@@ -23470,7 +23472,7 @@
         <v>75</v>
       </c>
       <c r="D844" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E844" s="5" t="n">
         <f aca="false">IF((F844+G844)&gt;0,ROUND((F844+G844)/30,2),"")</f>
@@ -23492,7 +23494,7 @@
         <v>75</v>
       </c>
       <c r="D845" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E845" s="5" t="n">
         <f aca="false">IF((F845+G845)&gt;0,ROUND((F845+G845)/30,2),"")</f>
@@ -23514,7 +23516,7 @@
         <v>75</v>
       </c>
       <c r="D846" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E846" s="5" t="n">
         <f aca="false">IF((F846+G846)&gt;0,ROUND((F846+G846)/30,2),"")</f>
@@ -23536,7 +23538,7 @@
         <v>75</v>
       </c>
       <c r="D847" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E847" s="5" t="str">
         <f aca="false">IF((F847+G847)&gt;0,ROUND((F847+G847)/30,2),"")</f>
@@ -23580,7 +23582,7 @@
         <v>75</v>
       </c>
       <c r="D849" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E849" s="5" t="n">
         <f aca="false">IF((F849+G849)&gt;0,ROUND((F849+G849)/30,2),"")</f>
@@ -23602,7 +23604,7 @@
         <v>75</v>
       </c>
       <c r="D850" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E850" s="5" t="n">
         <f aca="false">IF((F850+G850)&gt;0,ROUND((F850+G850)/30,2),"")</f>
@@ -23624,7 +23626,7 @@
         <v>75</v>
       </c>
       <c r="D851" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E851" s="5" t="str">
         <f aca="false">IF((F851+G851)&gt;0,ROUND((F851+G851)/30,2),"")</f>
@@ -23646,7 +23648,7 @@
         <v>75</v>
       </c>
       <c r="D852" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E852" s="5" t="str">
         <f aca="false">IF((F852+G852)&gt;0,ROUND((F852+G852)/30,2),"")</f>
@@ -23690,7 +23692,7 @@
         <v>75</v>
       </c>
       <c r="D854" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E854" s="5" t="n">
         <f aca="false">IF((F854+G854)&gt;0,ROUND((F854+G854)/30,2),"")</f>
@@ -23712,7 +23714,7 @@
         <v>75</v>
       </c>
       <c r="D855" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E855" s="5" t="n">
         <f aca="false">IF((F855+G855)&gt;0,ROUND((F855+G855)/30,2),"")</f>
@@ -23734,7 +23736,7 @@
         <v>75</v>
       </c>
       <c r="D856" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E856" s="5" t="n">
         <f aca="false">IF((F856+G856)&gt;0,ROUND((F856+G856)/30,2),"")</f>
@@ -23756,7 +23758,7 @@
         <v>75</v>
       </c>
       <c r="D857" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E857" s="5" t="n">
         <f aca="false">IF((F857+G857)&gt;0,ROUND((F857+G857)/30,2),"")</f>
@@ -23778,7 +23780,7 @@
         <v>75</v>
       </c>
       <c r="D858" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E858" s="5" t="n">
         <f aca="false">IF((F858+G858)&gt;0,ROUND((F858+G858)/30,2),"")</f>
@@ -23800,7 +23802,7 @@
         <v>75</v>
       </c>
       <c r="D859" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E859" s="5" t="n">
         <f aca="false">IF((F859+G859)&gt;0,ROUND((F859+G859)/30,2),"")</f>
@@ -23822,7 +23824,7 @@
         <v>75</v>
       </c>
       <c r="D860" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E860" s="5" t="n">
         <f aca="false">IF((F860+G860)&gt;0,ROUND((F860+G860)/30,2),"")</f>
@@ -23844,7 +23846,7 @@
         <v>75</v>
       </c>
       <c r="D861" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E861" s="5" t="n">
         <f aca="false">IF((F861+G861)&gt;0,ROUND((F861+G861)/30,2),"")</f>
@@ -23866,7 +23868,7 @@
         <v>75</v>
       </c>
       <c r="D862" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E862" s="5"/>
       <c r="F862" s="5" t="n">
@@ -23885,7 +23887,7 @@
         <v>75</v>
       </c>
       <c r="D863" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E863" s="5" t="n">
         <f aca="false">IF((F863+G863)&gt;0,ROUND((F863+G863)/30,2),"")</f>
@@ -23929,7 +23931,7 @@
         <v>75</v>
       </c>
       <c r="D865" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E865" s="5" t="n">
         <f aca="false">IF((F865+G865)&gt;0,ROUND((F865+G865)/30,2),"")</f>
@@ -23951,7 +23953,7 @@
         <v>75</v>
       </c>
       <c r="D866" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E866" s="5" t="n">
         <f aca="false">IF((F866+G866)&gt;0,ROUND((F866+G866)/30,2),"")</f>
@@ -23973,7 +23975,7 @@
         <v>75</v>
       </c>
       <c r="D867" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E867" s="5" t="n">
         <f aca="false">IF((F867+G867)&gt;0,ROUND((F867+G867)/30,2),"")</f>
@@ -23995,7 +23997,7 @@
         <v>75</v>
       </c>
       <c r="D868" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E868" s="5" t="str">
         <f aca="false">IF((F868+G868)&gt;0,ROUND((F868+G868)/30,2),"")</f>
@@ -24017,7 +24019,7 @@
         <v>75</v>
       </c>
       <c r="D869" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E869" s="5" t="str">
         <f aca="false">IF((F869+G869)&gt;0,ROUND((F869+G869)/30,2),"")</f>
@@ -24061,7 +24063,7 @@
         <v>75</v>
       </c>
       <c r="D871" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E871" s="5" t="n">
         <f aca="false">IF((F871+G871)&gt;0,ROUND((F871+G871)/30,2),"")</f>
@@ -24083,7 +24085,7 @@
         <v>75</v>
       </c>
       <c r="D872" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E872" s="5" t="str">
         <f aca="false">IF((F872+G872)&gt;0,ROUND((F872+G872)/30,2),"")</f>
@@ -24105,7 +24107,7 @@
         <v>75</v>
       </c>
       <c r="D873" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E873" s="5" t="str">
         <f aca="false">IF((F873+G873)&gt;0,ROUND((F873+G873)/30,2),"")</f>
@@ -24127,7 +24129,7 @@
         <v>75</v>
       </c>
       <c r="D874" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E874" s="5" t="n">
         <f aca="false">IF((F874+G874)&gt;0,ROUND((F874+G874)/30,2),"")</f>
@@ -24149,7 +24151,7 @@
         <v>75</v>
       </c>
       <c r="D875" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E875" s="5" t="n">
         <f aca="false">IF((F875+G875)&gt;0,ROUND((F875+G875)/30,2),"")</f>
@@ -24171,7 +24173,7 @@
         <v>75</v>
       </c>
       <c r="D876" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E876" s="5" t="n">
         <f aca="false">IF((F876+G876)&gt;0,ROUND((F876+G876)/30,2),"")</f>
@@ -24193,7 +24195,7 @@
         <v>75</v>
       </c>
       <c r="D877" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E877" s="5" t="n">
         <f aca="false">IF((F877+G877)&gt;0,ROUND((F877+G877)/30,2),"")</f>
@@ -24215,7 +24217,7 @@
         <v>75</v>
       </c>
       <c r="D878" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E878" s="5" t="n">
         <f aca="false">IF((F878+G878)&gt;0,ROUND((F878+G878)/30,2),"")</f>
@@ -24237,7 +24239,7 @@
         <v>75</v>
       </c>
       <c r="D879" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E879" s="5" t="str">
         <f aca="false">IF((F879+G879)&gt;0,ROUND((F879+G879)/30,2),"")</f>
@@ -24281,7 +24283,7 @@
         <v>75</v>
       </c>
       <c r="D881" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E881" s="5" t="n">
         <f aca="false">IF((F881+G881)&gt;0,ROUND((F881+G881)/30,2),"")</f>
@@ -24303,7 +24305,7 @@
         <v>75</v>
       </c>
       <c r="D882" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E882" s="5" t="str">
         <f aca="false">IF((F882+G882)&gt;0,ROUND((F882+G882)/30,2),"")</f>
@@ -24325,7 +24327,7 @@
         <v>75</v>
       </c>
       <c r="D883" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E883" s="5" t="n">
         <f aca="false">IF((F883+G883)&gt;0,ROUND((F883+G883)/30,2),"")</f>
@@ -24369,7 +24371,7 @@
         <v>75</v>
       </c>
       <c r="D885" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E885" s="5" t="n">
         <f aca="false">IF((F885+G885)&gt;0,ROUND((F885+G885)/30,2),"")</f>
@@ -24391,7 +24393,7 @@
         <v>75</v>
       </c>
       <c r="D886" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E886" s="5" t="n">
         <f aca="false">IF((F886+G886)&gt;0,ROUND((F886+G886)/30,2),"")</f>
@@ -24413,7 +24415,7 @@
         <v>75</v>
       </c>
       <c r="D887" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E887" s="5" t="n">
         <f aca="false">IF((F887+G887)&gt;0,ROUND((F887+G887)/30,2),"")</f>
@@ -24435,7 +24437,7 @@
         <v>75</v>
       </c>
       <c r="D888" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E888" s="5" t="n">
         <f aca="false">IF((F888+G888)&gt;0,ROUND((F888+G888)/30,2),"")</f>
@@ -24457,7 +24459,7 @@
         <v>75</v>
       </c>
       <c r="D889" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E889" s="5" t="n">
         <f aca="false">IF((F889+G889)&gt;0,ROUND((F889+G889)/30,2),"")</f>
@@ -24479,7 +24481,7 @@
         <v>75</v>
       </c>
       <c r="D890" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E890" s="5" t="str">
         <f aca="false">IF((F890+G890)&gt;0,ROUND((F890+G890)/30,2),"")</f>
@@ -24501,7 +24503,7 @@
         <v>75</v>
       </c>
       <c r="D891" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E891" s="5" t="n">
         <f aca="false">IF((F891+G891)&gt;0,ROUND((F891+G891)/30,2),"")</f>
@@ -24523,7 +24525,7 @@
         <v>75</v>
       </c>
       <c r="D892" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E892" s="5" t="n">
         <f aca="false">IF((F892+G892)&gt;0,ROUND((F892+G892)/30,2),"")</f>
@@ -24545,7 +24547,7 @@
         <v>75</v>
       </c>
       <c r="D893" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E893" s="5" t="n">
         <f aca="false">IF((F893+G893)&gt;0,ROUND((F893+G893)/30,2),"")</f>
@@ -24589,7 +24591,7 @@
         <v>75</v>
       </c>
       <c r="D895" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E895" s="5" t="n">
         <f aca="false">IF((F895+G895)&gt;0,ROUND((F895+G895)/30,2),"")</f>
@@ -24611,7 +24613,7 @@
         <v>75</v>
       </c>
       <c r="D896" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E896" s="5" t="str">
         <f aca="false">IF((F896+G896)&gt;0,ROUND((F896+G896)/30,2),"")</f>
@@ -24633,7 +24635,7 @@
         <v>75</v>
       </c>
       <c r="D897" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E897" s="5" t="n">
         <f aca="false">IF((F897+G897)&gt;0,ROUND((F897+G897)/30,2),"")</f>
@@ -24655,7 +24657,7 @@
         <v>75</v>
       </c>
       <c r="D898" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E898" s="5" t="str">
         <f aca="false">IF((F898+G898)&gt;0,ROUND((F898+G898)/30,2),"")</f>
@@ -24699,14 +24701,14 @@
         <v>75</v>
       </c>
       <c r="D900" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="E900" s="5" t="n">
+        <v>248</v>
+      </c>
+      <c r="E900" s="5" t="str">
         <f aca="false">IF((F900+G900)&gt;0,ROUND((F900+G900)/30,2),"")</f>
-        <v>1.67</v>
+        <v/>
       </c>
       <c r="F900" s="5" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="G900" s="5"/>
     </row>
@@ -24721,7 +24723,7 @@
         <v>75</v>
       </c>
       <c r="D901" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E901" s="5" t="str">
         <f aca="false">IF((F901+G901)&gt;0,ROUND((F901+G901)/30,2),"")</f>
@@ -24743,7 +24745,7 @@
         <v>75</v>
       </c>
       <c r="D902" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E902" s="5" t="n">
         <f aca="false">IF((F902+G902)&gt;0,ROUND((F902+G902)/30,2),"")</f>
@@ -24765,7 +24767,7 @@
         <v>75</v>
       </c>
       <c r="D903" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E903" s="5" t="n">
         <f aca="false">IF((F903+G903)&gt;0,ROUND((F903+G903)/30,2),"")</f>
@@ -24787,7 +24789,7 @@
         <v>75</v>
       </c>
       <c r="D904" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E904" s="5" t="n">
         <f aca="false">IF((F904+G904)&gt;0,ROUND((F904+G904)/30,2),"")</f>
@@ -24809,7 +24811,7 @@
         <v>75</v>
       </c>
       <c r="D905" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E905" s="5" t="n">
         <f aca="false">IF((F905+G905)&gt;0,ROUND((F905+G905)/30,2),"")</f>
@@ -24831,7 +24833,7 @@
         <v>75</v>
       </c>
       <c r="D906" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E906" s="5" t="n">
         <f aca="false">IF((F906+G906)&gt;0,ROUND((F906+G906)/30,2),"")</f>
@@ -24853,7 +24855,7 @@
         <v>75</v>
       </c>
       <c r="D907" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E907" s="5" t="n">
         <f aca="false">IF((F907+G907)&gt;0,ROUND((F907+G907)/30,2),"")</f>
@@ -24919,7 +24921,7 @@
         <v>75</v>
       </c>
       <c r="D910" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E910" s="5" t="n">
         <f aca="false">IF((F910+G910)&gt;0,ROUND((F910+G910)/30,2),"")</f>
@@ -24941,7 +24943,7 @@
         <v>75</v>
       </c>
       <c r="D911" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E911" s="5" t="n">
         <f aca="false">IF((F911+G911)&gt;0,ROUND((F911+G911)/30,2),"")</f>
@@ -24963,7 +24965,7 @@
         <v>75</v>
       </c>
       <c r="D912" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E912" s="5" t="n">
         <f aca="false">IF((F912+G912)&gt;0,ROUND((F912+G912)/30,2),"")</f>
@@ -25007,7 +25009,7 @@
         <v>75</v>
       </c>
       <c r="D914" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E914" s="5" t="n">
         <f aca="false">IF((F914+G914)&gt;0,ROUND((F914+G914)/30,2),"")</f>
@@ -25051,7 +25053,7 @@
         <v>75</v>
       </c>
       <c r="D916" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E916" s="5" t="n">
         <f aca="false">IF((F916+G916)&gt;0,ROUND((F916+G916)/30,2),"")</f>
@@ -25073,7 +25075,7 @@
         <v>75</v>
       </c>
       <c r="D917" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E917" s="5" t="n">
         <f aca="false">IF((F917+G917)&gt;0,ROUND((F917+G917)/30,2),"")</f>
@@ -25095,7 +25097,7 @@
         <v>75</v>
       </c>
       <c r="D918" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E918" s="5" t="n">
         <f aca="false">IF((F918+G918)&gt;0,ROUND((F918+G918)/30,2),"")</f>
@@ -25139,7 +25141,7 @@
         <v>75</v>
       </c>
       <c r="D920" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E920" s="5" t="n">
         <f aca="false">IF((F920+G920)&gt;0,ROUND((F920+G920)/30,2),"")</f>
@@ -25161,7 +25163,7 @@
         <v>75</v>
       </c>
       <c r="D921" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E921" s="5" t="n">
         <f aca="false">IF((F921+G921)&gt;0,ROUND((F921+G921)/30,2),"")</f>
@@ -25183,7 +25185,7 @@
         <v>81</v>
       </c>
       <c r="D922" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E922" s="5" t="n">
         <f aca="false">IF((F922+G922)&gt;0,ROUND((F922+G922)/30,2),"")</f>
@@ -25205,7 +25207,7 @@
         <v>81</v>
       </c>
       <c r="D923" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E923" s="5" t="n">
         <f aca="false">IF((F923+G923)&gt;0,ROUND((F923+G923)/30,2),"")</f>
@@ -25227,7 +25229,7 @@
         <v>81</v>
       </c>
       <c r="D924" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E924" s="5" t="n">
         <f aca="false">IF((F924+G924)&gt;0,ROUND((F924+G924)/30,2),"")</f>
@@ -25249,7 +25251,7 @@
         <v>81</v>
       </c>
       <c r="D925" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E925" s="5" t="n">
         <f aca="false">IF((F925+G925)&gt;0,ROUND((F925+G925)/30,2),"")</f>
@@ -25271,7 +25273,7 @@
         <v>81</v>
       </c>
       <c r="D926" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E926" s="5" t="n">
         <f aca="false">IF((F926+G926)&gt;0,ROUND((F926+G926)/30,2),"")</f>
@@ -25293,7 +25295,7 @@
         <v>81</v>
       </c>
       <c r="D927" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E927" s="5" t="n">
         <f aca="false">IF((F927+G927)&gt;0,ROUND((F927+G927)/30,2),"")</f>
@@ -25315,7 +25317,7 @@
         <v>81</v>
       </c>
       <c r="D928" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E928" s="5" t="n">
         <f aca="false">IF((F928+G928)&gt;0,ROUND((F928+G928)/30,2),"")</f>
@@ -25337,7 +25339,7 @@
         <v>81</v>
       </c>
       <c r="D929" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E929" s="5" t="n">
         <f aca="false">IF((F929+G929)&gt;0,ROUND((F929+G929)/30,2),"")</f>
@@ -25359,7 +25361,7 @@
         <v>81</v>
       </c>
       <c r="D930" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E930" s="5" t="n">
         <f aca="false">IF((F930+G930)&gt;0,ROUND((F930+G930)/30,2),"")</f>
@@ -25381,7 +25383,7 @@
         <v>81</v>
       </c>
       <c r="D931" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E931" s="5" t="n">
         <f aca="false">IF((F931+G931)&gt;0,ROUND((F931+G931)/30,2),"")</f>
@@ -25403,7 +25405,7 @@
         <v>81</v>
       </c>
       <c r="D932" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E932" s="5" t="n">
         <f aca="false">IF((F932+G932)&gt;0,ROUND((F932+G932)/30,2),"")</f>
@@ -25425,7 +25427,7 @@
         <v>81</v>
       </c>
       <c r="D933" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E933" s="5" t="n">
         <f aca="false">IF((F933+G933)&gt;0,ROUND((F933+G933)/30,2),"")</f>
@@ -25447,7 +25449,7 @@
         <v>81</v>
       </c>
       <c r="D934" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E934" s="5" t="n">
         <f aca="false">IF((F934+G934)&gt;0,ROUND((F934+G934)/30,2),"")</f>
@@ -25469,7 +25471,7 @@
         <v>81</v>
       </c>
       <c r="D935" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E935" s="5" t="n">
         <f aca="false">IF((F935+G935)&gt;0,ROUND((F935+G935)/30,2),"")</f>
@@ -25491,7 +25493,7 @@
         <v>81</v>
       </c>
       <c r="D936" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E936" s="5" t="n">
         <f aca="false">IF((F936+G936)&gt;0,ROUND((F936+G936)/30,2),"")</f>
@@ -25513,7 +25515,7 @@
         <v>81</v>
       </c>
       <c r="D937" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E937" s="5" t="n">
         <f aca="false">IF((F937+G937)&gt;0,ROUND((F937+G937)/30,2),"")</f>
@@ -25535,7 +25537,7 @@
         <v>81</v>
       </c>
       <c r="D938" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E938" s="5" t="n">
         <f aca="false">IF((F938+G938)&gt;0,ROUND((F938+G938)/30,2),"")</f>
@@ -25557,7 +25559,7 @@
         <v>81</v>
       </c>
       <c r="D939" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E939" s="5" t="n">
         <f aca="false">IF((F939+G939)&gt;0,ROUND((F939+G939)/30,2),"")</f>
@@ -25579,7 +25581,7 @@
         <v>81</v>
       </c>
       <c r="D940" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E940" s="5" t="n">
         <f aca="false">IF((F940+G940)&gt;0,ROUND((F940+G940)/30,2),"")</f>
@@ -25601,7 +25603,7 @@
         <v>81</v>
       </c>
       <c r="D941" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E941" s="5" t="n">
         <f aca="false">IF((F941+G941)&gt;0,ROUND((F941+G941)/30,2),"")</f>
@@ -25623,7 +25625,7 @@
         <v>81</v>
       </c>
       <c r="D942" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E942" s="5" t="n">
         <f aca="false">IF((F942+G942)&gt;0,ROUND((F942+G942)/30,2),"")</f>
@@ -25645,7 +25647,7 @@
         <v>81</v>
       </c>
       <c r="D943" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E943" s="5" t="n">
         <f aca="false">IF((F943+G943)&gt;0,ROUND((F943+G943)/30,2),"")</f>
@@ -25667,7 +25669,7 @@
         <v>81</v>
       </c>
       <c r="D944" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E944" s="5" t="n">
         <f aca="false">IF((F944+G944)&gt;0,ROUND((F944+G944)/30,2),"")</f>
@@ -25689,7 +25691,7 @@
         <v>81</v>
       </c>
       <c r="D945" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E945" s="5" t="n">
         <f aca="false">IF((F945+G945)&gt;0,ROUND((F945+G945)/30,2),"")</f>
@@ -25711,7 +25713,7 @@
         <v>81</v>
       </c>
       <c r="D946" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E946" s="5" t="n">
         <f aca="false">IF((F946+G946)&gt;0,ROUND((F946+G946)/30,2),"")</f>
@@ -25733,7 +25735,7 @@
         <v>81</v>
       </c>
       <c r="D947" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E947" s="5" t="n">
         <f aca="false">IF((F947+G947)&gt;0,ROUND((F947+G947)/30,2),"")</f>
@@ -25755,7 +25757,7 @@
         <v>81</v>
       </c>
       <c r="D948" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E948" s="5" t="n">
         <f aca="false">IF((F948+G948)&gt;0,ROUND((F948+G948)/30,2),"")</f>
@@ -25777,7 +25779,7 @@
         <v>81</v>
       </c>
       <c r="D949" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E949" s="5" t="n">
         <f aca="false">IF((F949+G949)&gt;0,ROUND((F949+G949)/30,2),"")</f>
@@ -25799,7 +25801,7 @@
         <v>81</v>
       </c>
       <c r="D950" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E950" s="5" t="n">
         <f aca="false">IF((F950+G950)&gt;0,ROUND((F950+G950)/30,2),"")</f>
@@ -25821,7 +25823,7 @@
         <v>81</v>
       </c>
       <c r="D951" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E951" s="5" t="n">
         <f aca="false">IF((F951+G951)&gt;0,ROUND((F951+G951)/30,2),"")</f>
@@ -25843,7 +25845,7 @@
         <v>81</v>
       </c>
       <c r="D952" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E952" s="5" t="n">
         <f aca="false">IF((F952+G952)&gt;0,ROUND((F952+G952)/30,2),"")</f>
@@ -25865,7 +25867,7 @@
         <v>81</v>
       </c>
       <c r="D953" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E953" s="5" t="n">
         <f aca="false">IF((F953+G953)&gt;0,ROUND((F953+G953)/30,2),"")</f>
@@ -25887,7 +25889,7 @@
         <v>81</v>
       </c>
       <c r="D954" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E954" s="5" t="n">
         <f aca="false">IF((F954+G954)&gt;0,ROUND((F954+G954)/30,2),"")</f>
@@ -25909,7 +25911,7 @@
         <v>86</v>
       </c>
       <c r="D955" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E955" s="5" t="n">
         <f aca="false">IF((F955+G955)&gt;0,ROUND((F955+G955)/30,2),"")</f>
@@ -25931,7 +25933,7 @@
         <v>86</v>
       </c>
       <c r="D956" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E956" s="5" t="n">
         <f aca="false">IF((F956+G956)&gt;0,ROUND((F956+G956)/30,2),"")</f>
@@ -25953,7 +25955,7 @@
         <v>86</v>
       </c>
       <c r="D957" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E957" s="5" t="n">
         <f aca="false">IF((F957+G957)&gt;0,ROUND((F957+G957)/30,2),"")</f>
@@ -25975,7 +25977,7 @@
         <v>86</v>
       </c>
       <c r="D958" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E958" s="5" t="str">
         <f aca="false">IF((F958+G958)&gt;0,ROUND((F958+G958)/30,2),"")</f>
@@ -25997,7 +25999,7 @@
         <v>86</v>
       </c>
       <c r="D959" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E959" s="5" t="n">
         <f aca="false">IF((F959+G959)&gt;0,ROUND((F959+G959)/30,2),"")</f>
@@ -26019,7 +26021,7 @@
         <v>86</v>
       </c>
       <c r="D960" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E960" s="5" t="n">
         <f aca="false">IF((F960+G960)&gt;0,ROUND((F960+G960)/30,2),"")</f>
@@ -26041,7 +26043,7 @@
         <v>86</v>
       </c>
       <c r="D961" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E961" s="5" t="n">
         <f aca="false">IF((F961+G961)&gt;0,ROUND((F961+G961)/30,2),"")</f>
@@ -26063,7 +26065,7 @@
         <v>86</v>
       </c>
       <c r="D962" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E962" s="5" t="str">
         <f aca="false">IF((F962+G962)&gt;0,ROUND((F962+G962)/30,2),"")</f>
@@ -26085,7 +26087,7 @@
         <v>86</v>
       </c>
       <c r="D963" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E963" s="5" t="n">
         <f aca="false">IF((F963+G963)&gt;0,ROUND((F963+G963)/30,2),"")</f>
@@ -26107,7 +26109,7 @@
         <v>86</v>
       </c>
       <c r="D964" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E964" s="5" t="n">
         <f aca="false">IF((F964+G964)&gt;0,ROUND((F964+G964)/30,2),"")</f>
@@ -26129,7 +26131,7 @@
         <v>86</v>
       </c>
       <c r="D965" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E965" s="5" t="n">
         <f aca="false">IF((F965+G965)&gt;0,ROUND((F965+G965)/30,2),"")</f>
@@ -26151,7 +26153,7 @@
         <v>86</v>
       </c>
       <c r="D966" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E966" s="5" t="n">
         <f aca="false">IF((F966+G966)&gt;0,ROUND((F966+G966)/30,2),"")</f>
@@ -26173,7 +26175,7 @@
         <v>86</v>
       </c>
       <c r="D967" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E967" s="5" t="n">
         <f aca="false">IF((F967+G967)&gt;0,ROUND((F967+G967)/30,2),"")</f>
@@ -26195,7 +26197,7 @@
         <v>86</v>
       </c>
       <c r="D968" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E968" s="5" t="str">
         <f aca="false">IF((F968+G968)&gt;0,ROUND((F968+G968)/30,2),"")</f>
@@ -26217,7 +26219,7 @@
         <v>86</v>
       </c>
       <c r="D969" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E969" s="5" t="n">
         <f aca="false">IF((F969+G969)&gt;0,ROUND((F969+G969)/30,2),"")</f>
@@ -26239,7 +26241,7 @@
         <v>86</v>
       </c>
       <c r="D970" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E970" s="5" t="n">
         <f aca="false">IF((F970+G970)&gt;0,ROUND((F970+G970)/30,2),"")</f>
@@ -26261,7 +26263,7 @@
         <v>86</v>
       </c>
       <c r="D971" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E971" s="5" t="n">
         <f aca="false">IF((F971+G971)&gt;0,ROUND((F971+G971)/30,2),"")</f>
@@ -26283,7 +26285,7 @@
         <v>86</v>
       </c>
       <c r="D972" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E972" s="5" t="str">
         <f aca="false">IF((F972+G972)&gt;0,ROUND((F972+G972)/30,2),"")</f>
@@ -26305,7 +26307,7 @@
         <v>86</v>
       </c>
       <c r="D973" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E973" s="5" t="n">
         <f aca="false">IF((F973+G973)&gt;0,ROUND((F973+G973)/30,2),"")</f>
@@ -26327,7 +26329,7 @@
         <v>86</v>
       </c>
       <c r="D974" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E974" s="5" t="n">
         <f aca="false">IF((F974+G974)&gt;0,ROUND((F974+G974)/30,2),"")</f>
@@ -26349,7 +26351,7 @@
         <v>86</v>
       </c>
       <c r="D975" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E975" s="5" t="n">
         <f aca="false">IF((F975+G975)&gt;0,ROUND((F975+G975)/30,2),"")</f>
@@ -26371,7 +26373,7 @@
         <v>86</v>
       </c>
       <c r="D976" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E976" s="5" t="n">
         <f aca="false">IF((F976+G976)&gt;0,ROUND((F976+G976)/30,2),"")</f>
@@ -26393,7 +26395,7 @@
         <v>86</v>
       </c>
       <c r="D977" s="8" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="E977" s="5" t="n">
         <f aca="false">IF((F977+G977)&gt;0,ROUND((F977+G977)/30,2),"")</f>
@@ -33214,10 +33216,10 @@
       <c r="D1318" s="9"/>
       <c r="E1318" s="5" t="n">
         <f aca="false">IF((F1318+G1318)&gt;0,ROUND((F1318+G1318)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F1318" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G1318" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -5602,7 +5602,9 @@
         <f aca="false">IF((F33+G33)&gt;0,ROUND((F33+G33)/30,2),"")</f>
         <v>100</v>
       </c>
-      <c r="F33" s="5"/>
+      <c r="F33" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="G33" s="5" t="n">
         <v>3000</v>
       </c>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -23036,12 +23036,12 @@
       <c r="D824" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="E824" s="5" t="str">
+      <c r="E824" s="5" t="n">
         <f aca="false">IF((F824+G824)&gt;0,ROUND((F824+G824)/30,2),"")</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="F824" s="5" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="G824" s="5"/>
     </row>

--- a/Minimal_zaxiralar/Min_Zaxira.xlsx
+++ b/Minimal_zaxiralar/Min_Zaxira.xlsx
@@ -23915,10 +23915,10 @@
       </c>
       <c r="E864" s="5" t="n">
         <f aca="false">IF((F864+G864)&gt;0,ROUND((F864+G864)/30,2),"")</f>
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="F864" s="5" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="G864" s="5"/>
     </row>
@@ -24267,10 +24267,10 @@
       </c>
       <c r="E880" s="5" t="n">
         <f aca="false">IF((F880+G880)&gt;0,ROUND((F880+G880)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F880" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G880" s="5"/>
     </row>
@@ -24355,10 +24355,10 @@
       </c>
       <c r="E884" s="5" t="n">
         <f aca="false">IF((F884+G884)&gt;0,ROUND((F884+G884)/30,2),"")</f>
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="F884" s="5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G884" s="5"/>
     </row>
@@ -24575,10 +24575,10 @@
       </c>
       <c r="E894" s="5" t="n">
         <f aca="false">IF((F894+G894)&gt;0,ROUND((F894+G894)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F894" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G894" s="5"/>
     </row>
@@ -24905,10 +24905,10 @@
       </c>
       <c r="E909" s="5" t="n">
         <f aca="false">IF((F909+G909)&gt;0,ROUND((F909+G909)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1.33</v>
       </c>
       <c r="F909" s="5" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G909" s="5"/>
     </row>
@@ -24993,10 +24993,10 @@
       </c>
       <c r="E913" s="5" t="n">
         <f aca="false">IF((F913+G913)&gt;0,ROUND((F913+G913)/30,2),"")</f>
-        <v>1.67</v>
+        <v>1</v>
       </c>
       <c r="F913" s="5" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="G913" s="5"/>
     </row>
@@ -25037,10 +25037,10 @@
       </c>
       <c r="E915" s="5" t="n">
         <f aca="false">IF((F915+G915)&gt;0,ROUND((F915+G915)/30,2),"")</f>
-        <v>1.67</v>
+        <v>0.67</v>
       </c>
       <c r="F915" s="5" t="n">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="G915" s="5"/>
     </row>
@@ -25125,10 +25125,10 @@
       </c>
       <c r="E919" s="5" t="n">
         <f aca="false">IF((F919+G919)&gt;0,ROUND((F919+G919)/30,2),"")</f>
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="F919" s="5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G919" s="5"/>
     </row>
@@ -34120,10 +34120,10 @@
       </c>
       <c r="E1363" s="5" t="n">
         <f aca="false">IF((F1363+G1363)&gt;0,ROUND((F1363+G1363)/30,2),"")</f>
-        <v>1.67</v>
+        <v>0.5</v>
       </c>
       <c r="F1363" s="5" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="G1363" s="5"/>
     </row>
